--- a/Översikt FÄRGELANDA.xlsx
+++ b/Översikt FÄRGELANDA.xlsx
@@ -601,7 +601,7 @@
         <v>44785</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45904</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>45303</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44935</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>45242</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>46239</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>45547</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>46175</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>45078</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>44504</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>44453</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>45474</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>45714</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>44911</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>45246</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>45766</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>45153</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>44837</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>44490</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>44595</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>44557</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>44490</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>44516</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>44525</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>44475</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>44526</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>44670</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>44658</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>44602</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>44496</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         <v>44566</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>44684</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>44593</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         <v>44858</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>44550</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>44711</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>44670</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>44518</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         <v>44572</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         <v>44686</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>44750</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>44490</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>44777</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v>44490</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4427,7 +4427,7 @@
         <v>44636</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>44465</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>45273</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>45418</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>45419</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         <v>44928</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>44581</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         <v>45315</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         <v>44706</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>44706</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>45091</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
         <v>44899</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         <v>45558</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5381,7 +5381,7 @@
         <v>45049</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>45384</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>45687</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         <v>44998</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
         <v>44600</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>45079</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         <v>45244</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>44916</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>45740</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         <v>44846</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>45758</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         <v>45196</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>45071</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>45209</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>44595</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6476,7 +6476,7 @@
         <v>44488</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>45321</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         <v>44459</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>44974</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         <v>45351</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
         <v>45351</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>44501</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6987,7 +6987,7 @@
         <v>44578</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         <v>44469</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>45212</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7206,7 +7206,7 @@
         <v>44546</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         <v>45180</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>45260</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7425,7 +7425,7 @@
         <v>44522</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         <v>45280</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7571,7 +7571,7 @@
         <v>44939</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7644,7 +7644,7 @@
         <v>45015</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>45049</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>45614</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7863,7 +7863,7 @@
         <v>45036</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>44571</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         <v>45247</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8082,7 +8082,7 @@
         <v>44893</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8155,7 +8155,7 @@
         <v>44935</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>45582</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         <v>45280</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         <v>45638</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         <v>44526</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8520,7 +8520,7 @@
         <v>45693</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8593,7 +8593,7 @@
         <v>45252</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         <v>45252</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         <v>45757</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         <v>45524</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8885,7 +8885,7 @@
         <v>45890</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>44470</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         <v>45777</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         <v>45904</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9177,7 +9177,7 @@
         <v>45730</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9250,7 +9250,7 @@
         <v>45895</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>45894</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>45894</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>45098</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>45491</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         <v>45362</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>45950</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9761,7 +9761,7 @@
         <v>45904</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>44578</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>45267</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9980,7 +9980,7 @@
         <v>45153</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10053,7 +10053,7 @@
         <v>45642</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10126,7 +10126,7 @@
         <v>45478</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10199,7 +10199,7 @@
         <v>45684</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10277,7 +10277,7 @@
         <v>45917</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10350,7 +10350,7 @@
         <v>45918</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10423,7 +10423,7 @@
         <v>45308</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10496,7 +10496,7 @@
         <v>46038</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>45530</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>45761</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>44917</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10788,7 +10788,7 @@
         <v>44837</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10861,7 +10861,7 @@
         <v>45740</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>45452</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11007,7 +11007,7 @@
         <v>45932</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11080,7 +11080,7 @@
         <v>44896</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11153,7 +11153,7 @@
         <v>45643</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11226,7 +11226,7 @@
         <v>45730</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11299,7 +11299,7 @@
         <v>44768</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11372,7 +11372,7 @@
         <v>45937</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11445,7 +11445,7 @@
         <v>45946</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11518,7 +11518,7 @@
         <v>45946</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11591,7 +11591,7 @@
         <v>45949</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
         <v>45950</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11737,7 +11737,7 @@
         <v>45950</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11810,7 +11810,7 @@
         <v>45392</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11883,7 +11883,7 @@
         <v>45293</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11956,7 +11956,7 @@
         <v>44638</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12029,7 +12029,7 @@
         <v>45957</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12102,7 +12102,7 @@
         <v>46150</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>45958</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12248,7 +12248,7 @@
         <v>45965</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12321,7 +12321,7 @@
         <v>45965</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12394,7 +12394,7 @@
         <v>45965</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         <v>44901</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12540,7 +12540,7 @@
         <v>45969</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12613,7 +12613,7 @@
         <v>45969</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12686,7 +12686,7 @@
         <v>45071</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
         <v>44488</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12832,7 +12832,7 @@
         <v>45975</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>45975</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12988,7 +12988,7 @@
         <v>45687</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13061,7 +13061,7 @@
         <v>45040</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13134,7 +13134,7 @@
         <v>45420</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13207,7 +13207,7 @@
         <v>45078</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13280,7 +13280,7 @@
         <v>44686</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
         <v>44958</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13426,7 +13426,7 @@
         <v>45643</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13499,7 +13499,7 @@
         <v>45987</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13572,7 +13572,7 @@
         <v>45989</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
         <v>45936</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13723,7 +13723,7 @@
         <v>45407</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13796,7 +13796,7 @@
         <v>45034</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13869,7 +13869,7 @@
         <v>45958</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>44977</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>45145</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>45712</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14161,7 +14161,7 @@
         <v>46166</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14234,7 +14234,7 @@
         <v>45705</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14307,7 +14307,7 @@
         <v>45987</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14380,7 +14380,7 @@
         <v>45775</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14453,7 +14453,7 @@
         <v>46007</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14526,7 +14526,7 @@
         <v>45764</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14599,7 +14599,7 @@
         <v>45558</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         <v>44841</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14745,7 +14745,7 @@
         <v>44899</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14818,7 +14818,7 @@
         <v>45558</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14891,7 +14891,7 @@
         <v>45215</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14964,7 +14964,7 @@
         <v>45470</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15037,7 +15037,7 @@
         <v>44869</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15110,7 +15110,7 @@
         <v>45643</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15183,7 +15183,7 @@
         <v>45532</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>45202</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15329,7 +15329,7 @@
         <v>46037</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15402,7 +15402,7 @@
         <v>45062</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15475,7 +15475,7 @@
         <v>44893</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15548,7 +15548,7 @@
         <v>45736</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15621,7 +15621,7 @@
         <v>45139</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15694,7 +15694,7 @@
         <v>46055</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15767,7 +15767,7 @@
         <v>45467</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15840,7 +15840,7 @@
         <v>46052</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15913,7 +15913,7 @@
         <v>46055</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15986,7 +15986,7 @@
         <v>46055</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
         <v>44883</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16132,7 +16132,7 @@
         <v>46058</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16210,7 +16210,7 @@
         <v>46063</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16283,7 +16283,7 @@
         <v>46177</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>44977</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16429,7 +16429,7 @@
         <v>46066</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16507,7 +16507,7 @@
         <v>45685</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16580,7 +16580,7 @@
         <v>46069</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>45159</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16731,7 +16731,7 @@
         <v>46069</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>46071</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>46071</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16950,7 +16950,7 @@
         <v>46076</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17028,7 +17028,7 @@
         <v>46080</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17101,7 +17101,7 @@
         <v>46080</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17174,7 +17174,7 @@
         <v>45218</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17247,7 +17247,7 @@
         <v>46188</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>45239</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17393,7 +17393,7 @@
         <v>46086</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17466,7 +17466,7 @@
         <v>46087</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17539,7 +17539,7 @@
         <v>46091</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17612,7 +17612,7 @@
         <v>46190</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17685,7 +17685,7 @@
         <v>46195</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17758,7 +17758,7 @@
         <v>46195</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>44544</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
         <v>46101</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17977,7 +17977,7 @@
         <v>44592</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18050,7 +18050,7 @@
         <v>45168</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>46107</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18196,7 +18196,7 @@
         <v>44811</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18269,7 +18269,7 @@
         <v>44917</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>45643</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18415,7 +18415,7 @@
         <v>45049</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18488,7 +18488,7 @@
         <v>46113</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18561,7 +18561,7 @@
         <v>46119</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18634,7 +18634,7 @@
         <v>45237</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18707,7 +18707,7 @@
         <v>46121</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18785,7 +18785,7 @@
         <v>46121</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18863,7 +18863,7 @@
         <v>46121</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>46121</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19014,7 +19014,7 @@
         <v>46121</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19087,7 +19087,7 @@
         <v>46124</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19160,7 +19160,7 @@
         <v>46202</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19238,7 +19238,7 @@
         <v>46244</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19311,7 +19311,7 @@
         <v>46125</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19389,7 +19389,7 @@
         <v>46204</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19462,7 +19462,7 @@
         <v>44873</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19535,7 +19535,7 @@
         <v>46134</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>45894</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19681,7 +19681,7 @@
         <v>45481</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19754,7 +19754,7 @@
         <v>45271</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19827,7 +19827,7 @@
         <v>46136</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19900,7 +19900,7 @@
         <v>45693</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -19973,7 +19973,7 @@
         <v>45532</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>45324</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20119,7 +20119,7 @@
         <v>45170</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>46251</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20265,7 +20265,7 @@
         <v>45141</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20338,7 +20338,7 @@
         <v>46248</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20411,7 +20411,7 @@
         <v>46248</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20484,7 +20484,7 @@
         <v>46251</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20557,7 +20557,7 @@
         <v>46209</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20635,7 +20635,7 @@
         <v>46205</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20713,7 +20713,7 @@
         <v>45670</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20786,7 +20786,7 @@
         <v>46252</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20859,7 +20859,7 @@
         <v>45252</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20932,7 +20932,7 @@
         <v>45700</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>44879</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21078,7 +21078,7 @@
         <v>45474</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21151,7 +21151,7 @@
         <v>44974</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21224,7 +21224,7 @@
         <v>46139</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21297,7 +21297,7 @@
         <v>45427</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21370,7 +21370,7 @@
         <v>44893</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21443,7 +21443,7 @@
         <v>46259</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>46258</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>45420</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21662,7 +21662,7 @@
         <v>44595</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>44546</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         <v>44777</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -21881,7 +21881,7 @@
         <v>45574</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -21954,7 +21954,7 @@
         <v>44749</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22027,7 +22027,7 @@
         <v>46262</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22100,7 +22100,7 @@
         <v>45415</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22173,7 +22173,7 @@
         <v>44895</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22246,7 +22246,7 @@
         <v>45159</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22319,7 +22319,7 @@
         <v>45159</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>45159</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22465,7 +22465,7 @@
         <v>45388</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22538,7 +22538,7 @@
         <v>44623</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22611,7 +22611,7 @@
         <v>45034</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22684,7 +22684,7 @@
         <v>45071</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22757,7 +22757,7 @@
         <v>45776</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>45777</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -22903,7 +22903,7 @@
         <v>45777</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -22976,7 +22976,7 @@
         <v>45033</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23049,7 +23049,7 @@
         <v>46156</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23122,7 +23122,7 @@
         <v>45338</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23195,7 +23195,7 @@
         <v>46279</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23268,7 +23268,7 @@
         <v>45259</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23341,7 +23341,7 @@
         <v>45743</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23414,7 +23414,7 @@
         <v>45740</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23487,7 +23487,7 @@
         <v>45714</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23560,7 +23560,7 @@
         <v>45419</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23638,7 +23638,7 @@
         <v>46281</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23711,7 +23711,7 @@
         <v>46239</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23784,7 +23784,7 @@
         <v>45796</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -23857,7 +23857,7 @@
         <v>45799</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -23930,7 +23930,7 @@
         <v>45355</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24003,7 +24003,7 @@
         <v>45799</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24076,7 +24076,7 @@
         <v>45800</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24149,7 +24149,7 @@
         <v>45805</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24222,7 +24222,7 @@
         <v>45811</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24295,7 +24295,7 @@
         <v>45598</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24368,7 +24368,7 @@
         <v>45324</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24441,7 +24441,7 @@
         <v>45815</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24514,7 +24514,7 @@
         <v>45831</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24587,7 +24587,7 @@
         <v>45832</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24660,7 +24660,7 @@
         <v>45832</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24733,7 +24733,7 @@
         <v>45835</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -24806,7 +24806,7 @@
         <v>45835</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -24879,7 +24879,7 @@
         <v>45835</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -24952,7 +24952,7 @@
         <v>45846</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25025,7 +25025,7 @@
         <v>45875</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25098,7 +25098,7 @@
         <v>45757</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25171,7 +25171,7 @@
         <v>45883</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25244,7 +25244,7 @@
         <v>45883</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25317,7 +25317,7 @@
         <v>45491</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>

--- a/Översikt FÄRGELANDA.xlsx
+++ b/Översikt FÄRGELANDA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE331"/>
+  <dimension ref="A1:AE328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44785</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45904</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>45303</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44935</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>45242</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>46239</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>45547</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>46175</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>45078</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>44504</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>44453</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>45474</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>45714</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>44911</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>45246</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>45766</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>45153</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>44837</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>44490</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>44595</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>44557</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>44490</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>44516</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>44525</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 55278-2021</t>
+          <t>A 68284-2021</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2949,10 +2949,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44475</v>
+        <v>44526</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 68284-2021</t>
+          <t>A 16267-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3022,10 +3022,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44526</v>
+        <v>44670</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3037,8 +3037,13 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3081,7 +3086,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 16267-2022</t>
+          <t>A 55278-2021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3095,10 +3100,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44670</v>
+        <v>44475</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3110,13 +3115,8 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3176,7 +3176,7 @@
         <v>44658</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>44602</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>44496</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         <v>44566</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>44684</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>44593</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         <v>44858</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>44550</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>44711</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>44670</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>44518</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         <v>44572</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         <v>44686</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 29188-2022</t>
+          <t>A 59062-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44750</v>
+        <v>44490</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4191,7 +4191,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 59062-2021</t>
+          <t>A 29188-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4205,10 +4205,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44490</v>
+        <v>44750</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4281,7 +4281,7 @@
         <v>44777</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v>44490</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4427,7 +4427,7 @@
         <v>44636</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>44465</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>45273</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 17627-2024</t>
+          <t>A 3010-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4643,10 +4643,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45418</v>
+        <v>45315</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4658,13 +4658,8 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>0.8</v>
+        <v>4.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4707,7 +4702,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 17974-2024</t>
+          <t>A 17627-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4721,10 +4716,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45419</v>
+        <v>45418</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4736,8 +4731,13 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4780,7 +4780,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 149-2023</t>
+          <t>A 40774-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4794,10 +4794,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44928</v>
+        <v>45558</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4853,7 +4853,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 2798-2022</t>
+          <t>A 17974-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4867,10 +4867,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44581</v>
+        <v>45419</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4926,7 +4926,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 3010-2024</t>
+          <t>A 149-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4940,10 +4940,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45315</v>
+        <v>44928</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4999,7 +4999,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 21547-2022</t>
+          <t>A 24284-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5013,10 +5013,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44706</v>
+        <v>45079</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5072,7 +5072,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 21588-2022</t>
+          <t>A 2798-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5086,10 +5086,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44706</v>
+        <v>44581</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 26108-2023</t>
+          <t>A 21547-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5159,10 +5159,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45091</v>
+        <v>44706</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5218,7 +5218,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 57868-2022</t>
+          <t>A 21588-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5232,10 +5232,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44899</v>
+        <v>44706</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5291,7 +5291,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 40774-2024</t>
+          <t>A 26108-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5305,10 +5305,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45558</v>
+        <v>45091</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.6</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5364,7 +5364,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 19389-2023</t>
+          <t>A 57868-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5378,10 +5378,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45049</v>
+        <v>44899</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5454,7 +5454,7 @@
         <v>45384</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 4525-2025</t>
+          <t>A 19389-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5524,10 +5524,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45687</v>
+        <v>45049</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5583,7 +5583,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 12198-2023</t>
+          <t>A 6180-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5597,10 +5597,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44998</v>
+        <v>44600</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5656,7 +5656,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 6180-2022</t>
+          <t>A 4525-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5670,10 +5670,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44600</v>
+        <v>45687</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5729,7 +5729,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 24284-2023</t>
+          <t>A 12198-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5743,10 +5743,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45079</v>
+        <v>44998</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5819,7 +5819,7 @@
         <v>45244</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>44916</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>45740</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         <v>44846</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>45758</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         <v>45196</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>45071</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>45209</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>44595</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6476,7 +6476,7 @@
         <v>44488</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 3657-2024</t>
+          <t>A 49825-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6546,10 +6546,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45321</v>
+        <v>45212</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.3</v>
+        <v>4.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6605,7 +6605,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 50454-2021</t>
+          <t>A 3657-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44459</v>
+        <v>45321</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6635,7 +6635,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6695,7 +6695,7 @@
         <v>44974</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         <v>45351</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
         <v>45351</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>44501</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 2301-2022</t>
+          <t>A 53906-2021</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6984,10 +6984,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44578</v>
+        <v>44469</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.9</v>
+        <v>20.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 53906-2021</t>
+          <t>A 2301-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7057,10 +7057,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44469</v>
+        <v>44578</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>20.8</v>
+        <v>0.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7116,7 +7116,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 49825-2023</t>
+          <t>A 72612-2021</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7130,10 +7130,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45212</v>
+        <v>44546</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4.7</v>
+        <v>2.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7189,7 +7189,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 72612-2021</t>
+          <t>A 60766-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7203,10 +7203,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44546</v>
+        <v>45260</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7279,7 +7279,7 @@
         <v>45180</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 60766-2023</t>
+          <t>A 64390-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7349,10 +7349,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45260</v>
+        <v>45280</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.7</v>
+        <v>7.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7425,7 +7425,7 @@
         <v>44522</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 64390-2023</t>
+          <t>A 1997-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7495,10 +7495,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45280</v>
+        <v>44939</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>7.4</v>
+        <v>0.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7554,7 +7554,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 1997-2023</t>
+          <t>A 15043-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7568,10 +7568,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44939</v>
+        <v>45015</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.7</v>
+        <v>5.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7627,7 +7627,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 15043-2023</t>
+          <t>A 1030-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7641,10 +7641,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45015</v>
+        <v>44571</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>5.7</v>
+        <v>0.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7700,7 +7700,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 19332-2023</t>
+          <t>A 57991-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45049</v>
+        <v>45247</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7730,7 +7730,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7773,7 +7773,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 53584-2024</t>
+          <t>A 19332-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7787,10 +7787,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45614</v>
+        <v>45049</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.7</v>
+        <v>4.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7846,7 +7846,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 17610-2023</t>
+          <t>A 37067-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7860,10 +7860,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45036</v>
+        <v>45875</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7919,7 +7919,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 1030-2022</t>
+          <t>A 17486-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7933,10 +7933,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44571</v>
+        <v>45757</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.7</v>
+        <v>4.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7992,7 +7992,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 57991-2023</t>
+          <t>A 40221-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8006,10 +8006,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45247</v>
+        <v>45894</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8065,7 +8065,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 56616-2022</t>
+          <t>A 53584-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8079,10 +8079,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44893</v>
+        <v>45614</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8138,7 +8138,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 1021-2023</t>
+          <t>A 38366-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8152,10 +8152,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44935</v>
+        <v>45883</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8211,7 +8211,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 46534-2024</t>
+          <t>A 29014-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8225,10 +8225,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45582</v>
+        <v>45481</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8284,7 +8284,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 64427-2023</t>
+          <t>A 38363-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8298,10 +8298,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45280</v>
+        <v>45883</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8314,7 +8314,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.6</v>
+        <v>7.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8357,7 +8357,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 59441-2024</t>
+          <t>A 20046-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8371,10 +8371,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45638</v>
+        <v>46136</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8430,7 +8430,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 68285-2021</t>
+          <t>A 5506-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8444,10 +8444,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44526</v>
+        <v>45693</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8503,7 +8503,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 5515-2025</t>
+          <t>A 17610-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8517,10 +8517,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45693</v>
+        <v>45036</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8576,7 +8576,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 59022-2023</t>
+          <t>A 39630-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8586,14 +8586,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45252</v>
+        <v>45890</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.5</v>
+        <v>4.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8649,7 +8649,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 59025-2023</t>
+          <t>A 40420-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8659,14 +8659,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45252</v>
+        <v>45895</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>44.5</v>
+        <v>0.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8722,7 +8722,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 17487-2025</t>
+          <t>A 40226-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8736,10 +8736,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45757</v>
+        <v>45894</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1</v>
+        <v>5.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8795,7 +8795,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 34241-2024</t>
+          <t>A 56616-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8809,10 +8809,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45524</v>
+        <v>44893</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8825,7 +8825,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8868,7 +8868,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 39630-2025</t>
+          <t>A 1021-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8882,10 +8882,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45890</v>
+        <v>44935</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8941,7 +8941,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 54038-2021</t>
+          <t>A 17487-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8955,10 +8955,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44470</v>
+        <v>45757</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9014,7 +9014,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 20861-2025</t>
+          <t>A 5515-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9028,10 +9028,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45777</v>
+        <v>45693</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9087,7 +9087,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 42257-2025</t>
+          <t>A 46534-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9101,10 +9101,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45904</v>
+        <v>45582</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9160,7 +9160,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 12533-2025</t>
+          <t>A 20861-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9174,10 +9174,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45730</v>
+        <v>45777</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9190,7 +9190,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9233,7 +9233,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 40420-2025</t>
+          <t>A 42257-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9247,10 +9247,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45895</v>
+        <v>45904</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9306,7 +9306,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 40213-2025</t>
+          <t>A 12533-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9320,10 +9320,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45894</v>
+        <v>45730</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9336,7 +9336,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>3.2</v>
+        <v>1.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9379,7 +9379,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 40226-2025</t>
+          <t>A 64427-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9393,10 +9393,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45894</v>
+        <v>45280</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9409,7 +9409,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>5.6</v>
+        <v>0.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9452,7 +9452,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 27841-2023</t>
+          <t>A 42329-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9466,10 +9466,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45098</v>
+        <v>45904</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9482,7 +9482,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.7</v>
+        <v>5.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9525,7 +9525,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 30406-2024</t>
+          <t>A 59441-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9539,10 +9539,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45491</v>
+        <v>45638</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9555,7 +9555,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>5.5</v>
+        <v>0.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9598,7 +9598,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 9736-2024</t>
+          <t>A 51468-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9612,10 +9612,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45362</v>
+        <v>45950</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9671,7 +9671,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 51468-2025</t>
+          <t>A 44552-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9685,10 +9685,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45950</v>
+        <v>45917</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9701,7 +9701,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9744,7 +9744,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 42329-2025</t>
+          <t>A 68285-2021</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9758,10 +9758,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45904</v>
+        <v>44526</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9774,7 +9774,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>5.7</v>
+        <v>1.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9817,7 +9817,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 2117-2022</t>
+          <t>A 44990-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9831,10 +9831,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44578</v>
+        <v>45918</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9890,7 +9890,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 62146-2023</t>
+          <t>A 2117-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9904,10 +9904,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45267</v>
+        <v>44578</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9920,7 +9920,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9963,7 +9963,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 36606-2023</t>
+          <t>A 59022-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9973,14 +9973,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45153</v>
+        <v>45252</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9993,7 +9993,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>13.5</v>
+        <v>0.5</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10036,7 +10036,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 59960-2024</t>
+          <t>A 59025-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10046,14 +10046,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45642</v>
+        <v>45252</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.4</v>
+        <v>44.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10109,7 +10109,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 28530-2024</t>
+          <t>A 34241-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10123,10 +10123,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45478</v>
+        <v>45524</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10182,7 +10182,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 3882-2025</t>
+          <t>A 54038-2021</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10196,10 +10196,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45684</v>
+        <v>44470</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10211,13 +10211,8 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10260,7 +10255,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 44552-2025</t>
+          <t>A 27841-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10274,10 +10269,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45917</v>
+        <v>45098</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10290,7 +10285,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10333,7 +10328,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 44990-2025</t>
+          <t>A 30406-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10347,10 +10342,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45918</v>
+        <v>45491</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10363,7 +10358,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10406,7 +10401,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 1944-2024</t>
+          <t>A 9736-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10420,10 +10415,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45308</v>
+        <v>45362</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10436,7 +10431,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10479,7 +10474,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 2948-2026</t>
+          <t>A 48087-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10493,10 +10488,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46038</v>
+        <v>45932</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10509,7 +10504,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10552,7 +10547,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 35173-2024</t>
+          <t>A 57446-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10566,10 +10561,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45530</v>
+        <v>44896</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10582,7 +10577,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10625,7 +10620,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 18178-2025</t>
+          <t>A 59960-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10639,10 +10634,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45761</v>
+        <v>45642</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10655,7 +10650,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10698,7 +10693,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 61915-2022</t>
+          <t>A 28530-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10712,10 +10707,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44917</v>
+        <v>45478</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10728,7 +10723,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10771,7 +10766,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 43684-2022</t>
+          <t>A 2948-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10785,10 +10780,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44837</v>
+        <v>46038</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10801,7 +10796,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10844,7 +10839,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 14015-2025</t>
+          <t>A 49069-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10858,10 +10853,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45740</v>
+        <v>45937</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10874,7 +10869,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10917,7 +10912,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 23222-2024</t>
+          <t>A 21897-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10931,10 +10926,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45452</v>
+        <v>46150</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10947,7 +10942,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>6.8</v>
+        <v>1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10990,7 +10985,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 48087-2025</t>
+          <t>A 62146-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11004,10 +10999,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45932</v>
+        <v>45267</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11020,7 +11015,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11063,7 +11058,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 57446-2022</t>
+          <t>A 36606-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11077,10 +11072,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44896</v>
+        <v>45153</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11093,7 +11088,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.1</v>
+        <v>13.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11136,7 +11131,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 60475-2024</t>
+          <t>A 3882-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11150,10 +11145,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45643</v>
+        <v>45684</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11165,8 +11160,13 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11209,7 +11209,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 12507-2025</t>
+          <t>A 50876-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11223,10 +11223,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45730</v>
+        <v>45946</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11239,7 +11239,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11282,7 +11282,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 30993-2022</t>
+          <t>A 50883-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11296,10 +11296,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44768</v>
+        <v>45946</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11312,7 +11312,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>4.4</v>
+        <v>1.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11355,7 +11355,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 49069-2025</t>
+          <t>A 51271-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11369,10 +11369,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45937</v>
+        <v>45949</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11385,7 +11385,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.9</v>
+        <v>10.1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11428,7 +11428,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 50876-2025</t>
+          <t>A 51476-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11442,10 +11442,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45946</v>
+        <v>45950</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11458,7 +11458,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11501,7 +11501,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 50883-2025</t>
+          <t>A 51483-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11515,10 +11515,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45946</v>
+        <v>45950</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11574,7 +11574,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 51271-2025</t>
+          <t>A 1944-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11588,10 +11588,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45949</v>
+        <v>45308</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>10.1</v>
+        <v>0.6</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11647,7 +11647,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 51476-2025</t>
+          <t>A 52725-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11661,10 +11661,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45950</v>
+        <v>45957</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11720,7 +11720,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 51483-2025</t>
+          <t>A 48479-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11734,10 +11734,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45950</v>
+        <v>45936</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11749,8 +11749,13 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11793,7 +11798,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 13960-2024</t>
+          <t>A 35173-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11807,10 +11812,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45392</v>
+        <v>45530</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11823,7 +11828,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11866,7 +11871,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 46-2024</t>
+          <t>A 53276-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11880,10 +11885,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45293</v>
+        <v>45958</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11896,7 +11901,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11939,7 +11944,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 12460-2022</t>
+          <t>A 18178-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11953,10 +11958,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44638</v>
+        <v>45761</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11969,7 +11974,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12012,7 +12017,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 52725-2025</t>
+          <t>A 61915-2022</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12026,10 +12031,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45957</v>
+        <v>44917</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12042,7 +12047,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12085,7 +12090,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 21897-2026</t>
+          <t>A 54405-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12099,10 +12104,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46150</v>
+        <v>45965</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12158,7 +12163,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 53276-2025</t>
+          <t>A 43684-2022</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12172,10 +12177,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45958</v>
+        <v>44837</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12188,7 +12193,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>4.7</v>
+        <v>1.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12231,7 +12236,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 54405-2025</t>
+          <t>A 54410-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12248,7 +12253,7 @@
         <v>45965</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12261,7 +12266,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12304,7 +12309,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 54410-2025</t>
+          <t>A 54401-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12321,7 +12326,7 @@
         <v>45965</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12334,7 +12339,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12377,7 +12382,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 54401-2025</t>
+          <t>A 14015-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12391,10 +12396,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45965</v>
+        <v>45740</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12407,7 +12412,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12450,7 +12455,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 58324-2022</t>
+          <t>A 23222-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12464,10 +12469,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44901</v>
+        <v>45452</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12480,7 +12485,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.9</v>
+        <v>6.8</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12540,7 +12545,7 @@
         <v>45969</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12613,7 +12618,7 @@
         <v>45969</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12669,7 +12674,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 22719-2023</t>
+          <t>A 60475-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12683,10 +12688,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45071</v>
+        <v>45643</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12699,7 +12704,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12742,7 +12747,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 58317-2021</t>
+          <t>A 12507-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12756,10 +12761,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44488</v>
+        <v>45730</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12772,7 +12777,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>6.6</v>
+        <v>1.8</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12815,7 +12820,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 56715-2025</t>
+          <t>A 23826-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12825,14 +12830,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45975</v>
+        <v>46166</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12844,13 +12849,8 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I161" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12893,7 +12893,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 56716-2025</t>
+          <t>A 30993-2022</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12907,10 +12907,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45975</v>
+        <v>44768</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12922,13 +12922,8 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I162" t="n">
-        <v>1.8</v>
+        <v>4.4</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12971,7 +12966,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 4672-2025</t>
+          <t>A 56715-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12985,10 +12980,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45687</v>
+        <v>45975</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13000,8 +12995,13 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I163" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13044,7 +13044,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 18003-2023</t>
+          <t>A 56716-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13058,10 +13058,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45040</v>
+        <v>45975</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13073,8 +13073,13 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I164" t="n">
-        <v>18.5</v>
+        <v>1.8</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13117,7 +13122,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 18188-2024</t>
+          <t>A 40778-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13131,10 +13136,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45420</v>
+        <v>45558</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13147,7 +13152,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13190,7 +13195,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 24075-2023</t>
+          <t>A 40778-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13204,10 +13209,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45078</v>
+        <v>45558</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13220,7 +13225,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13263,7 +13268,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 18538-2022</t>
+          <t>A 58869-2025</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13277,10 +13282,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44686</v>
+        <v>45987</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13293,7 +13298,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13336,7 +13341,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 5032-2023</t>
+          <t>A 59318-2025</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13350,10 +13355,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44958</v>
+        <v>45989</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13366,7 +13371,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>3.3</v>
+        <v>7</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13409,7 +13414,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 60321-2024</t>
+          <t>A 13960-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13423,10 +13428,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45643</v>
+        <v>45392</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13439,7 +13444,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13482,7 +13487,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 58869-2025</t>
+          <t>A 46-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13496,10 +13501,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45987</v>
+        <v>45293</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13512,7 +13517,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13555,7 +13560,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 59318-2025</t>
+          <t>A 12460-2022</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13569,10 +13574,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45989</v>
+        <v>44638</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13585,7 +13590,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>7</v>
+        <v>1.1</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13628,7 +13633,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 48479-2025</t>
+          <t>A 53196-2025</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13642,10 +13647,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45936</v>
+        <v>45958</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13657,13 +13662,8 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I172" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13706,7 +13706,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 16424-2024</t>
+          <t>A 58868-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13720,10 +13720,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45407</v>
+        <v>45987</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13736,7 +13736,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>9.800000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13779,7 +13779,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 17586-2023</t>
+          <t>A 58324-2022</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13789,14 +13789,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45034</v>
+        <v>44901</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13809,7 +13809,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>5.9</v>
+        <v>1.9</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13852,7 +13852,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 53196-2025</t>
+          <t>A 62435-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13866,10 +13866,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45958</v>
+        <v>46007</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13925,7 +13925,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 8452-2023</t>
+          <t>A 22719-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13939,10 +13939,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44977</v>
+        <v>45071</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13955,7 +13955,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13998,7 +13998,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 35098-2023</t>
+          <t>A 58317-2021</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14012,10 +14012,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45145</v>
+        <v>44488</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14028,7 +14028,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.6</v>
+        <v>6.6</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14071,7 +14071,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 8819-2025</t>
+          <t>A 25568-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14085,10 +14085,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45712</v>
+        <v>46177</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14101,7 +14101,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>8.1</v>
+        <v>1.4</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14144,7 +14144,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 23826-2026</t>
+          <t>A 4672-2025</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14154,14 +14154,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46166</v>
+        <v>45687</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14174,7 +14174,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.7</v>
+        <v>3.2</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14217,7 +14217,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 7387-2025</t>
+          <t>A 18003-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14231,10 +14231,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45705</v>
+        <v>45040</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14247,7 +14247,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.5</v>
+        <v>18.5</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14290,7 +14290,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 58868-2025</t>
+          <t>A 18188-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14304,10 +14304,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45987</v>
+        <v>45420</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14320,7 +14320,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14363,7 +14363,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 20359-2025</t>
+          <t>A 24075-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14377,10 +14377,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45775</v>
+        <v>45078</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14393,7 +14393,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14436,7 +14436,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 62435-2025</t>
+          <t>A 18538-2022</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14450,10 +14450,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46007</v>
+        <v>44686</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14466,7 +14466,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.2</v>
+        <v>3.9</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14509,7 +14509,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 18842-2025</t>
+          <t>A 5032-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14523,10 +14523,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45764</v>
+        <v>44958</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14539,7 +14539,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14582,7 +14582,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 40778-2024</t>
+          <t>A 60321-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14596,10 +14596,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45558</v>
+        <v>45643</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14612,7 +14612,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14655,7 +14655,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 44796-2022</t>
+          <t>A 27284-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14669,10 +14669,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44841</v>
+        <v>46188</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14685,7 +14685,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14728,7 +14728,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 57869-2022</t>
+          <t>A 2696-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14742,10 +14742,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44899</v>
+        <v>46037</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14801,7 +14801,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 40778-2024</t>
+          <t>A 16424-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14815,10 +14815,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45558</v>
+        <v>45407</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14831,7 +14831,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14874,7 +14874,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 50046-2023</t>
+          <t>A 17586-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14884,14 +14884,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45215</v>
+        <v>45034</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14904,7 +14904,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>2.4</v>
+        <v>5.9</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14947,7 +14947,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 26883-2024</t>
+          <t>A 27593-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14961,10 +14961,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45470</v>
+        <v>46190</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14977,7 +14977,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15020,7 +15020,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 51434-2022</t>
+          <t>A 8452-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15034,10 +15034,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>44869</v>
+        <v>44977</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15050,7 +15050,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15093,7 +15093,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 60468-2024</t>
+          <t>A 35098-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15107,10 +15107,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45643</v>
+        <v>45145</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15123,7 +15123,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>5.2</v>
+        <v>0.6</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15166,7 +15166,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 35845-2024</t>
+          <t>A 6210-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15180,10 +15180,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45532</v>
+        <v>46055</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15239,7 +15239,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 47461-2023</t>
+          <t>A 5962-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15253,10 +15253,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45202</v>
+        <v>46052</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15269,7 +15269,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.9</v>
+        <v>4.8</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15312,7 +15312,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 2696-2026</t>
+          <t>A 28163-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15326,10 +15326,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46037</v>
+        <v>46195</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15385,7 +15385,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 21311-2023</t>
+          <t>A 6194-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15399,10 +15399,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45062</v>
+        <v>46055</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15415,7 +15415,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15458,7 +15458,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 56619-2022</t>
+          <t>A 8819-2025</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15472,10 +15472,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44893</v>
+        <v>45712</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15488,7 +15488,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>2.4</v>
+        <v>8.1</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15531,7 +15531,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 13673-2025</t>
+          <t>A 7387-2025</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15545,10 +15545,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45736</v>
+        <v>45705</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15561,7 +15561,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15604,7 +15604,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 34433-2023</t>
+          <t>A 7230-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15618,10 +15618,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45139</v>
+        <v>46058</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15633,8 +15633,13 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I199" t="n">
-        <v>9.6</v>
+        <v>2.1</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15677,7 +15682,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 6210-2026</t>
+          <t>A 7909-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15691,10 +15696,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46055</v>
+        <v>46063</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15707,7 +15712,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.3</v>
+        <v>7.3</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15750,7 +15755,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 25826-2024</t>
+          <t>A 20359-2025</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15764,10 +15769,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45467</v>
+        <v>45775</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15780,7 +15785,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15823,7 +15828,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 5962-2026</t>
+          <t>A 8675-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15837,10 +15842,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46052</v>
+        <v>46066</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15852,8 +15857,13 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I202" t="n">
-        <v>4.8</v>
+        <v>0.7</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15896,7 +15906,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 6194-2026</t>
+          <t>A 8920-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15910,10 +15920,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46055</v>
+        <v>46069</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15925,8 +15935,13 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I203" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15969,7 +15984,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 6206-2026</t>
+          <t>A 18842-2025</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15983,10 +15998,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46055</v>
+        <v>45764</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15999,7 +16014,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16042,7 +16057,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 54698-2022</t>
+          <t>A 9090-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16056,10 +16071,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>44883</v>
+        <v>46069</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16072,7 +16087,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16115,7 +16130,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 7230-2026</t>
+          <t>A 9451-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16129,10 +16144,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46058</v>
+        <v>46071</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16144,13 +16159,8 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I206" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16193,7 +16203,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 7909-2026</t>
+          <t>A 9450-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16207,10 +16217,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46063</v>
+        <v>46071</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16223,7 +16233,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>7.3</v>
+        <v>1.4</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16266,7 +16276,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 25568-2026</t>
+          <t>A 10451-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16280,10 +16290,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46177</v>
+        <v>46076</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16295,8 +16305,13 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I208" t="n">
-        <v>1.4</v>
+        <v>15.3</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16339,7 +16354,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 8450-2023</t>
+          <t>A 11221-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16353,10 +16368,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>44977</v>
+        <v>46080</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16369,7 +16384,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>4.4</v>
+        <v>9.5</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16412,7 +16427,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 8675-2026</t>
+          <t>A 11223-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16426,10 +16441,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46066</v>
+        <v>46080</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16441,13 +16456,8 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I210" t="n">
-        <v>0.7</v>
+        <v>5.5</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16490,7 +16500,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 4285-2025</t>
+          <t>A 44796-2022</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16504,10 +16514,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45685</v>
+        <v>44841</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16520,7 +16530,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16563,7 +16573,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 8920-2026</t>
+          <t>A 57869-2022</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16577,10 +16587,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46069</v>
+        <v>44899</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16592,13 +16602,8 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I212" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16641,7 +16646,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 37783-2023</t>
+          <t>A 50046-2023</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16655,10 +16660,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45159</v>
+        <v>45215</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16671,7 +16676,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16714,7 +16719,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 9090-2026</t>
+          <t>A 26883-2024</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16728,10 +16733,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46069</v>
+        <v>45470</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16744,7 +16749,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16787,7 +16792,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 9451-2026</t>
+          <t>A 51434-2022</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16801,10 +16806,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46071</v>
+        <v>44869</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16817,7 +16822,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16860,7 +16865,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 9450-2026</t>
+          <t>A 60468-2024</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16874,10 +16879,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46071</v>
+        <v>45643</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16890,7 +16895,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1.4</v>
+        <v>5.2</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16933,7 +16938,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 10451-2026</t>
+          <t>A 30004-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16947,10 +16952,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46076</v>
+        <v>46202</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16968,7 +16973,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>15.3</v>
+        <v>1.7</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17011,7 +17016,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 11221-2026</t>
+          <t>A 12190-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17025,10 +17030,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46080</v>
+        <v>46086</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17041,7 +17046,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>9.5</v>
+        <v>1.3</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17084,7 +17089,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 11223-2026</t>
+          <t>A 12349-2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17098,10 +17103,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46080</v>
+        <v>46087</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17114,7 +17119,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>5.5</v>
+        <v>0.9</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17157,7 +17162,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 51019-2023</t>
+          <t>A 35845-2024</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17171,10 +17176,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45218</v>
+        <v>45532</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17187,7 +17192,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17230,7 +17235,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 27284-2026</t>
+          <t>A 12824-2026</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17244,10 +17249,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>46188</v>
+        <v>46091</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17260,7 +17265,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17303,7 +17308,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 55840-2023</t>
+          <t>A 29677-2026</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17317,10 +17322,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45239</v>
+        <v>46204</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17333,7 +17338,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17376,7 +17381,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 12190-2026</t>
+          <t>A 47461-2023</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17390,10 +17395,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>46086</v>
+        <v>45202</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17406,7 +17411,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17449,7 +17454,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 12349-2026</t>
+          <t>A 14662-2026</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17463,10 +17468,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>46087</v>
+        <v>46101</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17479,7 +17484,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17522,7 +17527,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 12824-2026</t>
+          <t>A 21311-2023</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17536,10 +17541,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46091</v>
+        <v>45062</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17552,7 +17557,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17595,7 +17600,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 27593-2026</t>
+          <t>A 15685-2026</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17609,10 +17614,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>46190</v>
+        <v>46107</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17625,7 +17630,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17668,7 +17673,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 28163-2026</t>
+          <t>A 56619-2022</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17682,10 +17687,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>46195</v>
+        <v>44893</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17698,7 +17703,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17741,7 +17746,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 28106-2026</t>
+          <t>A 13673-2025</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17755,10 +17760,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>46195</v>
+        <v>45736</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17771,7 +17776,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17814,7 +17819,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 71963-2021</t>
+          <t>A 34433-2023</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17828,10 +17833,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>44544</v>
+        <v>45139</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17844,7 +17849,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>1.3</v>
+        <v>9.6</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -17887,7 +17892,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 14662-2026</t>
+          <t>A 16836-2026</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -17901,10 +17906,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>46101</v>
+        <v>46113</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17917,7 +17922,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>1.7</v>
+        <v>7</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -17960,7 +17965,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 4838-2022</t>
+          <t>A 33722-2026</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -17974,10 +17979,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>44592</v>
+        <v>46251</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17990,7 +17995,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>1.2</v>
+        <v>12.5</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18033,7 +18038,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 39962-2023</t>
+          <t>A 25826-2024</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18047,10 +18052,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45168</v>
+        <v>45467</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18106,7 +18111,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 15685-2026</t>
+          <t>A 17375-2026</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18120,10 +18125,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>46107</v>
+        <v>46119</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18136,7 +18141,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>0.7</v>
+        <v>5.2</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18179,7 +18184,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 37898-2022</t>
+          <t>A 17887-2026</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18193,10 +18198,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>44811</v>
+        <v>46121</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18208,8 +18213,13 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I234" t="n">
-        <v>1.2</v>
+        <v>12.5</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18252,7 +18262,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 61914-2022</t>
+          <t>A 17777-2026</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18266,10 +18276,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>44917</v>
+        <v>46121</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18281,8 +18291,13 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I235" t="n">
-        <v>7.4</v>
+        <v>1.2</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18325,7 +18340,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 60330-2024</t>
+          <t>A 17646-2026</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18339,10 +18354,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45643</v>
+        <v>46121</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18355,7 +18370,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>4.3</v>
+        <v>0.9</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18398,7 +18413,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 19386-2023</t>
+          <t>A 17749-2026</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18412,10 +18427,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45049</v>
+        <v>46121</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18427,8 +18442,13 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I237" t="n">
-        <v>5.7</v>
+        <v>1.4</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18471,7 +18491,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 16836-2026</t>
+          <t>A 17696-2026</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18485,10 +18505,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>46113</v>
+        <v>46121</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18501,7 +18521,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>7</v>
+        <v>0.9</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18544,7 +18564,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 17375-2026</t>
+          <t>A 54698-2022</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18558,10 +18578,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>46119</v>
+        <v>44883</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18574,7 +18594,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>5.2</v>
+        <v>1</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18617,7 +18637,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 55310-2023</t>
+          <t>A 17991-2026</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18631,10 +18651,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45237</v>
+        <v>46124</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18647,7 +18667,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18690,7 +18710,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 17887-2026</t>
+          <t>A 18070-2026</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18704,10 +18724,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>46121</v>
+        <v>46125</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18721,11 +18741,11 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I241" t="n">
-        <v>12.5</v>
+        <v>7.5</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -18768,7 +18788,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 17777-2026</t>
+          <t>A 33591-2026</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -18782,10 +18802,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>46121</v>
+        <v>46248</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18797,13 +18817,8 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
-      <c r="H242" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I242" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -18846,7 +18861,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 17646-2026</t>
+          <t>A 33593-2026</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -18860,10 +18875,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>46121</v>
+        <v>46248</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18876,7 +18891,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -18919,7 +18934,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 17749-2026</t>
+          <t>A 8450-2023</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -18933,10 +18948,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>46121</v>
+        <v>44977</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -18948,13 +18963,8 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
-      <c r="H244" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I244" t="n">
-        <v>1.4</v>
+        <v>4.4</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -18997,7 +19007,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 17696-2026</t>
+          <t>A 4285-2025</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19011,10 +19021,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>46121</v>
+        <v>45685</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19027,7 +19037,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19070,7 +19080,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 17991-2026</t>
+          <t>A 37783-2023</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19084,10 +19094,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>46124</v>
+        <v>45159</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19100,7 +19110,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19143,7 +19153,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 30004-2026</t>
+          <t>A 19494-2026</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19157,10 +19167,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>46202</v>
+        <v>46134</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19172,13 +19182,8 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
-      <c r="H247" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I247" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19221,7 +19226,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 32904-2026</t>
+          <t>A 33726-2026</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19235,10 +19240,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19251,7 +19256,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19294,7 +19299,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 18070-2026</t>
+          <t>A 31159-2026</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19308,10 +19313,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>46125</v>
+        <v>46209</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19325,11 +19330,11 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I249" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19372,7 +19377,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 29677-2026</t>
+          <t>A 29961-2026</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19386,10 +19391,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19401,8 +19406,13 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I250" t="n">
-        <v>6.2</v>
+        <v>0.9</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19445,7 +19455,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 52151-2022</t>
+          <t>A 51019-2023</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19459,10 +19469,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>44873</v>
+        <v>45218</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19475,7 +19485,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>7.1</v>
+        <v>1.6</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -19518,7 +19528,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 19494-2026</t>
+          <t>A 34015-2026</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19532,10 +19542,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>46134</v>
+        <v>46252</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19548,7 +19558,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19591,7 +19601,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 40221-2025</t>
+          <t>A 55840-2023</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19605,10 +19615,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45894</v>
+        <v>45239</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19621,7 +19631,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>3.1</v>
+        <v>5.6</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -19664,7 +19674,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 29014-2024</t>
+          <t>A 71963-2021</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -19678,10 +19688,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45481</v>
+        <v>44544</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19694,7 +19704,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -19737,7 +19747,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 62643-2023</t>
+          <t>A 20266-2026</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -19751,10 +19761,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45271</v>
+        <v>46139</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19767,7 +19777,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -19810,7 +19820,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 20046-2026</t>
+          <t>A 4838-2022</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -19824,10 +19834,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>46136</v>
+        <v>44592</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19840,7 +19850,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -19883,7 +19893,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 5506-2025</t>
+          <t>A 35044-2026</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -19897,10 +19907,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>45693</v>
+        <v>46259</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -19913,7 +19923,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -19956,7 +19966,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 35844-2024</t>
+          <t>A 34863-2026</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -19970,10 +19980,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45532</v>
+        <v>46258</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -19986,7 +19996,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>2.1</v>
+        <v>13.9</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20029,7 +20039,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 4206-2024</t>
+          <t>A 39962-2023</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20043,10 +20053,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>45324</v>
+        <v>45168</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20059,7 +20069,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20102,7 +20112,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 40630-2023</t>
+          <t>A 37898-2022</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -20116,10 +20126,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45170</v>
+        <v>44811</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20132,7 +20142,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -20175,7 +20185,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 33722-2026</t>
+          <t>A 61914-2022</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -20189,10 +20199,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>46251</v>
+        <v>44917</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20205,7 +20215,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>12.5</v>
+        <v>7.4</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -20248,7 +20258,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 34715-2023</t>
+          <t>A 60330-2024</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -20262,10 +20272,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>45141</v>
+        <v>45643</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20278,7 +20288,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>7.2</v>
+        <v>4.3</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -20321,7 +20331,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 33591-2026</t>
+          <t>A 19386-2023</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -20335,10 +20345,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>46248</v>
+        <v>45049</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20351,7 +20361,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>1.6</v>
+        <v>5.7</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -20394,7 +20404,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 33593-2026</t>
+          <t>A 35507-2026</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -20408,10 +20418,10 @@
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>46248</v>
+        <v>46262</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20424,7 +20434,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -20467,7 +20477,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 33726-2026</t>
+          <t>A 55310-2023</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -20481,10 +20491,10 @@
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>46251</v>
+        <v>45237</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20497,7 +20507,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -20540,7 +20550,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>A 31159-2026</t>
+          <t>A 52151-2022</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -20554,10 +20564,10 @@
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>46209</v>
+        <v>44873</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20569,13 +20579,8 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
-      <c r="H266" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I266" t="n">
-        <v>5</v>
+        <v>7.1</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -20618,7 +20623,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>A 29961-2026</t>
+          <t>A 62643-2023</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -20632,10 +20637,10 @@
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>46205</v>
+        <v>45271</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20647,13 +20652,8 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
-      <c r="H267" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I267" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -20696,7 +20696,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>A 1678-2025</t>
+          <t>A 35844-2024</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -20710,10 +20710,10 @@
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>45670</v>
+        <v>45532</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20726,7 +20726,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -20769,7 +20769,7 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>A 34015-2026</t>
+          <t>A 4206-2024</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -20783,10 +20783,10 @@
         </is>
       </c>
       <c r="D269" s="1" t="n">
-        <v>46252</v>
+        <v>45324</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20799,7 +20799,7 @@
         </is>
       </c>
       <c r="I269" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -20842,7 +20842,7 @@
     <row r="270" ht="15" customHeight="1">
       <c r="A270" t="inlineStr">
         <is>
-          <t>A 59020-2023</t>
+          <t>A 40630-2023</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -20852,14 +20852,14 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D270" s="1" t="n">
-        <v>45252</v>
+        <v>45170</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20872,7 +20872,7 @@
         </is>
       </c>
       <c r="I270" t="n">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>
@@ -20915,7 +20915,7 @@
     <row r="271" ht="15" customHeight="1">
       <c r="A271" t="inlineStr">
         <is>
-          <t>A 6666-2025</t>
+          <t>A 34715-2023</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -20929,10 +20929,10 @@
         </is>
       </c>
       <c r="D271" s="1" t="n">
-        <v>45700</v>
+        <v>45141</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -20945,7 +20945,7 @@
         </is>
       </c>
       <c r="I271" t="n">
-        <v>1.3</v>
+        <v>7.2</v>
       </c>
       <c r="J271" t="n">
         <v>0</v>
@@ -20988,7 +20988,7 @@
     <row r="272" ht="15" customHeight="1">
       <c r="A272" t="inlineStr">
         <is>
-          <t>A 53559-2022</t>
+          <t>A 22679-2026</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -20998,14 +20998,14 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D272" s="1" t="n">
-        <v>44879</v>
+        <v>46156</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21018,7 +21018,7 @@
         </is>
       </c>
       <c r="I272" t="n">
-        <v>0.4</v>
+        <v>20.6</v>
       </c>
       <c r="J272" t="n">
         <v>0</v>
@@ -21061,7 +21061,7 @@
     <row r="273" ht="15" customHeight="1">
       <c r="A273" t="inlineStr">
         <is>
-          <t>A 27521-2024</t>
+          <t>A 37789-2026</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -21075,10 +21075,10 @@
         </is>
       </c>
       <c r="D273" s="1" t="n">
-        <v>45474</v>
+        <v>46279</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21091,7 +21091,7 @@
         </is>
       </c>
       <c r="I273" t="n">
-        <v>4.3</v>
+        <v>2.5</v>
       </c>
       <c r="J273" t="n">
         <v>0</v>
@@ -21134,7 +21134,7 @@
     <row r="274" ht="15" customHeight="1">
       <c r="A274" t="inlineStr">
         <is>
-          <t>A 8185-2023</t>
+          <t>A 1678-2025</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -21148,10 +21148,10 @@
         </is>
       </c>
       <c r="D274" s="1" t="n">
-        <v>44974</v>
+        <v>45670</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21164,7 +21164,7 @@
         </is>
       </c>
       <c r="I274" t="n">
-        <v>7.1</v>
+        <v>1.7</v>
       </c>
       <c r="J274" t="n">
         <v>0</v>
@@ -21207,7 +21207,7 @@
     <row r="275" ht="15" customHeight="1">
       <c r="A275" t="inlineStr">
         <is>
-          <t>A 20266-2026</t>
+          <t>A 59020-2023</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -21217,14 +21217,14 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D275" s="1" t="n">
-        <v>46139</v>
+        <v>45252</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21237,7 +21237,7 @@
         </is>
       </c>
       <c r="I275" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="J275" t="n">
         <v>0</v>
@@ -21280,7 +21280,7 @@
     <row r="276" ht="15" customHeight="1">
       <c r="A276" t="inlineStr">
         <is>
-          <t>A 18932-2024</t>
+          <t>A 6666-2025</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -21294,10 +21294,10 @@
         </is>
       </c>
       <c r="D276" s="1" t="n">
-        <v>45427</v>
+        <v>45700</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21310,7 +21310,7 @@
         </is>
       </c>
       <c r="I276" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J276" t="n">
         <v>0</v>
@@ -21353,7 +21353,7 @@
     <row r="277" ht="15" customHeight="1">
       <c r="A277" t="inlineStr">
         <is>
-          <t>A 56614-2022</t>
+          <t>A 38658-2026</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -21367,10 +21367,10 @@
         </is>
       </c>
       <c r="D277" s="1" t="n">
-        <v>44893</v>
+        <v>46281</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21383,7 +21383,7 @@
         </is>
       </c>
       <c r="I277" t="n">
-        <v>5.6</v>
+        <v>2.6</v>
       </c>
       <c r="J277" t="n">
         <v>0</v>
@@ -21426,7 +21426,7 @@
     <row r="278" ht="15" customHeight="1">
       <c r="A278" t="inlineStr">
         <is>
-          <t>A 35044-2026</t>
+          <t>A 53559-2022</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -21440,10 +21440,10 @@
         </is>
       </c>
       <c r="D278" s="1" t="n">
-        <v>46259</v>
+        <v>44879</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21456,7 +21456,7 @@
         </is>
       </c>
       <c r="I278" t="n">
-        <v>3.8</v>
+        <v>0.4</v>
       </c>
       <c r="J278" t="n">
         <v>0</v>
@@ -21499,7 +21499,7 @@
     <row r="279" ht="15" customHeight="1">
       <c r="A279" t="inlineStr">
         <is>
-          <t>A 34863-2026</t>
+          <t>A 27521-2024</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -21513,10 +21513,10 @@
         </is>
       </c>
       <c r="D279" s="1" t="n">
-        <v>46258</v>
+        <v>45474</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21529,7 +21529,7 @@
         </is>
       </c>
       <c r="I279" t="n">
-        <v>13.9</v>
+        <v>4.3</v>
       </c>
       <c r="J279" t="n">
         <v>0</v>
@@ -21572,7 +21572,7 @@
     <row r="280" ht="15" customHeight="1">
       <c r="A280" t="inlineStr">
         <is>
-          <t>A 18186-2024</t>
+          <t>A 32534-2026</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -21586,10 +21586,10 @@
         </is>
       </c>
       <c r="D280" s="1" t="n">
-        <v>45420</v>
+        <v>46239</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21602,7 +21602,7 @@
         </is>
       </c>
       <c r="I280" t="n">
-        <v>1.3</v>
+        <v>7.4</v>
       </c>
       <c r="J280" t="n">
         <v>0</v>
@@ -21645,7 +21645,7 @@
     <row r="281" ht="15" customHeight="1">
       <c r="A281" t="inlineStr">
         <is>
-          <t>A 5437-2022</t>
+          <t>A 8185-2023</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -21659,10 +21659,10 @@
         </is>
       </c>
       <c r="D281" s="1" t="n">
-        <v>44595</v>
+        <v>44974</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21675,7 +21675,7 @@
         </is>
       </c>
       <c r="I281" t="n">
-        <v>1</v>
+        <v>7.1</v>
       </c>
       <c r="J281" t="n">
         <v>0</v>
@@ -21718,7 +21718,7 @@
     <row r="282" ht="15" customHeight="1">
       <c r="A282" t="inlineStr">
         <is>
-          <t>A 72655-2021</t>
+          <t>A 18932-2024</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="D282" s="1" t="n">
-        <v>44546</v>
+        <v>45427</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21748,7 +21748,7 @@
         </is>
       </c>
       <c r="I282" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J282" t="n">
         <v>0</v>
@@ -21791,7 +21791,7 @@
     <row r="283" ht="15" customHeight="1">
       <c r="A283" t="inlineStr">
         <is>
-          <t>A 31885-2022</t>
+          <t>A 56614-2022</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -21805,10 +21805,10 @@
         </is>
       </c>
       <c r="D283" s="1" t="n">
-        <v>44777</v>
+        <v>44893</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -21821,7 +21821,7 @@
         </is>
       </c>
       <c r="I283" t="n">
-        <v>0.8</v>
+        <v>5.6</v>
       </c>
       <c r="J283" t="n">
         <v>0</v>
@@ -21864,7 +21864,7 @@
     <row r="284" ht="15" customHeight="1">
       <c r="A284" t="inlineStr">
         <is>
-          <t>A 44846-2024</t>
+          <t>A 18186-2024</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -21874,14 +21874,14 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D284" s="1" t="n">
-        <v>45574</v>
+        <v>45420</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -21894,7 +21894,7 @@
         </is>
       </c>
       <c r="I284" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J284" t="n">
         <v>0</v>
@@ -21937,7 +21937,7 @@
     <row r="285" ht="15" customHeight="1">
       <c r="A285" t="inlineStr">
         <is>
-          <t>A 28803-2022</t>
+          <t>A 5437-2022</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -21951,10 +21951,10 @@
         </is>
       </c>
       <c r="D285" s="1" t="n">
-        <v>44749</v>
+        <v>44595</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -21967,7 +21967,7 @@
         </is>
       </c>
       <c r="I285" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J285" t="n">
         <v>0</v>
@@ -22010,7 +22010,7 @@
     <row r="286" ht="15" customHeight="1">
       <c r="A286" t="inlineStr">
         <is>
-          <t>A 35507-2026</t>
+          <t>A 28106-2026</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -22024,10 +22024,10 @@
         </is>
       </c>
       <c r="D286" s="1" t="n">
-        <v>46262</v>
+        <v>46195</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22040,7 +22040,7 @@
         </is>
       </c>
       <c r="I286" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J286" t="n">
         <v>0</v>
@@ -22083,7 +22083,7 @@
     <row r="287" ht="15" customHeight="1">
       <c r="A287" t="inlineStr">
         <is>
-          <t>A 17456-2024</t>
+          <t>A 72655-2021</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -22097,10 +22097,10 @@
         </is>
       </c>
       <c r="D287" s="1" t="n">
-        <v>45415</v>
+        <v>44546</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22113,7 +22113,7 @@
         </is>
       </c>
       <c r="I287" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J287" t="n">
         <v>0</v>
@@ -22156,7 +22156,7 @@
     <row r="288" ht="15" customHeight="1">
       <c r="A288" t="inlineStr">
         <is>
-          <t>A 57267-2022</t>
+          <t>A 31885-2022</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -22170,10 +22170,10 @@
         </is>
       </c>
       <c r="D288" s="1" t="n">
-        <v>44895</v>
+        <v>44777</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22186,7 +22186,7 @@
         </is>
       </c>
       <c r="I288" t="n">
-        <v>7.2</v>
+        <v>0.8</v>
       </c>
       <c r="J288" t="n">
         <v>0</v>
@@ -22229,7 +22229,7 @@
     <row r="289" ht="15" customHeight="1">
       <c r="A289" t="inlineStr">
         <is>
-          <t>A 37784-2023</t>
+          <t>A 44846-2024</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -22239,14 +22239,14 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D289" s="1" t="n">
-        <v>45159</v>
+        <v>45574</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22259,7 +22259,7 @@
         </is>
       </c>
       <c r="I289" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J289" t="n">
         <v>0</v>
@@ -22302,7 +22302,7 @@
     <row r="290" ht="15" customHeight="1">
       <c r="A290" t="inlineStr">
         <is>
-          <t>A 37787-2023</t>
+          <t>A 28803-2022</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -22316,10 +22316,10 @@
         </is>
       </c>
       <c r="D290" s="1" t="n">
-        <v>45159</v>
+        <v>44749</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22332,7 +22332,7 @@
         </is>
       </c>
       <c r="I290" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J290" t="n">
         <v>0</v>
@@ -22375,7 +22375,7 @@
     <row r="291" ht="15" customHeight="1">
       <c r="A291" t="inlineStr">
         <is>
-          <t>A 37788-2023</t>
+          <t>A 40213-2025</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -22389,10 +22389,10 @@
         </is>
       </c>
       <c r="D291" s="1" t="n">
-        <v>45159</v>
+        <v>45894</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22405,7 +22405,7 @@
         </is>
       </c>
       <c r="I291" t="n">
-        <v>1.9</v>
+        <v>3.2</v>
       </c>
       <c r="J291" t="n">
         <v>0</v>
@@ -22448,7 +22448,7 @@
     <row r="292" ht="15" customHeight="1">
       <c r="A292" t="inlineStr">
         <is>
-          <t>A 13559-2024</t>
+          <t>A 32904-2026</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -22462,10 +22462,10 @@
         </is>
       </c>
       <c r="D292" s="1" t="n">
-        <v>45388</v>
+        <v>46244</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22478,7 +22478,7 @@
         </is>
       </c>
       <c r="I292" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J292" t="n">
         <v>0</v>
@@ -22521,7 +22521,7 @@
     <row r="293" ht="15" customHeight="1">
       <c r="A293" t="inlineStr">
         <is>
-          <t>A 10381-2022</t>
+          <t>A 17456-2024</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -22535,10 +22535,10 @@
         </is>
       </c>
       <c r="D293" s="1" t="n">
-        <v>44623</v>
+        <v>45415</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22551,7 +22551,7 @@
         </is>
       </c>
       <c r="I293" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J293" t="n">
         <v>0</v>
@@ -22594,7 +22594,7 @@
     <row r="294" ht="15" customHeight="1">
       <c r="A294" t="inlineStr">
         <is>
-          <t>A 17129-2023</t>
+          <t>A 57267-2022</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -22608,10 +22608,10 @@
         </is>
       </c>
       <c r="D294" s="1" t="n">
-        <v>45034</v>
+        <v>44895</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22624,7 +22624,7 @@
         </is>
       </c>
       <c r="I294" t="n">
-        <v>1.2</v>
+        <v>7.2</v>
       </c>
       <c r="J294" t="n">
         <v>0</v>
@@ -22667,7 +22667,7 @@
     <row r="295" ht="15" customHeight="1">
       <c r="A295" t="inlineStr">
         <is>
-          <t>A 22721-2023</t>
+          <t>A 37784-2023</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -22681,10 +22681,10 @@
         </is>
       </c>
       <c r="D295" s="1" t="n">
-        <v>45071</v>
+        <v>45159</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22697,7 +22697,7 @@
         </is>
       </c>
       <c r="I295" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J295" t="n">
         <v>0</v>
@@ -22740,7 +22740,7 @@
     <row r="296" ht="15" customHeight="1">
       <c r="A296" t="inlineStr">
         <is>
-          <t>A 20736-2025</t>
+          <t>A 37787-2023</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -22754,10 +22754,10 @@
         </is>
       </c>
       <c r="D296" s="1" t="n">
-        <v>45776</v>
+        <v>45159</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -22770,7 +22770,7 @@
         </is>
       </c>
       <c r="I296" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J296" t="n">
         <v>0</v>
@@ -22813,7 +22813,7 @@
     <row r="297" ht="15" customHeight="1">
       <c r="A297" t="inlineStr">
         <is>
-          <t>A 21126-2025</t>
+          <t>A 37788-2023</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -22827,10 +22827,10 @@
         </is>
       </c>
       <c r="D297" s="1" t="n">
-        <v>45777</v>
+        <v>45159</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         </is>
       </c>
       <c r="I297" t="n">
-        <v>5.2</v>
+        <v>1.9</v>
       </c>
       <c r="J297" t="n">
         <v>0</v>
@@ -22886,7 +22886,7 @@
     <row r="298" ht="15" customHeight="1">
       <c r="A298" t="inlineStr">
         <is>
-          <t>A 21125-2025</t>
+          <t>A 13559-2024</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -22900,10 +22900,10 @@
         </is>
       </c>
       <c r="D298" s="1" t="n">
-        <v>45777</v>
+        <v>45388</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -22916,7 +22916,7 @@
         </is>
       </c>
       <c r="I298" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="J298" t="n">
         <v>0</v>
@@ -22959,7 +22959,7 @@
     <row r="299" ht="15" customHeight="1">
       <c r="A299" t="inlineStr">
         <is>
-          <t>A 16828-2023</t>
+          <t>A 10381-2022</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -22973,10 +22973,10 @@
         </is>
       </c>
       <c r="D299" s="1" t="n">
-        <v>45033</v>
+        <v>44623</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -22989,7 +22989,7 @@
         </is>
       </c>
       <c r="I299" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J299" t="n">
         <v>0</v>
@@ -23032,7 +23032,7 @@
     <row r="300" ht="15" customHeight="1">
       <c r="A300" t="inlineStr">
         <is>
-          <t>A 22679-2026</t>
+          <t>A 17129-2023</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -23042,14 +23042,14 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D300" s="1" t="n">
-        <v>46156</v>
+        <v>45034</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23062,7 +23062,7 @@
         </is>
       </c>
       <c r="I300" t="n">
-        <v>20.6</v>
+        <v>1.2</v>
       </c>
       <c r="J300" t="n">
         <v>0</v>
@@ -23105,7 +23105,7 @@
     <row r="301" ht="15" customHeight="1">
       <c r="A301" t="inlineStr">
         <is>
-          <t>A 6322-2024</t>
+          <t>A 22721-2023</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -23119,10 +23119,10 @@
         </is>
       </c>
       <c r="D301" s="1" t="n">
-        <v>45338</v>
+        <v>45071</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
     <row r="302" ht="15" customHeight="1">
       <c r="A302" t="inlineStr">
         <is>
-          <t>A 37789-2026</t>
+          <t>A 20736-2025</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -23192,10 +23192,10 @@
         </is>
       </c>
       <c r="D302" s="1" t="n">
-        <v>46279</v>
+        <v>45776</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23208,7 +23208,7 @@
         </is>
       </c>
       <c r="I302" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="J302" t="n">
         <v>0</v>
@@ -23251,7 +23251,7 @@
     <row r="303" ht="15" customHeight="1">
       <c r="A303" t="inlineStr">
         <is>
-          <t>A 60382-2023</t>
+          <t>A 21126-2025</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -23265,10 +23265,10 @@
         </is>
       </c>
       <c r="D303" s="1" t="n">
-        <v>45259</v>
+        <v>45777</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23281,7 +23281,7 @@
         </is>
       </c>
       <c r="I303" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="J303" t="n">
         <v>0</v>
@@ -23324,7 +23324,7 @@
     <row r="304" ht="15" customHeight="1">
       <c r="A304" t="inlineStr">
         <is>
-          <t>A 15077-2025</t>
+          <t>A 21125-2025</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -23338,10 +23338,10 @@
         </is>
       </c>
       <c r="D304" s="1" t="n">
-        <v>45743</v>
+        <v>45777</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23354,7 +23354,7 @@
         </is>
       </c>
       <c r="I304" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J304" t="n">
         <v>0</v>
@@ -23397,7 +23397,7 @@
     <row r="305" ht="15" customHeight="1">
       <c r="A305" t="inlineStr">
         <is>
-          <t>A 14014-2025</t>
+          <t>A 16828-2023</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -23411,10 +23411,10 @@
         </is>
       </c>
       <c r="D305" s="1" t="n">
-        <v>45740</v>
+        <v>45033</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23427,7 +23427,7 @@
         </is>
       </c>
       <c r="I305" t="n">
-        <v>3.7</v>
+        <v>1.6</v>
       </c>
       <c r="J305" t="n">
         <v>0</v>
@@ -23470,7 +23470,7 @@
     <row r="306" ht="15" customHeight="1">
       <c r="A306" t="inlineStr">
         <is>
-          <t>A 9285-2025</t>
+          <t>A 6322-2024</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -23484,10 +23484,10 @@
         </is>
       </c>
       <c r="D306" s="1" t="n">
-        <v>45714</v>
+        <v>45338</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23500,7 +23500,7 @@
         </is>
       </c>
       <c r="I306" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J306" t="n">
         <v>0</v>
@@ -23543,7 +23543,7 @@
     <row r="307" ht="15" customHeight="1">
       <c r="A307" t="inlineStr">
         <is>
-          <t>A 17911-2024</t>
+          <t>A 60382-2023</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -23557,10 +23557,10 @@
         </is>
       </c>
       <c r="D307" s="1" t="n">
-        <v>45419</v>
+        <v>45259</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23572,13 +23572,8 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
-      <c r="H307" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I307" t="n">
-        <v>1</v>
+        <v>4.8</v>
       </c>
       <c r="J307" t="n">
         <v>0</v>
@@ -23621,7 +23616,7 @@
     <row r="308" ht="15" customHeight="1">
       <c r="A308" t="inlineStr">
         <is>
-          <t>A 38658-2026</t>
+          <t>A 15077-2025</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -23635,10 +23630,10 @@
         </is>
       </c>
       <c r="D308" s="1" t="n">
-        <v>46281</v>
+        <v>45743</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23651,7 +23646,7 @@
         </is>
       </c>
       <c r="I308" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J308" t="n">
         <v>0</v>
@@ -23694,7 +23689,7 @@
     <row r="309" ht="15" customHeight="1">
       <c r="A309" t="inlineStr">
         <is>
-          <t>A 32534-2026</t>
+          <t>A 14014-2025</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -23708,10 +23703,10 @@
         </is>
       </c>
       <c r="D309" s="1" t="n">
-        <v>46239</v>
+        <v>45740</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23724,7 +23719,7 @@
         </is>
       </c>
       <c r="I309" t="n">
-        <v>7.4</v>
+        <v>3.7</v>
       </c>
       <c r="J309" t="n">
         <v>0</v>
@@ -23767,7 +23762,7 @@
     <row r="310" ht="15" customHeight="1">
       <c r="A310" t="inlineStr">
         <is>
-          <t>A 24082-2025</t>
+          <t>A 9285-2025</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -23781,10 +23776,10 @@
         </is>
       </c>
       <c r="D310" s="1" t="n">
-        <v>45796</v>
+        <v>45714</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -23797,7 +23792,7 @@
         </is>
       </c>
       <c r="I310" t="n">
-        <v>4.4</v>
+        <v>0.9</v>
       </c>
       <c r="J310" t="n">
         <v>0</v>
@@ -23840,7 +23835,7 @@
     <row r="311" ht="15" customHeight="1">
       <c r="A311" t="inlineStr">
         <is>
-          <t>A 24731-2025</t>
+          <t>A 17911-2024</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -23854,10 +23849,10 @@
         </is>
       </c>
       <c r="D311" s="1" t="n">
-        <v>45799</v>
+        <v>45419</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -23869,8 +23864,13 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I311" t="n">
-        <v>6.5</v>
+        <v>1</v>
       </c>
       <c r="J311" t="n">
         <v>0</v>
@@ -23913,7 +23913,7 @@
     <row r="312" ht="15" customHeight="1">
       <c r="A312" t="inlineStr">
         <is>
-          <t>A 8574-2024</t>
+          <t>A 24082-2025</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -23923,14 +23923,14 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D312" s="1" t="n">
-        <v>45355</v>
+        <v>45796</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -23943,7 +23943,7 @@
         </is>
       </c>
       <c r="I312" t="n">
-        <v>2.2</v>
+        <v>4.4</v>
       </c>
       <c r="J312" t="n">
         <v>0</v>
@@ -23986,7 +23986,7 @@
     <row r="313" ht="15" customHeight="1">
       <c r="A313" t="inlineStr">
         <is>
-          <t>A 24751-2025</t>
+          <t>A 24731-2025</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -24003,7 +24003,7 @@
         <v>45799</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24016,7 +24016,7 @@
         </is>
       </c>
       <c r="I313" t="n">
-        <v>3.2</v>
+        <v>6.5</v>
       </c>
       <c r="J313" t="n">
         <v>0</v>
@@ -24059,7 +24059,7 @@
     <row r="314" ht="15" customHeight="1">
       <c r="A314" t="inlineStr">
         <is>
-          <t>A 25095-2025</t>
+          <t>A 8574-2024</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -24069,14 +24069,14 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D314" s="1" t="n">
-        <v>45800</v>
+        <v>45355</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24089,7 +24089,7 @@
         </is>
       </c>
       <c r="I314" t="n">
-        <v>4.9</v>
+        <v>2.2</v>
       </c>
       <c r="J314" t="n">
         <v>0</v>
@@ -24132,7 +24132,7 @@
     <row r="315" ht="15" customHeight="1">
       <c r="A315" t="inlineStr">
         <is>
-          <t>A 26292-2025</t>
+          <t>A 24751-2025</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -24146,10 +24146,10 @@
         </is>
       </c>
       <c r="D315" s="1" t="n">
-        <v>45805</v>
+        <v>45799</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24162,7 +24162,7 @@
         </is>
       </c>
       <c r="I315" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="J315" t="n">
         <v>0</v>
@@ -24205,7 +24205,7 @@
     <row r="316" ht="15" customHeight="1">
       <c r="A316" t="inlineStr">
         <is>
-          <t>A 27054-2025</t>
+          <t>A 25095-2025</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -24219,10 +24219,10 @@
         </is>
       </c>
       <c r="D316" s="1" t="n">
-        <v>45811</v>
+        <v>45800</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24235,7 +24235,7 @@
         </is>
       </c>
       <c r="I316" t="n">
-        <v>1.6</v>
+        <v>4.9</v>
       </c>
       <c r="J316" t="n">
         <v>0</v>
@@ -24278,7 +24278,7 @@
     <row r="317" ht="15" customHeight="1">
       <c r="A317" t="inlineStr">
         <is>
-          <t>A 50009-2024</t>
+          <t>A 26292-2025</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -24292,10 +24292,10 @@
         </is>
       </c>
       <c r="D317" s="1" t="n">
-        <v>45598</v>
+        <v>45805</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24308,7 +24308,7 @@
         </is>
       </c>
       <c r="I317" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J317" t="n">
         <v>0</v>
@@ -24351,7 +24351,7 @@
     <row r="318" ht="15" customHeight="1">
       <c r="A318" t="inlineStr">
         <is>
-          <t>A 4207-2024</t>
+          <t>A 27054-2025</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -24365,10 +24365,10 @@
         </is>
       </c>
       <c r="D318" s="1" t="n">
-        <v>45324</v>
+        <v>45811</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24381,7 +24381,7 @@
         </is>
       </c>
       <c r="I318" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J318" t="n">
         <v>0</v>
@@ -24424,7 +24424,7 @@
     <row r="319" ht="15" customHeight="1">
       <c r="A319" t="inlineStr">
         <is>
-          <t>A 27755-2025</t>
+          <t>A 50009-2024</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -24438,10 +24438,10 @@
         </is>
       </c>
       <c r="D319" s="1" t="n">
-        <v>45815</v>
+        <v>45598</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24454,7 +24454,7 @@
         </is>
       </c>
       <c r="I319" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="J319" t="n">
         <v>0</v>
@@ -24497,7 +24497,7 @@
     <row r="320" ht="15" customHeight="1">
       <c r="A320" t="inlineStr">
         <is>
-          <t>A 30737-2025</t>
+          <t>A 4207-2024</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -24511,10 +24511,10 @@
         </is>
       </c>
       <c r="D320" s="1" t="n">
-        <v>45831</v>
+        <v>45324</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24527,7 +24527,7 @@
         </is>
       </c>
       <c r="I320" t="n">
-        <v>7.6</v>
+        <v>1.4</v>
       </c>
       <c r="J320" t="n">
         <v>0</v>
@@ -24570,7 +24570,7 @@
     <row r="321" ht="15" customHeight="1">
       <c r="A321" t="inlineStr">
         <is>
-          <t>A 31146-2025</t>
+          <t>A 27755-2025</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -24584,10 +24584,10 @@
         </is>
       </c>
       <c r="D321" s="1" t="n">
-        <v>45832</v>
+        <v>45815</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24600,7 +24600,7 @@
         </is>
       </c>
       <c r="I321" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="J321" t="n">
         <v>0</v>
@@ -24643,7 +24643,7 @@
     <row r="322" ht="15" customHeight="1">
       <c r="A322" t="inlineStr">
         <is>
-          <t>A 30994-2025</t>
+          <t>A 30737-2025</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -24657,10 +24657,10 @@
         </is>
       </c>
       <c r="D322" s="1" t="n">
-        <v>45832</v>
+        <v>45831</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24673,7 +24673,7 @@
         </is>
       </c>
       <c r="I322" t="n">
-        <v>0.7</v>
+        <v>7.6</v>
       </c>
       <c r="J322" t="n">
         <v>0</v>
@@ -24716,7 +24716,7 @@
     <row r="323" ht="15" customHeight="1">
       <c r="A323" t="inlineStr">
         <is>
-          <t>A 31996-2025</t>
+          <t>A 30994-2025</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -24730,10 +24730,10 @@
         </is>
       </c>
       <c r="D323" s="1" t="n">
-        <v>45835</v>
+        <v>45832</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -24746,7 +24746,7 @@
         </is>
       </c>
       <c r="I323" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J323" t="n">
         <v>0</v>
@@ -24789,7 +24789,7 @@
     <row r="324" ht="15" customHeight="1">
       <c r="A324" t="inlineStr">
         <is>
-          <t>A 31984-2025</t>
+          <t>A 31996-2025</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -24806,7 +24806,7 @@
         <v>45835</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -24819,7 +24819,7 @@
         </is>
       </c>
       <c r="I324" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="J324" t="n">
         <v>0</v>
@@ -24862,7 +24862,7 @@
     <row r="325" ht="15" customHeight="1">
       <c r="A325" t="inlineStr">
         <is>
-          <t>A 32013-2025</t>
+          <t>A 31984-2025</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -24879,7 +24879,7 @@
         <v>45835</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -24892,7 +24892,7 @@
         </is>
       </c>
       <c r="I325" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="J325" t="n">
         <v>0</v>
@@ -24935,7 +24935,7 @@
     <row r="326" ht="15" customHeight="1">
       <c r="A326" t="inlineStr">
         <is>
-          <t>A 34379-2025</t>
+          <t>A 32013-2025</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -24949,10 +24949,10 @@
         </is>
       </c>
       <c r="D326" s="1" t="n">
-        <v>45846</v>
+        <v>45835</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -24965,7 +24965,7 @@
         </is>
       </c>
       <c r="I326" t="n">
-        <v>0.5</v>
+        <v>5.2</v>
       </c>
       <c r="J326" t="n">
         <v>0</v>
@@ -25008,7 +25008,7 @@
     <row r="327" ht="15" customHeight="1">
       <c r="A327" t="inlineStr">
         <is>
-          <t>A 37067-2025</t>
+          <t>A 34379-2025</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -25022,10 +25022,10 @@
         </is>
       </c>
       <c r="D327" s="1" t="n">
-        <v>45875</v>
+        <v>45846</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25038,7 +25038,7 @@
         </is>
       </c>
       <c r="I327" t="n">
-        <v>4.9</v>
+        <v>0.5</v>
       </c>
       <c r="J327" t="n">
         <v>0</v>
@@ -25078,27 +25078,27 @@
       </c>
       <c r="V327" s="2" t="inlineStr"/>
     </row>
-    <row r="328" ht="15" customHeight="1">
+    <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>A 17486-2025</t>
+          <t>S 2833-2024</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D328" s="1" t="n">
-        <v>45757</v>
+        <v>45491</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25111,7 +25111,7 @@
         </is>
       </c>
       <c r="I328" t="n">
-        <v>4.2</v>
+        <v>1</v>
       </c>
       <c r="J328" t="n">
         <v>0</v>
@@ -25150,225 +25150,6 @@
         <v>0</v>
       </c>
       <c r="V328" s="2" t="inlineStr"/>
-    </row>
-    <row r="329" ht="15" customHeight="1">
-      <c r="A329" t="inlineStr">
-        <is>
-          <t>A 38366-2025</t>
-        </is>
-      </c>
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D329" s="1" t="n">
-        <v>45883</v>
-      </c>
-      <c r="E329" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F329" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G329" t="inlineStr">
-        <is>
-          <t>FÄRGELANDA</t>
-        </is>
-      </c>
-      <c r="I329" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J329" t="n">
-        <v>0</v>
-      </c>
-      <c r="K329" t="n">
-        <v>0</v>
-      </c>
-      <c r="L329" t="n">
-        <v>0</v>
-      </c>
-      <c r="M329" t="n">
-        <v>0</v>
-      </c>
-      <c r="N329" t="n">
-        <v>0</v>
-      </c>
-      <c r="O329" t="n">
-        <v>0</v>
-      </c>
-      <c r="P329" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q329" t="n">
-        <v>0</v>
-      </c>
-      <c r="R329" t="n">
-        <v>0</v>
-      </c>
-      <c r="S329" t="n">
-        <v>0</v>
-      </c>
-      <c r="T329" t="n">
-        <v>0</v>
-      </c>
-      <c r="U329" t="n">
-        <v>0</v>
-      </c>
-      <c r="V329" s="2" t="inlineStr"/>
-    </row>
-    <row r="330" ht="15" customHeight="1">
-      <c r="A330" t="inlineStr">
-        <is>
-          <t>A 38363-2025</t>
-        </is>
-      </c>
-      <c r="B330" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D330" s="1" t="n">
-        <v>45883</v>
-      </c>
-      <c r="E330" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F330" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G330" t="inlineStr">
-        <is>
-          <t>FÄRGELANDA</t>
-        </is>
-      </c>
-      <c r="I330" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="J330" t="n">
-        <v>0</v>
-      </c>
-      <c r="K330" t="n">
-        <v>0</v>
-      </c>
-      <c r="L330" t="n">
-        <v>0</v>
-      </c>
-      <c r="M330" t="n">
-        <v>0</v>
-      </c>
-      <c r="N330" t="n">
-        <v>0</v>
-      </c>
-      <c r="O330" t="n">
-        <v>0</v>
-      </c>
-      <c r="P330" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q330" t="n">
-        <v>0</v>
-      </c>
-      <c r="R330" t="n">
-        <v>0</v>
-      </c>
-      <c r="S330" t="n">
-        <v>0</v>
-      </c>
-      <c r="T330" t="n">
-        <v>0</v>
-      </c>
-      <c r="U330" t="n">
-        <v>0</v>
-      </c>
-      <c r="V330" s="2" t="inlineStr"/>
-    </row>
-    <row r="331">
-      <c r="A331" t="inlineStr">
-        <is>
-          <t>S 2833-2024</t>
-        </is>
-      </c>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D331" s="1" t="n">
-        <v>45491</v>
-      </c>
-      <c r="E331" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F331" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G331" t="inlineStr">
-        <is>
-          <t>FÄRGELANDA</t>
-        </is>
-      </c>
-      <c r="I331" t="n">
-        <v>1</v>
-      </c>
-      <c r="J331" t="n">
-        <v>0</v>
-      </c>
-      <c r="K331" t="n">
-        <v>0</v>
-      </c>
-      <c r="L331" t="n">
-        <v>0</v>
-      </c>
-      <c r="M331" t="n">
-        <v>0</v>
-      </c>
-      <c r="N331" t="n">
-        <v>0</v>
-      </c>
-      <c r="O331" t="n">
-        <v>0</v>
-      </c>
-      <c r="P331" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q331" t="n">
-        <v>0</v>
-      </c>
-      <c r="R331" t="n">
-        <v>0</v>
-      </c>
-      <c r="S331" t="n">
-        <v>0</v>
-      </c>
-      <c r="T331" t="n">
-        <v>0</v>
-      </c>
-      <c r="U331" t="n">
-        <v>0</v>
-      </c>
-      <c r="V331" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt FÄRGELANDA.xlsx
+++ b/Översikt FÄRGELANDA.xlsx
@@ -601,7 +601,7 @@
         <v>44785</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45904</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>45303</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44935</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>45242</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>46239</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>46175</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>45078</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>44504</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>45547</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>44453</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>45474</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>45714</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>44911</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>45153</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>45246</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>45766</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>44837</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>44490</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>44595</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>44557</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>44516</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>44525</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>44490</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>44475</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>44526</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>44670</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>44658</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>44602</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>44496</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         <v>44566</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>44684</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>44593</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         <v>44858</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>44550</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>44711</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>44670</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>44518</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         <v>44572</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         <v>44686</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>44750</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>44490</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>44777</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v>44490</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4427,7 +4427,7 @@
         <v>44636</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>44465</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>44883</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>44811</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>45700</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
         <v>45244</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>45736</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>45418</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         <v>45419</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>45384</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>45239</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
         <v>44837</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         <v>44488</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5381,7 +5381,7 @@
         <v>45883</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>44546</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>45796</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         <v>45419</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>44469</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5751,7 +5751,7 @@
         <v>44526</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5824,7 +5824,7 @@
         <v>45355</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         <v>44470</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5970,7 +5970,7 @@
         <v>45757</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6043,7 +6043,7 @@
         <v>45280</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6116,7 +6116,7 @@
         <v>45890</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6189,7 +6189,7 @@
         <v>45799</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>46037</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>45420</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>45894</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>44901</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6554,7 +6554,7 @@
         <v>45895</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
         <v>45452</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         <v>44893</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>44899</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>44899</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6919,7 +6919,7 @@
         <v>45362</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6992,7 +6992,7 @@
         <v>45800</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>44488</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7138,7 +7138,7 @@
         <v>45904</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>45491</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>46052</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         <v>45799</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         <v>46055</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         <v>44544</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>46058</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         <v>45917</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>45918</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7800,7 +7800,7 @@
         <v>46063</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         <v>44939</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>45351</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
         <v>46066</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8097,7 +8097,7 @@
         <v>45351</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>46069</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
         <v>46069</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8321,7 +8321,7 @@
         <v>46071</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8394,7 +8394,7 @@
         <v>46071</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8467,7 +8467,7 @@
         <v>46076</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8545,7 +8545,7 @@
         <v>44977</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8618,7 +8618,7 @@
         <v>44600</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8691,7 +8691,7 @@
         <v>44592</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>45805</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>46080</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>46080</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         <v>45598</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9056,7 +9056,7 @@
         <v>44896</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>46086</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>46087</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9275,7 +9275,7 @@
         <v>44917</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9348,7 +9348,7 @@
         <v>45932</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9421,7 +9421,7 @@
         <v>46091</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         <v>45937</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9567,7 +9567,7 @@
         <v>45071</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9640,7 +9640,7 @@
         <v>45946</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>45324</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
         <v>45946</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9859,7 +9859,7 @@
         <v>46101</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9932,7 +9932,7 @@
         <v>45049</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>44638</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>45950</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10151,7 +10151,7 @@
         <v>45950</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
         <v>45949</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>45558</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10370,7 +10370,7 @@
         <v>46107</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>45957</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>45271</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10589,7 +10589,7 @@
         <v>46113</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>46119</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10735,7 +10735,7 @@
         <v>45958</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10808,7 +10808,7 @@
         <v>46121</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10886,7 +10886,7 @@
         <v>46121</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10964,7 +10964,7 @@
         <v>46121</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>46121</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11115,7 +11115,7 @@
         <v>46121</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11188,7 +11188,7 @@
         <v>46125</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11266,7 +11266,7 @@
         <v>46124</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11339,7 +11339,7 @@
         <v>45079</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>45965</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11485,7 +11485,7 @@
         <v>45643</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>45965</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>45965</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11704,7 +11704,7 @@
         <v>45811</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11777,7 +11777,7 @@
         <v>45969</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11850,7 +11850,7 @@
         <v>45969</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11923,7 +11923,7 @@
         <v>45643</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         <v>44998</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12069,7 +12069,7 @@
         <v>45638</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12142,7 +12142,7 @@
         <v>45975</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>45975</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12298,7 +12298,7 @@
         <v>45145</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12371,7 +12371,7 @@
         <v>46134</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12444,7 +12444,7 @@
         <v>45481</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         <v>44977</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12590,7 +12590,7 @@
         <v>45987</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12663,7 +12663,7 @@
         <v>45989</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12736,7 +12736,7 @@
         <v>45958</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         <v>46136</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12882,7 +12882,7 @@
         <v>45904</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12955,7 +12955,7 @@
         <v>45730</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13028,7 +13028,7 @@
         <v>45777</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13101,7 +13101,7 @@
         <v>45987</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13174,7 +13174,7 @@
         <v>45815</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13247,7 +13247,7 @@
         <v>45693</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13320,7 +13320,7 @@
         <v>45098</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13393,7 +13393,7 @@
         <v>45478</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13466,7 +13466,7 @@
         <v>46007</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13539,7 +13539,7 @@
         <v>45894</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13612,7 +13612,7 @@
         <v>45687</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13685,7 +13685,7 @@
         <v>44522</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13758,7 +13758,7 @@
         <v>45775</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
         <v>46038</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
         <v>45693</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>45950</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>44578</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>45071</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14196,7 +14196,7 @@
         <v>44916</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>45532</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14342,7 +14342,7 @@
         <v>45260</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14415,7 +14415,7 @@
         <v>45642</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14488,7 +14488,7 @@
         <v>45212</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14561,7 +14561,7 @@
         <v>44895</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14634,7 +14634,7 @@
         <v>45832</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14707,7 +14707,7 @@
         <v>46150</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14780,7 +14780,7 @@
         <v>45831</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14853,7 +14853,7 @@
         <v>45835</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14926,7 +14926,7 @@
         <v>45252</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14999,7 +14999,7 @@
         <v>45252</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
         <v>44873</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15145,7 +15145,7 @@
         <v>45835</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
         <v>45936</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15296,7 +15296,7 @@
         <v>45835</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15369,7 +15369,7 @@
         <v>45015</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>45758</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15515,7 +15515,7 @@
         <v>45846</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>45237</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15661,7 +15661,7 @@
         <v>46166</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15734,7 +15734,7 @@
         <v>45558</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15807,7 +15807,7 @@
         <v>45558</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15880,7 +15880,7 @@
         <v>44578</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15953,7 +15953,7 @@
         <v>45062</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16026,7 +16026,7 @@
         <v>45078</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16099,7 +16099,7 @@
         <v>46177</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16172,7 +16172,7 @@
         <v>44974</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16245,7 +16245,7 @@
         <v>45040</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16318,7 +16318,7 @@
         <v>45470</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16391,7 +16391,7 @@
         <v>45582</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>45388</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16537,7 +16537,7 @@
         <v>44893</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16610,7 +16610,7 @@
         <v>45467</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16683,7 +16683,7 @@
         <v>46188</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16756,7 +16756,7 @@
         <v>45034</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16829,7 +16829,7 @@
         <v>44581</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16902,7 +16902,7 @@
         <v>46190</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16975,7 +16975,7 @@
         <v>45643</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>46195</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17121,7 +17121,7 @@
         <v>45875</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17194,7 +17194,7 @@
         <v>44595</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17267,7 +17267,7 @@
         <v>45757</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17340,7 +17340,7 @@
         <v>46202</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17418,7 +17418,7 @@
         <v>45153</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17491,7 +17491,7 @@
         <v>45170</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
         <v>45315</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17637,7 +17637,7 @@
         <v>46204</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17710,7 +17710,7 @@
         <v>45883</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>46205</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17861,7 +17861,7 @@
         <v>46251</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17934,7 +17934,7 @@
         <v>45091</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>46209</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18085,7 +18085,7 @@
         <v>46252</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18158,7 +18158,7 @@
         <v>46251</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18231,7 +18231,7 @@
         <v>45180</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18304,7 +18304,7 @@
         <v>45684</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18382,7 +18382,7 @@
         <v>45209</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18455,7 +18455,7 @@
         <v>46258</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
         <v>46139</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
         <v>46259</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>44686</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18747,7 +18747,7 @@
         <v>46262</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18820,7 +18820,7 @@
         <v>45218</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18893,7 +18893,7 @@
         <v>44749</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18966,7 +18966,7 @@
         <v>45420</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19039,7 +19039,7 @@
         <v>44841</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19112,7 +19112,7 @@
         <v>45159</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19185,7 +19185,7 @@
         <v>45159</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19258,7 +19258,7 @@
         <v>45159</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19331,7 +19331,7 @@
         <v>45252</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19404,7 +19404,7 @@
         <v>45215</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19477,7 +19477,7 @@
         <v>45532</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>44768</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19623,7 +19623,7 @@
         <v>44706</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19696,7 +19696,7 @@
         <v>45196</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19769,7 +19769,7 @@
         <v>44869</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>44893</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19915,7 +19915,7 @@
         <v>44623</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -19988,7 +19988,7 @@
         <v>46156</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20061,7 +20061,7 @@
         <v>45293</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20134,7 +20134,7 @@
         <v>46279</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20207,7 +20207,7 @@
         <v>45202</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20280,7 +20280,7 @@
         <v>44879</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20353,7 +20353,7 @@
         <v>46239</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         <v>44546</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20499,7 +20499,7 @@
         <v>45267</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20572,7 +20572,7 @@
         <v>45685</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20645,7 +20645,7 @@
         <v>46281</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20718,7 +20718,7 @@
         <v>44501</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20791,7 +20791,7 @@
         <v>46244</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20864,7 +20864,7 @@
         <v>45034</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20937,7 +20937,7 @@
         <v>46195</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21010,7 +21010,7 @@
         <v>45894</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21083,7 +21083,7 @@
         <v>46248</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21156,7 +21156,7 @@
         <v>46248</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>45071</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21302,7 +21302,7 @@
         <v>44595</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21375,7 +21375,7 @@
         <v>45308</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21448,7 +21448,7 @@
         <v>46288</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21521,7 +21521,7 @@
         <v>44706</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
         <v>44917</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21667,7 +21667,7 @@
         <v>45427</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21740,7 +21740,7 @@
         <v>45614</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21813,7 +21813,7 @@
         <v>44935</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -21886,7 +21886,7 @@
         <v>44928</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -21959,7 +21959,7 @@
         <v>45712</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22032,7 +22032,7 @@
         <v>45392</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22105,7 +22105,7 @@
         <v>45049</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22178,7 +22178,7 @@
         <v>45168</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22251,7 +22251,7 @@
         <v>44846</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22324,7 +22324,7 @@
         <v>45036</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22397,7 +22397,7 @@
         <v>45324</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22470,7 +22470,7 @@
         <v>44974</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22543,7 +22543,7 @@
         <v>45139</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22616,7 +22616,7 @@
         <v>44958</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22689,7 +22689,7 @@
         <v>45530</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22762,7 +22762,7 @@
         <v>45761</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -22835,7 +22835,7 @@
         <v>45247</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -22908,7 +22908,7 @@
         <v>45415</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -22981,7 +22981,7 @@
         <v>45764</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23054,7 +23054,7 @@
         <v>45740</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23127,7 +23127,7 @@
         <v>45049</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>45524</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23273,7 +23273,7 @@
         <v>45474</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23346,7 +23346,7 @@
         <v>45705</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23419,7 +23419,7 @@
         <v>45574</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23492,7 +23492,7 @@
         <v>44777</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23565,7 +23565,7 @@
         <v>44571</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23638,7 +23638,7 @@
         <v>45141</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23711,7 +23711,7 @@
         <v>45670</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23784,7 +23784,7 @@
         <v>45159</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -23857,7 +23857,7 @@
         <v>45280</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -23930,7 +23930,7 @@
         <v>45321</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24003,7 +24003,7 @@
         <v>45643</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24076,7 +24076,7 @@
         <v>45407</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24149,7 +24149,7 @@
         <v>45687</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24222,7 +24222,7 @@
         <v>45273</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24295,7 +24295,7 @@
         <v>45730</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24368,7 +24368,7 @@
         <v>45740</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24441,7 +24441,7 @@
         <v>45776</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24514,7 +24514,7 @@
         <v>45777</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24587,7 +24587,7 @@
         <v>45777</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24660,7 +24660,7 @@
         <v>45033</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24733,7 +24733,7 @@
         <v>45338</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -24806,7 +24806,7 @@
         <v>45259</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -24879,7 +24879,7 @@
         <v>45714</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -24952,7 +24952,7 @@
         <v>45743</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25025,7 +25025,7 @@
         <v>45740</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25098,7 +25098,7 @@
         <v>45491</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>

--- a/Översikt FÄRGELANDA.xlsx
+++ b/Översikt FÄRGELANDA.xlsx
@@ -601,7 +601,7 @@
         <v>44785</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45904</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>45303</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44935</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>45242</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>46239</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>46175</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>45078</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>44504</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>45547</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>44453</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>45474</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>45714</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>44911</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>45153</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>45246</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>45766</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>44837</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>44490</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>44595</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>44557</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>44516</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>44525</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>44490</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>44475</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>44526</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>44670</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>44658</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>44602</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>44496</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         <v>44566</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>44684</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>44593</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         <v>44858</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>44550</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>44711</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>44670</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>44518</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         <v>44572</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         <v>44686</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>44750</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>44490</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>44777</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v>44490</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4427,7 +4427,7 @@
         <v>44636</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>44465</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>44883</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>44811</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>45700</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
         <v>45244</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>45736</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>45418</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         <v>45419</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>45384</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>45239</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
         <v>44837</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         <v>44488</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5381,7 +5381,7 @@
         <v>45883</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>44546</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>45796</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         <v>45419</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>44469</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5751,7 +5751,7 @@
         <v>44526</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5824,7 +5824,7 @@
         <v>45355</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         <v>44470</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5970,7 +5970,7 @@
         <v>45757</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6043,7 +6043,7 @@
         <v>45280</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6116,7 +6116,7 @@
         <v>45890</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6189,7 +6189,7 @@
         <v>45799</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>46037</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>45420</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>45894</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>44901</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6554,7 +6554,7 @@
         <v>45895</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
         <v>45452</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         <v>44893</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>44899</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>44899</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6919,7 +6919,7 @@
         <v>45362</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6992,7 +6992,7 @@
         <v>45800</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>44488</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7138,7 +7138,7 @@
         <v>45904</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>45491</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>46052</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         <v>45799</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         <v>46055</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         <v>44544</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>46058</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         <v>45917</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>45918</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7800,7 +7800,7 @@
         <v>46063</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         <v>44939</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>45351</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
         <v>46066</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8097,7 +8097,7 @@
         <v>45351</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>46069</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
         <v>46069</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8321,7 +8321,7 @@
         <v>46071</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8394,7 +8394,7 @@
         <v>46071</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8467,7 +8467,7 @@
         <v>46076</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8545,7 +8545,7 @@
         <v>44977</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8618,7 +8618,7 @@
         <v>44600</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8691,7 +8691,7 @@
         <v>44592</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>45805</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>46080</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>46080</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         <v>45598</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9056,7 +9056,7 @@
         <v>44896</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>46086</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>46087</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9275,7 +9275,7 @@
         <v>44917</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9348,7 +9348,7 @@
         <v>45932</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9421,7 +9421,7 @@
         <v>46091</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         <v>45937</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9567,7 +9567,7 @@
         <v>45071</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9640,7 +9640,7 @@
         <v>45946</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>45324</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
         <v>45946</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9859,7 +9859,7 @@
         <v>46101</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9932,7 +9932,7 @@
         <v>45049</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>44638</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>45950</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10151,7 +10151,7 @@
         <v>45950</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
         <v>45949</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>45558</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10370,7 +10370,7 @@
         <v>46107</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>45957</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>45271</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10589,7 +10589,7 @@
         <v>46113</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>46119</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10735,7 +10735,7 @@
         <v>45958</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10808,7 +10808,7 @@
         <v>46121</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10886,7 +10886,7 @@
         <v>46121</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10964,7 +10964,7 @@
         <v>46121</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>46121</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11115,7 +11115,7 @@
         <v>46121</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11188,7 +11188,7 @@
         <v>46125</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11266,7 +11266,7 @@
         <v>46124</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11339,7 +11339,7 @@
         <v>45079</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>45965</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11485,7 +11485,7 @@
         <v>45643</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>45965</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>45965</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11704,7 +11704,7 @@
         <v>45811</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11777,7 +11777,7 @@
         <v>45969</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11850,7 +11850,7 @@
         <v>45969</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11923,7 +11923,7 @@
         <v>45643</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         <v>44998</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12069,7 +12069,7 @@
         <v>45638</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12142,7 +12142,7 @@
         <v>45975</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>45975</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12298,7 +12298,7 @@
         <v>45145</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12371,7 +12371,7 @@
         <v>46134</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12444,7 +12444,7 @@
         <v>45481</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         <v>44977</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12590,7 +12590,7 @@
         <v>45987</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12663,7 +12663,7 @@
         <v>45989</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12736,7 +12736,7 @@
         <v>45958</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         <v>46136</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12882,7 +12882,7 @@
         <v>45904</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12955,7 +12955,7 @@
         <v>45730</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13028,7 +13028,7 @@
         <v>45777</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13101,7 +13101,7 @@
         <v>45987</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13174,7 +13174,7 @@
         <v>45815</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13247,7 +13247,7 @@
         <v>45693</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13320,7 +13320,7 @@
         <v>45098</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13393,7 +13393,7 @@
         <v>45478</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13466,7 +13466,7 @@
         <v>46007</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13539,7 +13539,7 @@
         <v>45894</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13612,7 +13612,7 @@
         <v>45687</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13685,7 +13685,7 @@
         <v>44522</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13758,7 +13758,7 @@
         <v>45775</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
         <v>46038</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
         <v>45693</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>45950</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>44578</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>45071</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14196,7 +14196,7 @@
         <v>44916</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>45532</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14342,7 +14342,7 @@
         <v>45260</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14415,7 +14415,7 @@
         <v>45642</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14488,7 +14488,7 @@
         <v>45212</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14561,7 +14561,7 @@
         <v>44895</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14634,7 +14634,7 @@
         <v>45832</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14707,7 +14707,7 @@
         <v>46150</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14780,7 +14780,7 @@
         <v>45831</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14853,7 +14853,7 @@
         <v>45835</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14926,7 +14926,7 @@
         <v>45252</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14999,7 +14999,7 @@
         <v>45252</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
         <v>44873</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15145,7 +15145,7 @@
         <v>45835</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
         <v>45936</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15296,7 +15296,7 @@
         <v>45835</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15369,7 +15369,7 @@
         <v>45015</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>45758</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15515,7 +15515,7 @@
         <v>45846</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>45237</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15661,7 +15661,7 @@
         <v>46166</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15734,7 +15734,7 @@
         <v>45558</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15807,7 +15807,7 @@
         <v>45558</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15880,7 +15880,7 @@
         <v>44578</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15953,7 +15953,7 @@
         <v>45062</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16026,7 +16026,7 @@
         <v>45078</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16099,7 +16099,7 @@
         <v>46177</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16172,7 +16172,7 @@
         <v>44974</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16245,7 +16245,7 @@
         <v>45040</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16318,7 +16318,7 @@
         <v>45470</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16391,7 +16391,7 @@
         <v>45582</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>45388</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16537,7 +16537,7 @@
         <v>44893</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16610,7 +16610,7 @@
         <v>45467</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16683,7 +16683,7 @@
         <v>46188</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16756,7 +16756,7 @@
         <v>45034</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16829,7 +16829,7 @@
         <v>44581</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16902,7 +16902,7 @@
         <v>46190</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16975,7 +16975,7 @@
         <v>45643</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>46195</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17121,7 +17121,7 @@
         <v>45875</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17194,7 +17194,7 @@
         <v>44595</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17267,7 +17267,7 @@
         <v>45757</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17340,7 +17340,7 @@
         <v>46202</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17418,7 +17418,7 @@
         <v>45153</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17491,7 +17491,7 @@
         <v>45170</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
         <v>45315</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17637,7 +17637,7 @@
         <v>46204</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17710,7 +17710,7 @@
         <v>45883</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>46205</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17861,7 +17861,7 @@
         <v>46251</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17934,7 +17934,7 @@
         <v>45091</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>46209</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18085,7 +18085,7 @@
         <v>46252</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18158,7 +18158,7 @@
         <v>46251</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18231,7 +18231,7 @@
         <v>45180</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18304,7 +18304,7 @@
         <v>45684</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18382,7 +18382,7 @@
         <v>45209</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18455,7 +18455,7 @@
         <v>46258</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
         <v>46139</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
         <v>46259</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>44686</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18747,7 +18747,7 @@
         <v>46262</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18820,7 +18820,7 @@
         <v>45218</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18893,7 +18893,7 @@
         <v>44749</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18966,7 +18966,7 @@
         <v>45420</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19039,7 +19039,7 @@
         <v>44841</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19112,7 +19112,7 @@
         <v>45159</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19185,7 +19185,7 @@
         <v>45159</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19258,7 +19258,7 @@
         <v>45159</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19331,7 +19331,7 @@
         <v>45252</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19404,7 +19404,7 @@
         <v>45215</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19477,7 +19477,7 @@
         <v>45532</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>44768</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19623,7 +19623,7 @@
         <v>44706</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19696,7 +19696,7 @@
         <v>45196</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19769,7 +19769,7 @@
         <v>44869</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>44893</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19915,7 +19915,7 @@
         <v>44623</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -19988,7 +19988,7 @@
         <v>46156</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20061,7 +20061,7 @@
         <v>45293</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20134,7 +20134,7 @@
         <v>46279</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20207,7 +20207,7 @@
         <v>45202</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20280,7 +20280,7 @@
         <v>44879</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20353,7 +20353,7 @@
         <v>46239</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         <v>44546</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20499,7 +20499,7 @@
         <v>45267</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20572,7 +20572,7 @@
         <v>45685</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20645,7 +20645,7 @@
         <v>46281</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20718,7 +20718,7 @@
         <v>44501</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20791,7 +20791,7 @@
         <v>46244</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20864,7 +20864,7 @@
         <v>45034</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20937,7 +20937,7 @@
         <v>46195</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21010,7 +21010,7 @@
         <v>45894</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21083,7 +21083,7 @@
         <v>46248</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21156,7 +21156,7 @@
         <v>46248</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>45071</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21302,7 +21302,7 @@
         <v>44595</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21375,7 +21375,7 @@
         <v>45308</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21448,7 +21448,7 @@
         <v>46288</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21521,7 +21521,7 @@
         <v>44706</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
         <v>44917</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21667,7 +21667,7 @@
         <v>45427</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21740,7 +21740,7 @@
         <v>45614</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21813,7 +21813,7 @@
         <v>44935</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -21886,7 +21886,7 @@
         <v>44928</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -21959,7 +21959,7 @@
         <v>45712</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22032,7 +22032,7 @@
         <v>45392</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22105,7 +22105,7 @@
         <v>45049</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22178,7 +22178,7 @@
         <v>45168</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22251,7 +22251,7 @@
         <v>44846</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22324,7 +22324,7 @@
         <v>45036</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22397,7 +22397,7 @@
         <v>45324</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22470,7 +22470,7 @@
         <v>44974</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22543,7 +22543,7 @@
         <v>45139</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22616,7 +22616,7 @@
         <v>44958</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22689,7 +22689,7 @@
         <v>45530</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22762,7 +22762,7 @@
         <v>45761</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -22835,7 +22835,7 @@
         <v>45247</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -22908,7 +22908,7 @@
         <v>45415</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -22981,7 +22981,7 @@
         <v>45764</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23054,7 +23054,7 @@
         <v>45740</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23127,7 +23127,7 @@
         <v>45049</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>45524</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23273,7 +23273,7 @@
         <v>45474</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23346,7 +23346,7 @@
         <v>45705</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23419,7 +23419,7 @@
         <v>45574</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23492,7 +23492,7 @@
         <v>44777</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23565,7 +23565,7 @@
         <v>44571</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23638,7 +23638,7 @@
         <v>45141</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23711,7 +23711,7 @@
         <v>45670</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23784,7 +23784,7 @@
         <v>45159</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -23857,7 +23857,7 @@
         <v>45280</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -23930,7 +23930,7 @@
         <v>45321</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24003,7 +24003,7 @@
         <v>45643</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24076,7 +24076,7 @@
         <v>45407</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24149,7 +24149,7 @@
         <v>45687</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24222,7 +24222,7 @@
         <v>45273</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24295,7 +24295,7 @@
         <v>45730</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24368,7 +24368,7 @@
         <v>45740</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24441,7 +24441,7 @@
         <v>45776</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24514,7 +24514,7 @@
         <v>45777</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24587,7 +24587,7 @@
         <v>45777</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24660,7 +24660,7 @@
         <v>45033</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24733,7 +24733,7 @@
         <v>45338</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -24806,7 +24806,7 @@
         <v>45259</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -24879,7 +24879,7 @@
         <v>45714</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -24952,7 +24952,7 @@
         <v>45743</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25025,7 +25025,7 @@
         <v>45740</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25098,7 +25098,7 @@
         <v>45491</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>

--- a/Översikt FÄRGELANDA.xlsx
+++ b/Översikt FÄRGELANDA.xlsx
@@ -601,7 +601,7 @@
         <v>44785</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45904</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>45303</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44935</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>45242</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>46239</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 38771-2024</t>
+          <t>A 24074-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45547</v>
+        <v>45078</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1288,16 +1288,16 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.9</v>
+        <v>0.5</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1312,7 +1312,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1321,43 +1321,43 @@
         <v>2</v>
       </c>
       <c r="T8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp
-Revlummer</t>
+          <t>Vätteros
+Blåsippa</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1439/artfynd/A 38771-2024 artfynd.xlsx", "A 38771-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1439/artfynd/A 24074-2023 artfynd.xlsx", "A 24074-2023")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1439/kartor/A 38771-2024 karta.png", "A 38771-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1439/kartor/A 24074-2023 karta.png", "A 24074-2023")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1439/kartor_geotiff/A 38771-2024 georefererad karta.tif", "A 38771-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1439/kartor_geotiff/A 24074-2023 georefererad karta.tif", "A 24074-2023")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1439/klagomål/A 38771-2024 FSC-klagomål.docx", "A 38771-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1439/klagomål/A 24074-2023 FSC-klagomål.docx", "A 24074-2023")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1439/klagomålsmail/A 38771-2024 FSC-klagomål mail.docx", "A 38771-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1439/klagomålsmail/A 24074-2023 FSC-klagomål mail.docx", "A 24074-2023")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1439/tillsyn/A 38771-2024 tillsynsbegäran.docx", "A 38771-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1439/tillsyn/A 24074-2023 tillsynsbegäran.docx", "A 24074-2023")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1439/tillsynsmail/A 38771-2024 tillsynsbegäran mail.docx", "A 38771-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1439/tillsynsmail/A 24074-2023 tillsynsbegäran mail.docx", "A 24074-2023")</f>
         <v/>
       </c>
     </row>
@@ -1381,7 +1381,7 @@
         <v>46175</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 24074-2023</t>
+          <t>A 62751-2021</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1484,10 +1484,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45078</v>
+        <v>44504</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1500,16 +1500,16 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.5</v>
+        <v>7.1</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1524,7 +1524,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1536,47 +1536,47 @@
         <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Vätteros
-Blåsippa</t>
+          <t>Grynig filtlav
+Korallblylav</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1439/artfynd/A 24074-2023 artfynd.xlsx", "A 24074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1439/artfynd/A 62751-2021 artfynd.xlsx", "A 62751-2021")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1439/kartor/A 24074-2023 karta.png", "A 24074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1439/kartor/A 62751-2021 karta.png", "A 62751-2021")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1439/kartor_geotiff/A 24074-2023 georefererad karta.tif", "A 24074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1439/kartor_geotiff/A 62751-2021 georefererad karta.tif", "A 62751-2021")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1439/klagomål/A 24074-2023 FSC-klagomål.docx", "A 24074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1439/klagomål/A 62751-2021 FSC-klagomål.docx", "A 62751-2021")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1439/klagomålsmail/A 24074-2023 FSC-klagomål mail.docx", "A 24074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1439/klagomålsmail/A 62751-2021 FSC-klagomål mail.docx", "A 62751-2021")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1439/tillsyn/A 24074-2023 tillsynsbegäran.docx", "A 24074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1439/tillsyn/A 62751-2021 tillsynsbegäran.docx", "A 62751-2021")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1439/tillsynsmail/A 24074-2023 tillsynsbegäran mail.docx", "A 24074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1439/tillsynsmail/A 62751-2021 tillsynsbegäran mail.docx", "A 62751-2021")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 62751-2021</t>
+          <t>A 38771-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44504</v>
+        <v>45547</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>7.1</v>
+        <v>4.9</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>1</v>
@@ -1639,43 +1639,43 @@
         <v>2</v>
       </c>
       <c r="T11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Grynig filtlav
-Korallblylav</t>
+          <t>Dropptaggsvamp
+Revlummer</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1439/artfynd/A 62751-2021 artfynd.xlsx", "A 62751-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1439/artfynd/A 38771-2024 artfynd.xlsx", "A 38771-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1439/kartor/A 62751-2021 karta.png", "A 62751-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1439/kartor/A 38771-2024 karta.png", "A 38771-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1439/kartor_geotiff/A 62751-2021 georefererad karta.tif", "A 62751-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1439/kartor_geotiff/A 38771-2024 georefererad karta.tif", "A 38771-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1439/klagomål/A 62751-2021 FSC-klagomål.docx", "A 62751-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1439/klagomål/A 38771-2024 FSC-klagomål.docx", "A 38771-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1439/klagomålsmail/A 62751-2021 FSC-klagomål mail.docx", "A 62751-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1439/klagomålsmail/A 38771-2024 FSC-klagomål mail.docx", "A 38771-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1439/tillsyn/A 62751-2021 tillsynsbegäran.docx", "A 62751-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1439/tillsyn/A 38771-2024 tillsynsbegäran.docx", "A 38771-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1439/tillsynsmail/A 62751-2021 tillsynsbegäran mail.docx", "A 62751-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1439/tillsynsmail/A 38771-2024 tillsynsbegäran mail.docx", "A 38771-2024")</f>
         <v/>
       </c>
     </row>
@@ -1699,7 +1699,7 @@
         <v>44453</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>45474</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>45714</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>44911</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 57683-2023</t>
+          <t>A 36645-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45246</v>
+        <v>45153</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2134,19 +2134,19 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.1</v>
+        <v>6.6</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2158,10 +2158,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2170,252 +2170,252 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1439/artfynd/A 36645-2023 artfynd.xlsx", "A 36645-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1439/kartor/A 36645-2023 karta.png", "A 36645-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1439/kartor_geotiff/A 36645-2023 georefererad karta.tif", "A 36645-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1439/klagomål/A 36645-2023 FSC-klagomål.docx", "A 36645-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1439/klagomålsmail/A 36645-2023 FSC-klagomål mail.docx", "A 36645-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1439/tillsyn/A 36645-2023 tillsynsbegäran.docx", "A 36645-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1439/tillsynsmail/A 36645-2023 tillsynsbegäran mail.docx", "A 36645-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 57683-2023</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45246</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>FÄRGELANDA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>1</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Källfräne</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1439/artfynd/A 57683-2023 artfynd.xlsx", "A 57683-2023")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1439/kartor/A 57683-2023 karta.png", "A 57683-2023")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1439/kartor_geotiff/A 57683-2023 georefererad karta.tif", "A 57683-2023")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1439/klagomål/A 57683-2023 FSC-klagomål.docx", "A 57683-2023")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1439/klagomålsmail/A 57683-2023 FSC-klagomål mail.docx", "A 57683-2023")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1439/tillsyn/A 57683-2023 tillsynsbegäran.docx", "A 57683-2023")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1439/tillsynsmail/A 57683-2023 tillsynsbegäran mail.docx", "A 57683-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>A 19083-2025</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
         <v>45766</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>FÄRGELANDA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
+      <c r="E18" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>FÄRGELANDA</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
         <v>6.2</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>1</v>
       </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>1</v>
       </c>
-      <c r="R17" t="n">
+      <c r="R18" t="n">
         <v>1</v>
       </c>
-      <c r="S17" t="n">
+      <c r="S18" t="n">
         <v>1</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T18" t="n">
         <v>1</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U18" t="n">
         <v>1</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Igelkott</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1439/artfynd/A 19083-2025 artfynd.xlsx", "A 19083-2025")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1439/kartor/A 19083-2025 karta.png", "A 19083-2025")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1439/kartor_geotiff/A 19083-2025 georefererad karta.tif", "A 19083-2025")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1439/klagomål/A 19083-2025 FSC-klagomål.docx", "A 19083-2025")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1439/klagomålsmail/A 19083-2025 FSC-klagomål mail.docx", "A 19083-2025")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1439/tillsyn/A 19083-2025 tillsynsbegäran.docx", "A 19083-2025")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1439/tillsynsmail/A 19083-2025 tillsynsbegäran mail.docx", "A 19083-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 36645-2023</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45153</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>FÄRGELANDA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1439/artfynd/A 36645-2023 artfynd.xlsx", "A 36645-2023")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1439/kartor/A 36645-2023 karta.png", "A 36645-2023")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1439/kartor_geotiff/A 36645-2023 georefererad karta.tif", "A 36645-2023")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1439/klagomål/A 36645-2023 FSC-klagomål.docx", "A 36645-2023")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1439/klagomålsmail/A 36645-2023 FSC-klagomål mail.docx", "A 36645-2023")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1439/tillsyn/A 36645-2023 tillsynsbegäran.docx", "A 36645-2023")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1439/tillsynsmail/A 36645-2023 tillsynsbegäran mail.docx", "A 36645-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>44837</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>44490</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>44595</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>44557</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>44490</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>44516</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>44525</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>44475</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>44526</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>44670</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>44658</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>44602</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>44496</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         <v>44566</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>44684</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>44593</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         <v>44858</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>44550</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>44711</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>44670</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>44518</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         <v>44572</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         <v>44686</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>44490</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>44750</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>44777</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v>44490</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4427,7 +4427,7 @@
         <v>44636</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 3010-2024</t>
+          <t>A 37898-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4497,10 +4497,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45315</v>
+        <v>44811</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4.6</v>
+        <v>1.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4556,7 +4556,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 17627-2024</t>
+          <t>A 6666-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4570,10 +4570,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45418</v>
+        <v>45700</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4585,13 +4585,8 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4634,7 +4629,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 17974-2024</t>
+          <t>A 54698-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4648,10 +4643,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45419</v>
+        <v>44883</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4664,7 +4659,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4707,7 +4702,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 40774-2024</t>
+          <t>A 13673-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4721,10 +4716,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45558</v>
+        <v>45736</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4737,7 +4732,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.6</v>
+        <v>0.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4780,7 +4775,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 63176-2023</t>
+          <t>A 17627-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4794,10 +4789,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45273</v>
+        <v>45418</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4809,8 +4804,13 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4853,7 +4853,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 24284-2023</t>
+          <t>A 12710-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4867,10 +4867,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45079</v>
+        <v>45384</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4926,7 +4926,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 149-2023</t>
+          <t>A 17974-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4940,10 +4940,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44928</v>
+        <v>45419</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4999,7 +4999,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 2798-2022</t>
+          <t>A 55840-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5013,10 +5013,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44581</v>
+        <v>45239</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.3</v>
+        <v>5.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5072,7 +5072,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 21588-2022</t>
+          <t>A 56918-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5086,10 +5086,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44706</v>
+        <v>45244</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 26108-2023</t>
+          <t>A 38363-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5159,10 +5159,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45091</v>
+        <v>45883</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.5</v>
+        <v>7.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5218,7 +5218,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 57868-2022</t>
+          <t>A 9285-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5232,10 +5232,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44899</v>
+        <v>45714</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5291,7 +5291,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 12710-2024</t>
+          <t>A 58330-2021</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5305,10 +5305,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45384</v>
+        <v>44488</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.9</v>
+        <v>10.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5364,7 +5364,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 19389-2023</t>
+          <t>A 15077-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5378,10 +5378,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45049</v>
+        <v>45743</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5437,7 +5437,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 6180-2022</t>
+          <t>A 43684-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5451,10 +5451,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44600</v>
+        <v>44837</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5510,7 +5510,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 21547-2022</t>
+          <t>A 72655-2021</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5524,10 +5524,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44706</v>
+        <v>44546</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5583,7 +5583,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 4525-2025</t>
+          <t>A 14014-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5597,10 +5597,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45687</v>
+        <v>45740</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.6</v>
+        <v>3.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5656,7 +5656,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 12198-2023</t>
+          <t>A 24082-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5670,10 +5670,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44998</v>
+        <v>45796</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.3</v>
+        <v>4.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5729,7 +5729,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 60382-2023</t>
+          <t>A 17911-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5743,10 +5743,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45259</v>
+        <v>45419</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5758,8 +5758,13 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5802,7 +5807,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 15077-2025</t>
+          <t>A 53906-2021</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5816,10 +5821,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45743</v>
+        <v>44469</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5832,7 +5837,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.1</v>
+        <v>20.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5875,7 +5880,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 62435-2025</t>
+          <t>A 68285-2021</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5889,10 +5894,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46007</v>
+        <v>44526</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5905,7 +5910,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5948,7 +5953,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 14014-2025</t>
+          <t>A 8574-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5958,14 +5963,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45740</v>
+        <v>45355</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5978,7 +5983,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6021,7 +6026,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 9285-2025</t>
+          <t>A 17487-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6035,10 +6040,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45714</v>
+        <v>45757</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6051,7 +6056,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6094,7 +6099,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 17911-2024</t>
+          <t>A 39630-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6108,10 +6113,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45419</v>
+        <v>45890</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6123,13 +6128,8 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>4.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6172,7 +6172,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 56918-2023</t>
+          <t>A 54038-2021</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6186,10 +6186,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45244</v>
+        <v>44470</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6202,7 +6202,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6245,7 +6245,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 61642-2022</t>
+          <t>A 24731-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6259,10 +6259,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44916</v>
+        <v>45799</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>9.4</v>
+        <v>6.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6318,7 +6318,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 24082-2025</t>
+          <t>A 40226-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6332,10 +6332,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45796</v>
+        <v>45894</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6391,7 +6391,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 24731-2025</t>
+          <t>A 25095-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6405,10 +6405,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45799</v>
+        <v>45800</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>6.5</v>
+        <v>4.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6464,7 +6464,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 14018-2025</t>
+          <t>A 40420-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6478,10 +6478,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45740</v>
+        <v>45895</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6494,7 +6494,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6537,7 +6537,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 8574-2024</t>
+          <t>A 64427-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6547,14 +6547,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45355</v>
+        <v>45280</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6610,7 +6610,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 39630-2025</t>
+          <t>A 24751-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6624,10 +6624,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45890</v>
+        <v>45799</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6683,7 +6683,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 40420-2025</t>
+          <t>A 18186-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6697,10 +6697,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45895</v>
+        <v>45420</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6713,7 +6713,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6756,7 +6756,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 40226-2025</t>
+          <t>A 58324-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6770,10 +6770,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45894</v>
+        <v>44901</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>5.6</v>
+        <v>1.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6829,7 +6829,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 24751-2025</t>
+          <t>A 23222-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6843,10 +6843,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45799</v>
+        <v>45452</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.2</v>
+        <v>6.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6902,7 +6902,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 25095-2025</t>
+          <t>A 56619-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6916,10 +6916,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45800</v>
+        <v>44893</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6932,7 +6932,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6992,7 +6992,7 @@
         <v>45805</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 17640-2025</t>
+          <t>A 57868-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45758</v>
+        <v>44899</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7078,7 +7078,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7121,7 +7121,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 45833-2022</t>
+          <t>A 57869-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7135,10 +7135,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44846</v>
+        <v>44899</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7151,7 +7151,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>8.300000000000001</v>
+        <v>1.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7194,7 +7194,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 42329-2025</t>
+          <t>A 50009-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7208,10 +7208,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45904</v>
+        <v>45598</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>5.7</v>
+        <v>1.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7267,7 +7267,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 27054-2025</t>
+          <t>A 9736-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7281,10 +7281,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45811</v>
+        <v>45362</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7340,7 +7340,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 50009-2024</t>
+          <t>A 42329-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7354,10 +7354,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45598</v>
+        <v>45904</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.5</v>
+        <v>5.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7413,7 +7413,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 46037-2023</t>
+          <t>A 58317-2021</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7427,10 +7427,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45196</v>
+        <v>44488</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.4</v>
+        <v>6.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7486,7 +7486,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 22722-2023</t>
+          <t>A 4207-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7500,10 +7500,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45071</v>
+        <v>45324</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7516,7 +7516,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7559,7 +7559,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 4207-2024</t>
+          <t>A 30406-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45324</v>
+        <v>45491</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7589,7 +7589,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.4</v>
+        <v>5.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7632,7 +7632,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 27755-2025</t>
+          <t>A 27054-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7646,10 +7646,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45815</v>
+        <v>45811</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7662,7 +7662,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>4.5</v>
+        <v>1.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7705,7 +7705,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 48850-2023</t>
+          <t>A 27755-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7719,10 +7719,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45209</v>
+        <v>45815</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7778,7 +7778,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 44552-2025</t>
+          <t>A 71963-2021</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7792,10 +7792,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45917</v>
+        <v>44544</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7851,7 +7851,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 5436-2022</t>
+          <t>A 2696-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7865,10 +7865,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44595</v>
+        <v>46037</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>11.3</v>
+        <v>1.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7924,7 +7924,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 44990-2025</t>
+          <t>A 1997-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7938,10 +7938,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45918</v>
+        <v>44939</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>5.3</v>
+        <v>0.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 58330-2021</t>
+          <t>A 8223-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8011,10 +8011,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44488</v>
+        <v>45351</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8027,7 +8027,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>10.1</v>
+        <v>2.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8070,7 +8070,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 49825-2023</t>
+          <t>A 8224-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8084,10 +8084,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45212</v>
+        <v>45351</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>4.7</v>
+        <v>2.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8143,7 +8143,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 30737-2025</t>
+          <t>A 44552-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8157,10 +8157,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45831</v>
+        <v>45917</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>7.6</v>
+        <v>1.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8216,7 +8216,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 30994-2025</t>
+          <t>A 44990-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8230,10 +8230,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45832</v>
+        <v>45918</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.7</v>
+        <v>5.3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8289,7 +8289,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 31996-2025</t>
+          <t>A 30994-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8303,10 +8303,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45835</v>
+        <v>45832</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8319,7 +8319,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8362,7 +8362,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 48087-2025</t>
+          <t>A 30737-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8376,10 +8376,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45932</v>
+        <v>45831</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>4</v>
+        <v>7.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8435,7 +8435,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 31984-2025</t>
+          <t>A 8452-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8449,10 +8449,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45835</v>
+        <v>44977</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8508,7 +8508,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 32013-2025</t>
+          <t>A 31984-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8525,7 +8525,7 @@
         <v>45835</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8581,7 +8581,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 57446-2022</t>
+          <t>A 6180-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8595,10 +8595,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44896</v>
+        <v>44600</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8654,7 +8654,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 3657-2024</t>
+          <t>A 31996-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8668,10 +8668,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45321</v>
+        <v>45835</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8727,7 +8727,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 49069-2025</t>
+          <t>A 4838-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8741,10 +8741,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45937</v>
+        <v>44592</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8757,7 +8757,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8800,7 +8800,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 8223-2024</t>
+          <t>A 32013-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8814,10 +8814,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45351</v>
+        <v>45835</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.6</v>
+        <v>5.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8873,7 +8873,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 8224-2024</t>
+          <t>A 57446-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8887,10 +8887,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45351</v>
+        <v>44896</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8903,7 +8903,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8946,7 +8946,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 2301-2022</t>
+          <t>A 61914-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8960,10 +8960,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44578</v>
+        <v>44917</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8976,7 +8976,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.9</v>
+        <v>7.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9019,7 +9019,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 8257-2023</t>
+          <t>A 34379-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9033,10 +9033,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44974</v>
+        <v>45846</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9049,7 +9049,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9092,7 +9092,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 61698-2021</t>
+          <t>A 48087-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9106,10 +9106,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44501</v>
+        <v>45932</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9165,7 +9165,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 34379-2025</t>
+          <t>A 49069-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9179,10 +9179,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45846</v>
+        <v>45937</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9238,7 +9238,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 50876-2025</t>
+          <t>A 22719-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9252,10 +9252,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45946</v>
+        <v>45071</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9268,7 +9268,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9311,7 +9311,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 53906-2021</t>
+          <t>A 50883-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9325,10 +9325,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44469</v>
+        <v>45946</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>20.8</v>
+        <v>1.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9384,7 +9384,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 50883-2025</t>
+          <t>A 50876-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9401,7 +9401,7 @@
         <v>45946</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9457,7 +9457,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 51271-2025</t>
+          <t>A 19332-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9471,10 +9471,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45949</v>
+        <v>45049</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>10.1</v>
+        <v>4.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9530,7 +9530,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 51476-2025</t>
+          <t>A 12460-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9544,10 +9544,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45950</v>
+        <v>44638</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9620,7 +9620,7 @@
         <v>45950</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 52725-2025</t>
+          <t>A 51476-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9690,10 +9690,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45957</v>
+        <v>45950</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9706,7 +9706,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9749,7 +9749,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 72612-2021</t>
+          <t>A 51271-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9763,10 +9763,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44546</v>
+        <v>45949</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9779,7 +9779,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.1</v>
+        <v>10.1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9822,7 +9822,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 53276-2025</t>
+          <t>A 40774-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9836,10 +9836,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45958</v>
+        <v>45558</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9895,7 +9895,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 42402-2023</t>
+          <t>A 5962-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9909,10 +9909,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45180</v>
+        <v>46052</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.6</v>
+        <v>4.8</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9968,7 +9968,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 54405-2025</t>
+          <t>A 37067-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9982,10 +9982,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45965</v>
+        <v>45875</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9998,7 +9998,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1</v>
+        <v>4.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10041,7 +10041,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 54410-2025</t>
+          <t>A 6210-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10055,10 +10055,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45965</v>
+        <v>46055</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10071,7 +10071,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10114,7 +10114,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 54401-2025</t>
+          <t>A 17486-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10128,10 +10128,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45965</v>
+        <v>45757</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10144,7 +10144,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10187,7 +10187,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 37067-2025</t>
+          <t>A 52725-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10201,10 +10201,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45875</v>
+        <v>45957</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10217,7 +10217,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>4.9</v>
+        <v>2.3</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10260,7 +10260,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 60766-2023</t>
+          <t>A 62643-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10274,10 +10274,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45260</v>
+        <v>45271</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10290,7 +10290,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10333,7 +10333,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 17486-2025</t>
+          <t>A 53276-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10347,10 +10347,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45757</v>
+        <v>45958</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 64390-2023</t>
+          <t>A 7230-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10420,10 +10420,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45280</v>
+        <v>46058</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10435,8 +10435,13 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>7.4</v>
+        <v>2.1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10479,7 +10484,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 55299-2025</t>
+          <t>A 24284-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10493,10 +10498,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45969</v>
+        <v>45079</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10509,7 +10514,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10552,7 +10557,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 55300-2025</t>
+          <t>A 54410-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10566,10 +10571,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45969</v>
+        <v>45965</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10582,7 +10587,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10625,7 +10630,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 38366-2025</t>
+          <t>A 54401-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10639,10 +10644,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45883</v>
+        <v>45965</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10655,7 +10660,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>7.2</v>
+        <v>2.2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10698,7 +10703,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 1997-2023</t>
+          <t>A 54405-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10712,10 +10717,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44939</v>
+        <v>45965</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10728,7 +10733,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10771,7 +10776,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 38363-2025</t>
+          <t>A 60321-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10785,10 +10790,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45883</v>
+        <v>45643</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10801,7 +10806,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>7.6</v>
+        <v>3.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10844,7 +10849,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 66955-2021</t>
+          <t>A 7909-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10858,10 +10863,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44522</v>
+        <v>46063</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10874,7 +10879,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2</v>
+        <v>7.3</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10917,7 +10922,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 2696-2026</t>
+          <t>A 38366-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10931,10 +10936,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46037</v>
+        <v>45883</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10947,7 +10952,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.5</v>
+        <v>7.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10990,7 +10995,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 56715-2025</t>
+          <t>A 55299-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11004,10 +11009,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45975</v>
+        <v>45969</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11019,13 +11024,8 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11068,7 +11068,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 56716-2025</t>
+          <t>A 55300-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11082,10 +11082,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45975</v>
+        <v>45969</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11097,13 +11097,8 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I137" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11146,7 +11141,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 17487-2025</t>
+          <t>A 8675-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11160,10 +11155,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45757</v>
+        <v>46066</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11175,8 +11170,13 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11219,7 +11219,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 15043-2023</t>
+          <t>A 9090-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11233,10 +11233,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45015</v>
+        <v>46069</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11249,7 +11249,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>5.7</v>
+        <v>3.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11292,7 +11292,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 1030-2022</t>
+          <t>A 60468-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11306,10 +11306,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44571</v>
+        <v>45643</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11322,7 +11322,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.7</v>
+        <v>5.2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11365,7 +11365,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 57991-2023</t>
+          <t>A 56715-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11379,10 +11379,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45247</v>
+        <v>45975</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11394,8 +11394,13 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11438,7 +11443,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 19332-2023</t>
+          <t>A 56716-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11452,10 +11457,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45049</v>
+        <v>45975</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11467,8 +11472,13 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>4.7</v>
+        <v>1.8</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11511,7 +11521,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 58869-2025</t>
+          <t>A 8920-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11525,10 +11535,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45987</v>
+        <v>46069</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11540,8 +11550,13 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I143" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11584,7 +11599,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 59318-2025</t>
+          <t>A 12198-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11598,10 +11613,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45989</v>
+        <v>44998</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11614,7 +11629,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>7</v>
+        <v>1.3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11657,7 +11672,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 53584-2024</t>
+          <t>A 59441-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11671,10 +11686,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45614</v>
+        <v>45638</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11687,7 +11702,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11730,7 +11745,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 53196-2025</t>
+          <t>A 35098-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11744,10 +11759,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45958</v>
+        <v>45145</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11760,7 +11775,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11803,7 +11818,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 17610-2023</t>
+          <t>A 9450-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11817,10 +11832,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45036</v>
+        <v>46071</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11833,7 +11848,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11876,7 +11891,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 6210-2026</t>
+          <t>A 9451-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11890,10 +11905,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46055</v>
+        <v>46071</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11906,7 +11921,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11949,7 +11964,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 5962-2026</t>
+          <t>A 10451-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11963,10 +11978,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46052</v>
+        <v>46076</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11978,8 +11993,13 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>4.8</v>
+        <v>15.3</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12022,7 +12042,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 58868-2025</t>
+          <t>A 8450-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12036,10 +12056,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45987</v>
+        <v>44977</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12052,7 +12072,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12095,7 +12115,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 56616-2022</t>
+          <t>A 58869-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12109,10 +12129,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44893</v>
+        <v>45987</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12125,7 +12145,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12168,7 +12188,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 1021-2023</t>
+          <t>A 59318-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12182,10 +12202,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44935</v>
+        <v>45989</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12198,7 +12218,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12241,7 +12261,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 46534-2024</t>
+          <t>A 53196-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12255,10 +12275,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45582</v>
+        <v>45958</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12271,7 +12291,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>4.2</v>
+        <v>1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12314,7 +12334,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 7230-2026</t>
+          <t>A 11221-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12328,10 +12348,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46058</v>
+        <v>46080</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12343,13 +12363,8 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I154" t="n">
-        <v>2.1</v>
+        <v>9.5</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12392,7 +12407,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 64427-2023</t>
+          <t>A 11223-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12406,10 +12421,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45280</v>
+        <v>46080</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12422,7 +12437,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.6</v>
+        <v>5.5</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12465,7 +12480,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 59441-2024</t>
+          <t>A 27841-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12479,10 +12494,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45638</v>
+        <v>45098</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12495,7 +12510,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12538,7 +12553,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 7909-2026</t>
+          <t>A 58868-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12552,10 +12567,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46063</v>
+        <v>45987</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12568,7 +12583,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>7.3</v>
+        <v>4.2</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12611,7 +12626,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 68285-2021</t>
+          <t>A 12190-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12625,10 +12640,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44526</v>
+        <v>46086</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12641,7 +12656,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12684,7 +12699,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 8675-2026</t>
+          <t>A 12349-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12698,10 +12713,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46066</v>
+        <v>46087</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12713,13 +12728,8 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I159" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12762,7 +12772,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 8920-2026</t>
+          <t>A 12824-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12776,10 +12786,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46069</v>
+        <v>46091</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12791,13 +12801,8 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I160" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12840,7 +12845,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 9090-2026</t>
+          <t>A 62435-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12854,10 +12859,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46069</v>
+        <v>46007</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12870,7 +12875,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12913,7 +12918,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 9451-2026</t>
+          <t>A 4525-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12927,10 +12932,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46071</v>
+        <v>45687</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12943,7 +12948,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12986,7 +12991,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 9450-2026</t>
+          <t>A 66955-2021</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13000,10 +13005,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46071</v>
+        <v>44522</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13016,7 +13021,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13059,7 +13064,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 59022-2023</t>
+          <t>A 20359-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13069,14 +13074,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45252</v>
+        <v>45775</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13089,7 +13094,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13132,7 +13137,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 59025-2023</t>
+          <t>A 14662-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13142,14 +13147,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45252</v>
+        <v>46101</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13162,7 +13167,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>44.5</v>
+        <v>1.7</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13205,7 +13210,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 34241-2024</t>
+          <t>A 22722-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13219,10 +13224,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45524</v>
+        <v>45071</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13235,7 +13240,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13278,7 +13283,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 54038-2021</t>
+          <t>A 15685-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13292,10 +13297,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44470</v>
+        <v>46107</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13308,7 +13313,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13351,7 +13356,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 10451-2026</t>
+          <t>A 61642-2022</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13365,10 +13370,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46076</v>
+        <v>44916</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13380,13 +13385,8 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I168" t="n">
-        <v>15.3</v>
+        <v>9.4</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13429,7 +13429,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 27841-2023</t>
+          <t>A 35845-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13443,10 +13443,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45098</v>
+        <v>45532</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13459,7 +13459,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13502,7 +13502,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 11221-2026</t>
+          <t>A 60766-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13516,10 +13516,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46080</v>
+        <v>45260</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13532,7 +13532,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>9.5</v>
+        <v>2.7</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13575,7 +13575,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 11223-2026</t>
+          <t>A 16836-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13589,10 +13589,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46080</v>
+        <v>46113</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13605,7 +13605,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13648,7 +13648,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 30406-2024</t>
+          <t>A 49825-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13662,10 +13662,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45491</v>
+        <v>45212</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13721,7 +13721,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 9736-2024</t>
+          <t>A 17375-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13735,10 +13735,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45362</v>
+        <v>46119</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13751,7 +13751,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>0.3</v>
+        <v>5.2</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13794,7 +13794,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 12190-2026</t>
+          <t>A 17749-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13808,10 +13808,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46086</v>
+        <v>46121</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13823,8 +13823,13 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I174" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13867,7 +13872,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 12349-2026</t>
+          <t>A 17777-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13881,10 +13886,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46087</v>
+        <v>46121</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13896,8 +13901,13 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I175" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13940,7 +13950,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 12824-2026</t>
+          <t>A 17646-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13954,10 +13964,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46091</v>
+        <v>46121</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13970,7 +13980,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14013,7 +14023,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 62146-2023</t>
+          <t>A 17887-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14027,10 +14037,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45267</v>
+        <v>46121</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14042,8 +14052,13 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I177" t="n">
-        <v>3</v>
+        <v>12.5</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14086,7 +14101,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 36606-2023</t>
+          <t>A 17696-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14100,10 +14115,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45153</v>
+        <v>46121</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14116,7 +14131,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>13.5</v>
+        <v>0.9</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14159,7 +14174,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 3882-2025</t>
+          <t>A 18070-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14173,10 +14188,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45684</v>
+        <v>46125</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14194,7 +14209,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.1</v>
+        <v>7.5</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14237,7 +14252,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 1944-2024</t>
+          <t>A 57267-2022</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14251,10 +14266,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45308</v>
+        <v>44895</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14267,7 +14282,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.6</v>
+        <v>7.2</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14310,7 +14325,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 14662-2026</t>
+          <t>A 17991-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14324,10 +14339,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46101</v>
+        <v>46124</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14340,7 +14355,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14383,7 +14398,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 35173-2024</t>
+          <t>A 59022-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14393,14 +14408,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45530</v>
+        <v>45252</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14413,7 +14428,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14456,7 +14471,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 18178-2025</t>
+          <t>A 59025-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14466,14 +14481,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45761</v>
+        <v>45252</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14486,7 +14501,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>2</v>
+        <v>44.5</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14529,7 +14544,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 61915-2022</t>
+          <t>A 19494-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14543,10 +14558,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44917</v>
+        <v>46134</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14559,7 +14574,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14602,7 +14617,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 43684-2022</t>
+          <t>A 52151-2022</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14616,10 +14631,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44837</v>
+        <v>44873</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14632,7 +14647,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.5</v>
+        <v>7.1</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14675,7 +14690,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 15685-2026</t>
+          <t>A 29014-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14689,10 +14704,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46107</v>
+        <v>45481</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14705,7 +14720,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14748,7 +14763,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 14015-2025</t>
+          <t>A 15043-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14762,10 +14777,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45740</v>
+        <v>45015</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14778,7 +14793,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.1</v>
+        <v>5.7</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14821,7 +14836,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 23222-2024</t>
+          <t>A 17640-2025</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14835,10 +14850,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45452</v>
+        <v>45758</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14851,7 +14866,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>6.8</v>
+        <v>0.7</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14894,7 +14909,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 60475-2024</t>
+          <t>A 20046-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14908,10 +14923,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45643</v>
+        <v>46136</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14924,7 +14939,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14967,7 +14982,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 12507-2025</t>
+          <t>A 55310-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14981,10 +14996,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45730</v>
+        <v>45237</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14997,7 +15012,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15040,7 +15055,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 30993-2022</t>
+          <t>A 42257-2025</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15054,10 +15069,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>44768</v>
+        <v>45904</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15070,7 +15085,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15113,7 +15128,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 16836-2026</t>
+          <t>A 12533-2025</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15127,10 +15142,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46113</v>
+        <v>45730</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15143,7 +15158,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>7</v>
+        <v>1.7</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15186,7 +15201,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 17375-2026</t>
+          <t>A 20861-2025</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15200,10 +15215,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46119</v>
+        <v>45777</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15216,7 +15231,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>5.2</v>
+        <v>1.3</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15259,7 +15274,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 17887-2026</t>
+          <t>A 2301-2022</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15273,10 +15288,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46121</v>
+        <v>44578</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15288,13 +15303,8 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I194" t="n">
-        <v>12.5</v>
+        <v>0.9</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15337,7 +15347,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 17777-2026</t>
+          <t>A 21311-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15351,10 +15361,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46121</v>
+        <v>45062</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15366,13 +15376,8 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I195" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15415,7 +15420,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 17646-2026</t>
+          <t>A 5506-2025</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15429,10 +15434,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46121</v>
+        <v>45693</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15445,7 +15450,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15488,7 +15493,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 17749-2026</t>
+          <t>A 24075-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15502,10 +15507,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46121</v>
+        <v>45078</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15517,13 +15522,8 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I197" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15566,7 +15566,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 17696-2026</t>
+          <t>A 28530-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15580,10 +15580,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46121</v>
+        <v>45478</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15596,7 +15596,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15639,7 +15639,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 17991-2026</t>
+          <t>A 40221-2025</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15653,10 +15653,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46124</v>
+        <v>45894</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15669,7 +15669,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15712,7 +15712,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 18070-2026</t>
+          <t>A 2948-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15726,10 +15726,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46125</v>
+        <v>46038</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15741,13 +15741,8 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I200" t="n">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15790,7 +15785,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 13960-2024</t>
+          <t>A 8257-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15804,10 +15799,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45392</v>
+        <v>44974</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15820,7 +15815,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15863,7 +15858,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 46-2024</t>
+          <t>A 5515-2025</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15877,10 +15872,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45293</v>
+        <v>45693</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15893,7 +15888,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15936,7 +15931,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 12460-2022</t>
+          <t>A 51468-2025</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15950,10 +15945,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>44638</v>
+        <v>45950</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15966,7 +15961,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16009,7 +16004,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 19494-2026</t>
+          <t>A 18003-2023</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16023,10 +16018,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46134</v>
+        <v>45040</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16039,7 +16034,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>2.5</v>
+        <v>18.5</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16082,7 +16077,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 40221-2025</t>
+          <t>A 26883-2024</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16096,10 +16091,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45894</v>
+        <v>45470</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16112,7 +16107,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16155,7 +16150,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 29014-2024</t>
+          <t>A 46534-2024</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16169,10 +16164,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45481</v>
+        <v>45582</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16185,7 +16180,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16228,7 +16223,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 20046-2026</t>
+          <t>A 2117-2022</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16242,10 +16237,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46136</v>
+        <v>44578</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16258,7 +16253,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16301,7 +16296,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 5506-2025</t>
+          <t>A 13559-2024</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16315,10 +16310,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45693</v>
+        <v>45388</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16331,7 +16326,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16374,7 +16369,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 58324-2022</t>
+          <t>A 56614-2022</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16388,10 +16383,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>44901</v>
+        <v>44893</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16404,7 +16399,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.9</v>
+        <v>5.6</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16447,7 +16442,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 22719-2023</t>
+          <t>A 25826-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16461,10 +16456,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45071</v>
+        <v>45467</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16477,7 +16472,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16520,7 +16515,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 5515-2025</t>
+          <t>A 17129-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16534,10 +16529,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45693</v>
+        <v>45034</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16550,7 +16545,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16593,7 +16588,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 58317-2021</t>
+          <t>A 2798-2022</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16607,10 +16602,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>44488</v>
+        <v>44581</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16623,7 +16618,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>6.6</v>
+        <v>1.3</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16666,7 +16661,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 20861-2025</t>
+          <t>A 59960-2024</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16680,10 +16675,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45777</v>
+        <v>45642</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16696,7 +16691,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16739,7 +16734,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 42257-2025</t>
+          <t>A 60330-2024</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16753,10 +16748,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45904</v>
+        <v>45643</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16769,7 +16764,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>2.2</v>
+        <v>4.3</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16812,7 +16807,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 12533-2025</t>
+          <t>A 5437-2022</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16826,10 +16821,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45730</v>
+        <v>44595</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16842,7 +16837,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16885,7 +16880,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 4672-2025</t>
+          <t>A 21897-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16899,10 +16894,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45687</v>
+        <v>46150</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16915,7 +16910,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16958,7 +16953,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 51468-2025</t>
+          <t>A 36606-2023</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16972,10 +16967,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45950</v>
+        <v>45153</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16988,7 +16983,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>0.7</v>
+        <v>13.5</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17031,7 +17026,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 18003-2023</t>
+          <t>A 40630-2023</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17045,10 +17040,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45040</v>
+        <v>45170</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17061,7 +17056,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>18.5</v>
+        <v>1.1</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17104,7 +17099,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 18188-2024</t>
+          <t>A 3010-2024</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17118,10 +17113,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45420</v>
+        <v>45315</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17134,7 +17129,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>1.3</v>
+        <v>4.6</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17177,7 +17172,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 24075-2023</t>
+          <t>A 26108-2023</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17191,10 +17186,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45078</v>
+        <v>45091</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17207,7 +17202,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17250,7 +17245,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 18538-2022</t>
+          <t>A 42402-2023</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17264,10 +17259,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>44686</v>
+        <v>45180</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17280,7 +17275,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>3.9</v>
+        <v>1.6</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17323,7 +17318,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 5032-2023</t>
+          <t>A 48479-2025</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17337,10 +17332,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>44958</v>
+        <v>45936</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17352,8 +17347,13 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I222" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17396,7 +17396,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 60321-2024</t>
+          <t>A 3882-2025</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17410,10 +17410,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45643</v>
+        <v>45684</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17425,8 +17425,13 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I223" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17469,7 +17474,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 2117-2022</t>
+          <t>A 23826-2026</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17479,14 +17484,14 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>44578</v>
+        <v>46166</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17499,7 +17504,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>4.8</v>
+        <v>0.7</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17542,7 +17547,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 16424-2024</t>
+          <t>A 48850-2023</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17556,10 +17561,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45407</v>
+        <v>45209</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17572,7 +17577,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>9.800000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17615,7 +17620,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 17586-2023</t>
+          <t>A 40778-2024</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17625,14 +17630,14 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45034</v>
+        <v>45558</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17645,7 +17650,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>5.9</v>
+        <v>1.9</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17688,7 +17693,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 59960-2024</t>
+          <t>A 40778-2024</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17702,10 +17707,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45642</v>
+        <v>45558</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17718,7 +17723,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17761,7 +17766,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 28530-2024</t>
+          <t>A 18538-2022</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17775,10 +17780,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45478</v>
+        <v>44686</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17791,7 +17796,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>1.9</v>
+        <v>3.9</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17834,7 +17839,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 8452-2023</t>
+          <t>A 51019-2023</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17848,10 +17853,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>44977</v>
+        <v>45218</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17864,7 +17869,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -17907,7 +17912,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 35098-2023</t>
+          <t>A 28803-2022</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -17921,10 +17926,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45145</v>
+        <v>44749</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17937,7 +17942,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -17980,7 +17985,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 2948-2026</t>
+          <t>A 18188-2024</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -17994,10 +17999,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>46038</v>
+        <v>45420</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18010,7 +18015,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18053,7 +18058,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 8819-2025</t>
+          <t>A 44796-2022</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18067,10 +18072,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45712</v>
+        <v>44841</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18083,7 +18088,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>8.1</v>
+        <v>2.1</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18126,7 +18131,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 7387-2025</t>
+          <t>A 25568-2026</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18140,10 +18145,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45705</v>
+        <v>46177</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18156,7 +18161,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18199,7 +18204,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 20359-2025</t>
+          <t>A 37784-2023</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18213,10 +18218,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45775</v>
+        <v>45159</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18229,7 +18234,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18272,7 +18277,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 18842-2025</t>
+          <t>A 37787-2023</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18286,10 +18291,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45764</v>
+        <v>45159</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18302,7 +18307,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18345,7 +18350,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 21897-2026</t>
+          <t>A 37788-2023</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18359,10 +18364,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>46150</v>
+        <v>45159</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18375,7 +18380,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18418,7 +18423,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 44796-2022</t>
+          <t>A 59020-2023</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18428,14 +18433,14 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>44841</v>
+        <v>45252</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18448,7 +18453,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>2.1</v>
+        <v>3.7</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18491,7 +18496,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 57869-2022</t>
+          <t>A 50046-2023</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18505,10 +18510,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>44899</v>
+        <v>45215</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18521,7 +18526,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18564,7 +18569,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 50046-2023</t>
+          <t>A 35844-2024</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18578,10 +18583,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45215</v>
+        <v>45532</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18594,7 +18599,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18637,7 +18642,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 26883-2024</t>
+          <t>A 30993-2022</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18651,10 +18656,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45470</v>
+        <v>44768</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18667,7 +18672,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18710,7 +18715,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 51434-2022</t>
+          <t>A 21547-2022</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18724,10 +18729,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>44869</v>
+        <v>44706</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18740,7 +18745,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -18783,7 +18788,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 60468-2024</t>
+          <t>A 46037-2023</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -18797,10 +18802,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45643</v>
+        <v>45196</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18813,7 +18818,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -18856,7 +18861,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 48479-2025</t>
+          <t>A 27284-2026</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -18870,10 +18875,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45936</v>
+        <v>46188</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18885,13 +18890,8 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
-      <c r="H243" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I243" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -18934,7 +18934,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 35845-2024</t>
+          <t>A 51434-2022</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -18948,10 +18948,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45532</v>
+        <v>44869</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -18964,7 +18964,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19007,7 +19007,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 23826-2026</t>
+          <t>A 27593-2026</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19017,14 +19017,14 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>46166</v>
+        <v>46190</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19037,7 +19037,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19080,7 +19080,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 47461-2023</t>
+          <t>A 56616-2022</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19094,10 +19094,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45202</v>
+        <v>44893</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19110,7 +19110,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19153,7 +19153,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 40778-2024</t>
+          <t>A 10381-2022</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19167,10 +19167,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45558</v>
+        <v>44623</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19183,7 +19183,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19226,7 +19226,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 21311-2023</t>
+          <t>A 28163-2026</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19240,10 +19240,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>45062</v>
+        <v>46195</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19256,7 +19256,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19299,7 +19299,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 40778-2024</t>
+          <t>A 46-2024</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19313,10 +19313,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45558</v>
+        <v>45293</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19329,7 +19329,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>1.9</v>
+        <v>3.6</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19372,7 +19372,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 56619-2022</t>
+          <t>A 47461-2023</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19386,10 +19386,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>44893</v>
+        <v>45202</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19402,7 +19402,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19445,7 +19445,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 13673-2025</t>
+          <t>A 53559-2022</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19459,10 +19459,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>45736</v>
+        <v>44879</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19518,7 +19518,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 34433-2023</t>
+          <t>A 30004-2026</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19532,10 +19532,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45139</v>
+        <v>46202</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19547,8 +19547,13 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I252" t="n">
-        <v>9.6</v>
+        <v>1.7</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19591,7 +19596,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 25826-2024</t>
+          <t>A 72612-2021</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19605,10 +19610,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45467</v>
+        <v>44546</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19621,7 +19626,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -19664,7 +19669,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 54698-2022</t>
+          <t>A 62146-2023</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -19678,10 +19683,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>44883</v>
+        <v>45267</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19694,7 +19699,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -19737,7 +19742,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 8450-2023</t>
+          <t>A 4285-2025</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -19751,10 +19756,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>44977</v>
+        <v>45685</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19767,7 +19772,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>4.4</v>
+        <v>0.5</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -19810,7 +19815,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 4285-2025</t>
+          <t>A 29677-2026</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -19824,10 +19829,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>45685</v>
+        <v>46204</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19840,7 +19845,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>0.5</v>
+        <v>6.2</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -19883,7 +19888,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 37783-2023</t>
+          <t>A 61698-2021</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -19897,10 +19902,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>45159</v>
+        <v>44501</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -19913,7 +19918,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -19956,7 +19961,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 25568-2026</t>
+          <t>A 29961-2026</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -19970,10 +19975,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>46177</v>
+        <v>46205</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -19985,8 +19990,13 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I258" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20029,7 +20039,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 51019-2023</t>
+          <t>A 31159-2026</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20043,10 +20053,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>45218</v>
+        <v>46209</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20058,8 +20068,13 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I259" t="n">
-        <v>1.6</v>
+        <v>5</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20102,7 +20117,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 27284-2026</t>
+          <t>A 17586-2023</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -20112,14 +20127,14 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>46188</v>
+        <v>45034</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20132,7 +20147,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>1.1</v>
+        <v>5.9</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -20175,7 +20190,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 55840-2023</t>
+          <t>A 22721-2023</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -20189,10 +20204,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>45239</v>
+        <v>45071</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20205,7 +20220,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>5.6</v>
+        <v>1.5</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -20248,7 +20263,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 27593-2026</t>
+          <t>A 5436-2022</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -20262,10 +20277,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>46190</v>
+        <v>44595</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20278,7 +20293,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>2.9</v>
+        <v>11.3</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -20321,7 +20336,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 28163-2026</t>
+          <t>A 1944-2024</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -20335,10 +20350,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>46195</v>
+        <v>45308</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20351,7 +20366,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -20394,7 +20409,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 71963-2021</t>
+          <t>A 21588-2022</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -20408,10 +20423,10 @@
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>44544</v>
+        <v>44706</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20424,7 +20439,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -20467,7 +20482,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 4838-2022</t>
+          <t>A 61915-2022</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -20481,10 +20496,10 @@
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>44592</v>
+        <v>44917</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20497,7 +20512,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -20540,7 +20555,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>A 39962-2023</t>
+          <t>A 18932-2024</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -20554,10 +20569,10 @@
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>45168</v>
+        <v>45427</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20570,7 +20585,7 @@
         </is>
       </c>
       <c r="I266" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -20613,7 +20628,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>A 37898-2022</t>
+          <t>A 53584-2024</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -20627,10 +20642,10 @@
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>44811</v>
+        <v>45614</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20643,7 +20658,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -20686,7 +20701,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>A 61914-2022</t>
+          <t>A 1021-2023</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -20700,10 +20715,10 @@
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>44917</v>
+        <v>44935</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20716,7 +20731,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>7.4</v>
+        <v>5.3</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -20759,7 +20774,7 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>A 30004-2026</t>
+          <t>A 34863-2026</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -20773,10 +20788,10 @@
         </is>
       </c>
       <c r="D269" s="1" t="n">
-        <v>46202</v>
+        <v>46258</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20788,13 +20803,8 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
-      <c r="H269" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I269" t="n">
-        <v>1.7</v>
+        <v>13.9</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -20837,7 +20847,7 @@
     <row r="270" ht="15" customHeight="1">
       <c r="A270" t="inlineStr">
         <is>
-          <t>A 60330-2024</t>
+          <t>A 149-2023</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -20851,10 +20861,10 @@
         </is>
       </c>
       <c r="D270" s="1" t="n">
-        <v>45643</v>
+        <v>44928</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20867,7 +20877,7 @@
         </is>
       </c>
       <c r="I270" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>
@@ -20910,7 +20920,7 @@
     <row r="271" ht="15" customHeight="1">
       <c r="A271" t="inlineStr">
         <is>
-          <t>A 19386-2023</t>
+          <t>A 20266-2026</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -20924,10 +20934,10 @@
         </is>
       </c>
       <c r="D271" s="1" t="n">
-        <v>45049</v>
+        <v>46139</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -20940,7 +20950,7 @@
         </is>
       </c>
       <c r="I271" t="n">
-        <v>5.7</v>
+        <v>1.1</v>
       </c>
       <c r="J271" t="n">
         <v>0</v>
@@ -20983,7 +20993,7 @@
     <row r="272" ht="15" customHeight="1">
       <c r="A272" t="inlineStr">
         <is>
-          <t>A 29677-2026</t>
+          <t>A 8819-2025</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -20997,10 +21007,10 @@
         </is>
       </c>
       <c r="D272" s="1" t="n">
-        <v>46204</v>
+        <v>45712</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21013,7 +21023,7 @@
         </is>
       </c>
       <c r="I272" t="n">
-        <v>6.2</v>
+        <v>8.1</v>
       </c>
       <c r="J272" t="n">
         <v>0</v>
@@ -21056,7 +21066,7 @@
     <row r="273" ht="15" customHeight="1">
       <c r="A273" t="inlineStr">
         <is>
-          <t>A 55310-2023</t>
+          <t>A 13960-2024</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -21070,10 +21080,10 @@
         </is>
       </c>
       <c r="D273" s="1" t="n">
-        <v>45237</v>
+        <v>45392</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21086,7 +21096,7 @@
         </is>
       </c>
       <c r="I273" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="J273" t="n">
         <v>0</v>
@@ -21129,7 +21139,7 @@
     <row r="274" ht="15" customHeight="1">
       <c r="A274" t="inlineStr">
         <is>
-          <t>A 31159-2026</t>
+          <t>A 19386-2023</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -21143,10 +21153,10 @@
         </is>
       </c>
       <c r="D274" s="1" t="n">
-        <v>46209</v>
+        <v>45049</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21158,13 +21168,8 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
-      <c r="H274" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I274" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="J274" t="n">
         <v>0</v>
@@ -21207,7 +21212,7 @@
     <row r="275" ht="15" customHeight="1">
       <c r="A275" t="inlineStr">
         <is>
-          <t>A 29961-2026</t>
+          <t>A 35044-2026</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -21221,10 +21226,10 @@
         </is>
       </c>
       <c r="D275" s="1" t="n">
-        <v>46205</v>
+        <v>46259</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21236,13 +21241,8 @@
           <t>FÄRGELANDA</t>
         </is>
       </c>
-      <c r="H275" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I275" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J275" t="n">
         <v>0</v>
@@ -21285,7 +21285,7 @@
     <row r="276" ht="15" customHeight="1">
       <c r="A276" t="inlineStr">
         <is>
-          <t>A 34015-2026</t>
+          <t>A 39962-2023</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -21299,10 +21299,10 @@
         </is>
       </c>
       <c r="D276" s="1" t="n">
-        <v>46252</v>
+        <v>45168</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
         </is>
       </c>
       <c r="I276" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="J276" t="n">
         <v>0</v>
@@ -21358,7 +21358,7 @@
     <row r="277" ht="15" customHeight="1">
       <c r="A277" t="inlineStr">
         <is>
-          <t>A 52151-2022</t>
+          <t>A 45833-2022</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -21372,10 +21372,10 @@
         </is>
       </c>
       <c r="D277" s="1" t="n">
-        <v>44873</v>
+        <v>44846</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21388,7 +21388,7 @@
         </is>
       </c>
       <c r="I277" t="n">
-        <v>7.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J277" t="n">
         <v>0</v>
@@ -21431,7 +21431,7 @@
     <row r="278" ht="15" customHeight="1">
       <c r="A278" t="inlineStr">
         <is>
-          <t>A 62643-2023</t>
+          <t>A 17610-2023</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -21445,10 +21445,10 @@
         </is>
       </c>
       <c r="D278" s="1" t="n">
-        <v>45271</v>
+        <v>45036</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21461,7 +21461,7 @@
         </is>
       </c>
       <c r="I278" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="J278" t="n">
         <v>0</v>
@@ -21504,7 +21504,7 @@
     <row r="279" ht="15" customHeight="1">
       <c r="A279" t="inlineStr">
         <is>
-          <t>A 35844-2024</t>
+          <t>A 35507-2026</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -21518,10 +21518,10 @@
         </is>
       </c>
       <c r="D279" s="1" t="n">
-        <v>45532</v>
+        <v>46262</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21534,7 +21534,7 @@
         </is>
       </c>
       <c r="I279" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J279" t="n">
         <v>0</v>
@@ -21594,7 +21594,7 @@
         <v>45324</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21650,7 +21650,7 @@
     <row r="281" ht="15" customHeight="1">
       <c r="A281" t="inlineStr">
         <is>
-          <t>A 40630-2023</t>
+          <t>A 8185-2023</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -21664,10 +21664,10 @@
         </is>
       </c>
       <c r="D281" s="1" t="n">
-        <v>45170</v>
+        <v>44974</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21680,7 +21680,7 @@
         </is>
       </c>
       <c r="I281" t="n">
-        <v>1.1</v>
+        <v>7.1</v>
       </c>
       <c r="J281" t="n">
         <v>0</v>
@@ -21723,7 +21723,7 @@
     <row r="282" ht="15" customHeight="1">
       <c r="A282" t="inlineStr">
         <is>
-          <t>A 20266-2026</t>
+          <t>A 34433-2023</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -21737,10 +21737,10 @@
         </is>
       </c>
       <c r="D282" s="1" t="n">
-        <v>46139</v>
+        <v>45139</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21753,7 +21753,7 @@
         </is>
       </c>
       <c r="I282" t="n">
-        <v>1.1</v>
+        <v>9.6</v>
       </c>
       <c r="J282" t="n">
         <v>0</v>
@@ -21796,7 +21796,7 @@
     <row r="283" ht="15" customHeight="1">
       <c r="A283" t="inlineStr">
         <is>
-          <t>A 34715-2023</t>
+          <t>A 5032-2023</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -21810,10 +21810,10 @@
         </is>
       </c>
       <c r="D283" s="1" t="n">
-        <v>45141</v>
+        <v>44958</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -21826,7 +21826,7 @@
         </is>
       </c>
       <c r="I283" t="n">
-        <v>7.2</v>
+        <v>3.3</v>
       </c>
       <c r="J283" t="n">
         <v>0</v>
@@ -21869,7 +21869,7 @@
     <row r="284" ht="15" customHeight="1">
       <c r="A284" t="inlineStr">
         <is>
-          <t>A 35044-2026</t>
+          <t>A 35173-2024</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -21883,10 +21883,10 @@
         </is>
       </c>
       <c r="D284" s="1" t="n">
-        <v>46259</v>
+        <v>45530</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -21899,7 +21899,7 @@
         </is>
       </c>
       <c r="I284" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="J284" t="n">
         <v>0</v>
@@ -21942,7 +21942,7 @@
     <row r="285" ht="15" customHeight="1">
       <c r="A285" t="inlineStr">
         <is>
-          <t>A 34863-2026</t>
+          <t>A 18178-2025</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -21956,10 +21956,10 @@
         </is>
       </c>
       <c r="D285" s="1" t="n">
-        <v>46258</v>
+        <v>45761</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -21972,7 +21972,7 @@
         </is>
       </c>
       <c r="I285" t="n">
-        <v>13.9</v>
+        <v>2</v>
       </c>
       <c r="J285" t="n">
         <v>0</v>
@@ -22015,7 +22015,7 @@
     <row r="286" ht="15" customHeight="1">
       <c r="A286" t="inlineStr">
         <is>
-          <t>A 1678-2025</t>
+          <t>A 57991-2023</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -22029,10 +22029,10 @@
         </is>
       </c>
       <c r="D286" s="1" t="n">
-        <v>45670</v>
+        <v>45247</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         </is>
       </c>
       <c r="I286" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J286" t="n">
         <v>0</v>
@@ -22088,7 +22088,7 @@
     <row r="287" ht="15" customHeight="1">
       <c r="A287" t="inlineStr">
         <is>
-          <t>A 35507-2026</t>
+          <t>A 17456-2024</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -22102,10 +22102,10 @@
         </is>
       </c>
       <c r="D287" s="1" t="n">
-        <v>46262</v>
+        <v>45415</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22118,7 +22118,7 @@
         </is>
       </c>
       <c r="I287" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J287" t="n">
         <v>0</v>
@@ -22161,7 +22161,7 @@
     <row r="288" ht="15" customHeight="1">
       <c r="A288" t="inlineStr">
         <is>
-          <t>A 59020-2023</t>
+          <t>A 18842-2025</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -22171,14 +22171,14 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D288" s="1" t="n">
-        <v>45252</v>
+        <v>45764</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22191,7 +22191,7 @@
         </is>
       </c>
       <c r="I288" t="n">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="J288" t="n">
         <v>0</v>
@@ -22234,7 +22234,7 @@
     <row r="289" ht="15" customHeight="1">
       <c r="A289" t="inlineStr">
         <is>
-          <t>A 6666-2025</t>
+          <t>A 14015-2025</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -22248,10 +22248,10 @@
         </is>
       </c>
       <c r="D289" s="1" t="n">
-        <v>45700</v>
+        <v>45740</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22264,7 +22264,7 @@
         </is>
       </c>
       <c r="I289" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J289" t="n">
         <v>0</v>
@@ -22307,7 +22307,7 @@
     <row r="290" ht="15" customHeight="1">
       <c r="A290" t="inlineStr">
         <is>
-          <t>A 53559-2022</t>
+          <t>A 22679-2026</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -22317,14 +22317,14 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D290" s="1" t="n">
-        <v>44879</v>
+        <v>46156</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22337,7 +22337,7 @@
         </is>
       </c>
       <c r="I290" t="n">
-        <v>0.4</v>
+        <v>20.6</v>
       </c>
       <c r="J290" t="n">
         <v>0</v>
@@ -22380,7 +22380,7 @@
     <row r="291" ht="15" customHeight="1">
       <c r="A291" t="inlineStr">
         <is>
-          <t>A 27521-2024</t>
+          <t>A 19389-2023</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -22394,10 +22394,10 @@
         </is>
       </c>
       <c r="D291" s="1" t="n">
-        <v>45474</v>
+        <v>45049</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22410,7 +22410,7 @@
         </is>
       </c>
       <c r="I291" t="n">
-        <v>4.3</v>
+        <v>2.2</v>
       </c>
       <c r="J291" t="n">
         <v>0</v>
@@ -22453,7 +22453,7 @@
     <row r="292" ht="15" customHeight="1">
       <c r="A292" t="inlineStr">
         <is>
-          <t>A 8185-2023</t>
+          <t>A 37789-2026</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -22467,10 +22467,10 @@
         </is>
       </c>
       <c r="D292" s="1" t="n">
-        <v>44974</v>
+        <v>46279</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22483,7 +22483,7 @@
         </is>
       </c>
       <c r="I292" t="n">
-        <v>7.1</v>
+        <v>2.5</v>
       </c>
       <c r="J292" t="n">
         <v>0</v>
@@ -22526,7 +22526,7 @@
     <row r="293" ht="15" customHeight="1">
       <c r="A293" t="inlineStr">
         <is>
-          <t>A 18932-2024</t>
+          <t>A 34241-2024</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -22540,10 +22540,10 @@
         </is>
       </c>
       <c r="D293" s="1" t="n">
-        <v>45427</v>
+        <v>45524</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22556,7 +22556,7 @@
         </is>
       </c>
       <c r="I293" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J293" t="n">
         <v>0</v>
@@ -22599,7 +22599,7 @@
     <row r="294" ht="15" customHeight="1">
       <c r="A294" t="inlineStr">
         <is>
-          <t>A 56614-2022</t>
+          <t>A 27521-2024</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -22613,10 +22613,10 @@
         </is>
       </c>
       <c r="D294" s="1" t="n">
-        <v>44893</v>
+        <v>45474</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22629,7 +22629,7 @@
         </is>
       </c>
       <c r="I294" t="n">
-        <v>5.6</v>
+        <v>4.3</v>
       </c>
       <c r="J294" t="n">
         <v>0</v>
@@ -22672,7 +22672,7 @@
     <row r="295" ht="15" customHeight="1">
       <c r="A295" t="inlineStr">
         <is>
-          <t>A 18186-2024</t>
+          <t>A 7387-2025</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -22686,10 +22686,10 @@
         </is>
       </c>
       <c r="D295" s="1" t="n">
-        <v>45420</v>
+        <v>45705</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22702,7 +22702,7 @@
         </is>
       </c>
       <c r="I295" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J295" t="n">
         <v>0</v>
@@ -22745,7 +22745,7 @@
     <row r="296" ht="15" customHeight="1">
       <c r="A296" t="inlineStr">
         <is>
-          <t>A 5437-2022</t>
+          <t>A 44846-2024</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -22755,14 +22755,14 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D296" s="1" t="n">
-        <v>44595</v>
+        <v>45574</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -22775,7 +22775,7 @@
         </is>
       </c>
       <c r="I296" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J296" t="n">
         <v>0</v>
@@ -22818,7 +22818,7 @@
     <row r="297" ht="15" customHeight="1">
       <c r="A297" t="inlineStr">
         <is>
-          <t>A 72655-2021</t>
+          <t>A 32534-2026</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -22832,10 +22832,10 @@
         </is>
       </c>
       <c r="D297" s="1" t="n">
-        <v>44546</v>
+        <v>46239</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -22848,7 +22848,7 @@
         </is>
       </c>
       <c r="I297" t="n">
-        <v>2.5</v>
+        <v>7.4</v>
       </c>
       <c r="J297" t="n">
         <v>0</v>
@@ -22908,7 +22908,7 @@
         <v>44777</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -22964,7 +22964,7 @@
     <row r="299" ht="15" customHeight="1">
       <c r="A299" t="inlineStr">
         <is>
-          <t>A 44846-2024</t>
+          <t>A 1030-2022</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -22974,14 +22974,14 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D299" s="1" t="n">
-        <v>45574</v>
+        <v>44571</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -22994,7 +22994,7 @@
         </is>
       </c>
       <c r="I299" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J299" t="n">
         <v>0</v>
@@ -23037,7 +23037,7 @@
     <row r="300" ht="15" customHeight="1">
       <c r="A300" t="inlineStr">
         <is>
-          <t>A 28803-2022</t>
+          <t>A 34715-2023</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -23051,10 +23051,10 @@
         </is>
       </c>
       <c r="D300" s="1" t="n">
-        <v>44749</v>
+        <v>45141</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23067,7 +23067,7 @@
         </is>
       </c>
       <c r="I300" t="n">
-        <v>1.6</v>
+        <v>7.2</v>
       </c>
       <c r="J300" t="n">
         <v>0</v>
@@ -23110,7 +23110,7 @@
     <row r="301" ht="15" customHeight="1">
       <c r="A301" t="inlineStr">
         <is>
-          <t>A 17456-2024</t>
+          <t>A 1678-2025</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -23124,10 +23124,10 @@
         </is>
       </c>
       <c r="D301" s="1" t="n">
-        <v>45415</v>
+        <v>45670</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23140,7 +23140,7 @@
         </is>
       </c>
       <c r="I301" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J301" t="n">
         <v>0</v>
@@ -23183,7 +23183,7 @@
     <row r="302" ht="15" customHeight="1">
       <c r="A302" t="inlineStr">
         <is>
-          <t>A 57267-2022</t>
+          <t>A 37783-2023</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -23197,10 +23197,10 @@
         </is>
       </c>
       <c r="D302" s="1" t="n">
-        <v>44895</v>
+        <v>45159</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23213,7 +23213,7 @@
         </is>
       </c>
       <c r="I302" t="n">
-        <v>7.2</v>
+        <v>0.5</v>
       </c>
       <c r="J302" t="n">
         <v>0</v>
@@ -23256,7 +23256,7 @@
     <row r="303" ht="15" customHeight="1">
       <c r="A303" t="inlineStr">
         <is>
-          <t>A 22679-2026</t>
+          <t>A 64390-2023</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -23266,14 +23266,14 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D303" s="1" t="n">
-        <v>46156</v>
+        <v>45280</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23286,7 +23286,7 @@
         </is>
       </c>
       <c r="I303" t="n">
-        <v>20.6</v>
+        <v>7.4</v>
       </c>
       <c r="J303" t="n">
         <v>0</v>
@@ -23329,7 +23329,7 @@
     <row r="304" ht="15" customHeight="1">
       <c r="A304" t="inlineStr">
         <is>
-          <t>A 37784-2023</t>
+          <t>A 3657-2024</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -23343,10 +23343,10 @@
         </is>
       </c>
       <c r="D304" s="1" t="n">
-        <v>45159</v>
+        <v>45321</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23359,7 +23359,7 @@
         </is>
       </c>
       <c r="I304" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J304" t="n">
         <v>0</v>
@@ -23402,7 +23402,7 @@
     <row r="305" ht="15" customHeight="1">
       <c r="A305" t="inlineStr">
         <is>
-          <t>A 37787-2023</t>
+          <t>A 38658-2026</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -23416,10 +23416,10 @@
         </is>
       </c>
       <c r="D305" s="1" t="n">
-        <v>45159</v>
+        <v>46281</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23432,7 +23432,7 @@
         </is>
       </c>
       <c r="I305" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J305" t="n">
         <v>0</v>
@@ -23475,7 +23475,7 @@
     <row r="306" ht="15" customHeight="1">
       <c r="A306" t="inlineStr">
         <is>
-          <t>A 37788-2023</t>
+          <t>A 60475-2024</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -23489,10 +23489,10 @@
         </is>
       </c>
       <c r="D306" s="1" t="n">
-        <v>45159</v>
+        <v>45643</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23505,7 +23505,7 @@
         </is>
       </c>
       <c r="I306" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J306" t="n">
         <v>0</v>
@@ -23548,7 +23548,7 @@
     <row r="307" ht="15" customHeight="1">
       <c r="A307" t="inlineStr">
         <is>
-          <t>A 13559-2024</t>
+          <t>A 16424-2024</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -23562,10 +23562,10 @@
         </is>
       </c>
       <c r="D307" s="1" t="n">
-        <v>45388</v>
+        <v>45407</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23578,7 +23578,7 @@
         </is>
       </c>
       <c r="I307" t="n">
-        <v>2.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J307" t="n">
         <v>0</v>
@@ -23621,7 +23621,7 @@
     <row r="308" ht="15" customHeight="1">
       <c r="A308" t="inlineStr">
         <is>
-          <t>A 37789-2026</t>
+          <t>A 4672-2025</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -23635,10 +23635,10 @@
         </is>
       </c>
       <c r="D308" s="1" t="n">
-        <v>46279</v>
+        <v>45687</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23651,7 +23651,7 @@
         </is>
       </c>
       <c r="I308" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="J308" t="n">
         <v>0</v>
@@ -23694,7 +23694,7 @@
     <row r="309" ht="15" customHeight="1">
       <c r="A309" t="inlineStr">
         <is>
-          <t>A 10381-2022</t>
+          <t>A 63176-2023</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -23708,10 +23708,10 @@
         </is>
       </c>
       <c r="D309" s="1" t="n">
-        <v>44623</v>
+        <v>45273</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23724,7 +23724,7 @@
         </is>
       </c>
       <c r="I309" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J309" t="n">
         <v>0</v>
@@ -23767,7 +23767,7 @@
     <row r="310" ht="15" customHeight="1">
       <c r="A310" t="inlineStr">
         <is>
-          <t>A 17129-2023</t>
+          <t>A 32904-2026</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -23781,10 +23781,10 @@
         </is>
       </c>
       <c r="D310" s="1" t="n">
-        <v>45034</v>
+        <v>46244</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -23797,7 +23797,7 @@
         </is>
       </c>
       <c r="I310" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J310" t="n">
         <v>0</v>
@@ -23840,7 +23840,7 @@
     <row r="311" ht="15" customHeight="1">
       <c r="A311" t="inlineStr">
         <is>
-          <t>A 22721-2023</t>
+          <t>A 12507-2025</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -23854,10 +23854,10 @@
         </is>
       </c>
       <c r="D311" s="1" t="n">
-        <v>45071</v>
+        <v>45730</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -23870,7 +23870,7 @@
         </is>
       </c>
       <c r="I311" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J311" t="n">
         <v>0</v>
@@ -23913,7 +23913,7 @@
     <row r="312" ht="15" customHeight="1">
       <c r="A312" t="inlineStr">
         <is>
-          <t>A 20736-2025</t>
+          <t>A 14018-2025</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -23927,10 +23927,10 @@
         </is>
       </c>
       <c r="D312" s="1" t="n">
-        <v>45776</v>
+        <v>45740</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -23943,7 +23943,7 @@
         </is>
       </c>
       <c r="I312" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J312" t="n">
         <v>0</v>
@@ -23986,7 +23986,7 @@
     <row r="313" ht="15" customHeight="1">
       <c r="A313" t="inlineStr">
         <is>
-          <t>A 21126-2025</t>
+          <t>A 28106-2026</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -24000,10 +24000,10 @@
         </is>
       </c>
       <c r="D313" s="1" t="n">
-        <v>45777</v>
+        <v>46195</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24016,7 +24016,7 @@
         </is>
       </c>
       <c r="I313" t="n">
-        <v>5.2</v>
+        <v>1.6</v>
       </c>
       <c r="J313" t="n">
         <v>0</v>
@@ -24059,7 +24059,7 @@
     <row r="314" ht="15" customHeight="1">
       <c r="A314" t="inlineStr">
         <is>
-          <t>A 21125-2025</t>
+          <t>A 40213-2025</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -24073,10 +24073,10 @@
         </is>
       </c>
       <c r="D314" s="1" t="n">
-        <v>45777</v>
+        <v>45894</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24089,7 +24089,7 @@
         </is>
       </c>
       <c r="I314" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="J314" t="n">
         <v>0</v>
@@ -24132,7 +24132,7 @@
     <row r="315" ht="15" customHeight="1">
       <c r="A315" t="inlineStr">
         <is>
-          <t>A 38658-2026</t>
+          <t>A 20736-2025</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -24146,10 +24146,10 @@
         </is>
       </c>
       <c r="D315" s="1" t="n">
-        <v>46281</v>
+        <v>45776</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24162,7 +24162,7 @@
         </is>
       </c>
       <c r="I315" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J315" t="n">
         <v>0</v>
@@ -24205,7 +24205,7 @@
     <row r="316" ht="15" customHeight="1">
       <c r="A316" t="inlineStr">
         <is>
-          <t>A 32534-2026</t>
+          <t>A 21126-2025</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -24219,10 +24219,10 @@
         </is>
       </c>
       <c r="D316" s="1" t="n">
-        <v>46239</v>
+        <v>45777</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24235,7 +24235,7 @@
         </is>
       </c>
       <c r="I316" t="n">
-        <v>7.4</v>
+        <v>5.2</v>
       </c>
       <c r="J316" t="n">
         <v>0</v>
@@ -24278,7 +24278,7 @@
     <row r="317" ht="15" customHeight="1">
       <c r="A317" t="inlineStr">
         <is>
-          <t>A 16828-2023</t>
+          <t>A 21125-2025</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -24292,10 +24292,10 @@
         </is>
       </c>
       <c r="D317" s="1" t="n">
-        <v>45033</v>
+        <v>45777</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24308,7 +24308,7 @@
         </is>
       </c>
       <c r="I317" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="J317" t="n">
         <v>0</v>
@@ -24351,7 +24351,7 @@
     <row r="318" ht="15" customHeight="1">
       <c r="A318" t="inlineStr">
         <is>
-          <t>A 6322-2024</t>
+          <t>A 16828-2023</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -24365,10 +24365,10 @@
         </is>
       </c>
       <c r="D318" s="1" t="n">
-        <v>45338</v>
+        <v>45033</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24381,7 +24381,7 @@
         </is>
       </c>
       <c r="I318" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J318" t="n">
         <v>0</v>
@@ -24424,7 +24424,7 @@
     <row r="319" ht="15" customHeight="1">
       <c r="A319" t="inlineStr">
         <is>
-          <t>A 28106-2026</t>
+          <t>A 39253-2026</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -24438,10 +24438,10 @@
         </is>
       </c>
       <c r="D319" s="1" t="n">
-        <v>46195</v>
+        <v>46288</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24454,7 +24454,7 @@
         </is>
       </c>
       <c r="I319" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J319" t="n">
         <v>0</v>
@@ -24497,7 +24497,7 @@
     <row r="320" ht="15" customHeight="1">
       <c r="A320" t="inlineStr">
         <is>
-          <t>A 40213-2025</t>
+          <t>A 6322-2024</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -24511,10 +24511,10 @@
         </is>
       </c>
       <c r="D320" s="1" t="n">
-        <v>45894</v>
+        <v>45338</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24527,7 +24527,7 @@
         </is>
       </c>
       <c r="I320" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J320" t="n">
         <v>0</v>
@@ -24570,7 +24570,7 @@
     <row r="321" ht="15" customHeight="1">
       <c r="A321" t="inlineStr">
         <is>
-          <t>A 32904-2026</t>
+          <t>A 60382-2023</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -24584,10 +24584,10 @@
         </is>
       </c>
       <c r="D321" s="1" t="n">
-        <v>46244</v>
+        <v>45259</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24600,7 +24600,7 @@
         </is>
       </c>
       <c r="I321" t="n">
-        <v>0.8</v>
+        <v>4.8</v>
       </c>
       <c r="J321" t="n">
         <v>0</v>
@@ -24643,7 +24643,7 @@
     <row r="322" ht="15" customHeight="1">
       <c r="A322" t="inlineStr">
         <is>
-          <t>A 39253-2026</t>
+          <t>A 34015-2026</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -24657,10 +24657,10 @@
         </is>
       </c>
       <c r="D322" s="1" t="n">
-        <v>46288</v>
+        <v>46252</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24673,7 +24673,7 @@
         </is>
       </c>
       <c r="I322" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="J322" t="n">
         <v>0</v>
@@ -24716,7 +24716,7 @@
     <row r="323" ht="15" customHeight="1">
       <c r="A323" t="inlineStr">
         <is>
-          <t>A 33591-2026</t>
+          <t>A 33593-2026</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -24733,7 +24733,7 @@
         <v>46248</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -24746,7 +24746,7 @@
         </is>
       </c>
       <c r="I323" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J323" t="n">
         <v>0</v>
@@ -24789,7 +24789,7 @@
     <row r="324" ht="15" customHeight="1">
       <c r="A324" t="inlineStr">
         <is>
-          <t>A 33722-2026</t>
+          <t>A 33591-2026</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -24803,10 +24803,10 @@
         </is>
       </c>
       <c r="D324" s="1" t="n">
-        <v>46251</v>
+        <v>46248</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -24819,7 +24819,7 @@
         </is>
       </c>
       <c r="I324" t="n">
-        <v>12.5</v>
+        <v>1.6</v>
       </c>
       <c r="J324" t="n">
         <v>0</v>
@@ -24862,7 +24862,7 @@
     <row r="325" ht="15" customHeight="1">
       <c r="A325" t="inlineStr">
         <is>
-          <t>A 33726-2026</t>
+          <t>A 33722-2026</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -24879,7 +24879,7 @@
         <v>46251</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -24892,7 +24892,7 @@
         </is>
       </c>
       <c r="I325" t="n">
-        <v>0.7</v>
+        <v>12.5</v>
       </c>
       <c r="J325" t="n">
         <v>0</v>
@@ -24935,7 +24935,7 @@
     <row r="326" ht="15" customHeight="1">
       <c r="A326" t="inlineStr">
         <is>
-          <t>A 33593-2026</t>
+          <t>A 33726-2026</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -24949,10 +24949,10 @@
         </is>
       </c>
       <c r="D326" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -24965,7 +24965,7 @@
         </is>
       </c>
       <c r="I326" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J326" t="n">
         <v>0</v>
@@ -25025,7 +25025,7 @@
         <v>45491</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>

--- a/Översikt FÄRGELANDA.xlsx
+++ b/Översikt FÄRGELANDA.xlsx
@@ -601,7 +601,7 @@
         <v>44785</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45904</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>45303</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44935</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>46239</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>45242</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>45547</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>46175</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>45078</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>44504</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>44453</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>45474</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>45714</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>44911</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>45246</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>45766</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>45153</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>44837</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>44490</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>44595</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>44557</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>44490</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>44516</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>44525</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>44475</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>44526</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>44670</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>44658</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>44602</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>44496</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         <v>44566</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>44684</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>44593</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         <v>44858</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>44550</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>44711</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>44670</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>44518</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         <v>44572</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         <v>44686</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>44490</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>44750</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>44777</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v>44490</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4427,7 +4427,7 @@
         <v>44636</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>45273</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>45418</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>45419</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>45315</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         <v>45558</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>44581</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         <v>44928</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         <v>45079</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>44706</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>44706</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
         <v>45091</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         <v>44899</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5381,7 +5381,7 @@
         <v>45384</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>44600</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>45049</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         <v>45687</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
         <v>44998</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>45259</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         <v>46007</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>45244</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>44916</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         <v>45743</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>45740</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         <v>45890</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>45895</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>45894</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>45740</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6476,7 +6476,7 @@
         <v>45758</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>44846</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         <v>45714</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>45196</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         <v>45071</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
         <v>46037</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>45904</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6987,7 +6987,7 @@
         <v>45209</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         <v>45419</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7138,7 +7138,7 @@
         <v>44595</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>44488</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>45917</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         <v>45796</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         <v>45799</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         <v>45355</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>45799</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         <v>45212</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7722,7 +7722,7 @@
         <v>45800</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7795,7 +7795,7 @@
         <v>45805</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>45918</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>46055</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8014,7 +8014,7 @@
         <v>46052</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8087,7 +8087,7 @@
         <v>46058</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>45321</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         <v>46063</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>45351</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         <v>45351</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         <v>45932</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8530,7 +8530,7 @@
         <v>45811</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         <v>44578</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         <v>44896</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>46066</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>44974</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>46069</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8978,7 +8978,7 @@
         <v>44501</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9051,7 +9051,7 @@
         <v>45598</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9124,7 +9124,7 @@
         <v>46069</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>46071</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         <v>46071</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         <v>45937</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>46076</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         <v>45946</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9567,7 +9567,7 @@
         <v>45946</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9640,7 +9640,7 @@
         <v>46080</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>46080</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
         <v>45949</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9859,7 +9859,7 @@
         <v>44546</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9932,7 +9932,7 @@
         <v>45950</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>45950</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>45180</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10151,7 +10151,7 @@
         <v>45957</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
         <v>45260</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>45958</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10370,7 +10370,7 @@
         <v>46086</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>46087</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>45280</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10589,7 +10589,7 @@
         <v>45324</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>44939</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10735,7 +10735,7 @@
         <v>46091</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10808,7 +10808,7 @@
         <v>45965</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
         <v>44522</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10954,7 +10954,7 @@
         <v>45965</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11027,7 +11027,7 @@
         <v>45965</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11100,7 +11100,7 @@
         <v>45815</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11173,7 +11173,7 @@
         <v>45969</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>45969</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11319,7 +11319,7 @@
         <v>45015</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11392,7 +11392,7 @@
         <v>44571</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11465,7 +11465,7 @@
         <v>45247</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11538,7 +11538,7 @@
         <v>45049</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
         <v>45975</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11689,7 +11689,7 @@
         <v>45975</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11767,7 +11767,7 @@
         <v>46101</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11840,7 +11840,7 @@
         <v>45614</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>46107</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11986,7 +11986,7 @@
         <v>45036</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12059,7 +12059,7 @@
         <v>45987</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12132,7 +12132,7 @@
         <v>46113</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12205,7 +12205,7 @@
         <v>45989</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>46119</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         <v>44893</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>44935</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
         <v>46121</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12575,7 +12575,7 @@
         <v>46121</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12653,7 +12653,7 @@
         <v>45958</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12726,7 +12726,7 @@
         <v>46121</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12799,7 +12799,7 @@
         <v>46121</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12877,7 +12877,7 @@
         <v>46121</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12950,7 +12950,7 @@
         <v>46124</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13023,7 +13023,7 @@
         <v>45582</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13096,7 +13096,7 @@
         <v>46125</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13174,7 +13174,7 @@
         <v>45280</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13247,7 +13247,7 @@
         <v>45638</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13320,7 +13320,7 @@
         <v>45987</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13393,7 +13393,7 @@
         <v>45831</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13466,7 +13466,7 @@
         <v>44526</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13539,7 +13539,7 @@
         <v>45832</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13612,7 +13612,7 @@
         <v>45252</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13685,7 +13685,7 @@
         <v>45252</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13758,7 +13758,7 @@
         <v>46134</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
         <v>45524</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
         <v>45835</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>45894</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>45098</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>45835</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14196,7 +14196,7 @@
         <v>45835</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>45481</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14342,7 +14342,7 @@
         <v>46136</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14415,7 +14415,7 @@
         <v>45491</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14488,7 +14488,7 @@
         <v>45362</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14561,7 +14561,7 @@
         <v>45693</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14634,7 +14634,7 @@
         <v>45846</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14707,7 +14707,7 @@
         <v>45267</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14780,7 +14780,7 @@
         <v>45153</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14853,7 +14853,7 @@
         <v>45684</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>45693</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15004,7 +15004,7 @@
         <v>45777</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>45904</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15150,7 +15150,7 @@
         <v>45730</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15223,7 +15223,7 @@
         <v>45308</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15296,7 +15296,7 @@
         <v>45950</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15369,7 +15369,7 @@
         <v>45530</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>45761</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15515,7 +15515,7 @@
         <v>44917</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>44837</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15661,7 +15661,7 @@
         <v>45740</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15734,7 +15734,7 @@
         <v>44578</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15807,7 +15807,7 @@
         <v>45452</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15880,7 +15880,7 @@
         <v>45643</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15953,7 +15953,7 @@
         <v>45730</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16026,7 +16026,7 @@
         <v>44768</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16099,7 +16099,7 @@
         <v>45642</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16172,7 +16172,7 @@
         <v>45478</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16245,7 +16245,7 @@
         <v>46038</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16318,7 +16318,7 @@
         <v>45392</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16391,7 +16391,7 @@
         <v>45293</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>44638</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16537,7 +16537,7 @@
         <v>46150</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16610,7 +16610,7 @@
         <v>44901</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16683,7 +16683,7 @@
         <v>45071</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16756,7 +16756,7 @@
         <v>45936</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16834,7 +16834,7 @@
         <v>45875</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         <v>44488</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16980,7 +16980,7 @@
         <v>46166</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17053,7 +17053,7 @@
         <v>45687</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17126,7 +17126,7 @@
         <v>45040</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17199,7 +17199,7 @@
         <v>45420</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17272,7 +17272,7 @@
         <v>45757</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>45078</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17418,7 +17418,7 @@
         <v>44686</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17491,7 +17491,7 @@
         <v>45558</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
         <v>44958</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17637,7 +17637,7 @@
         <v>45558</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17710,7 +17710,7 @@
         <v>45643</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>45883</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17856,7 +17856,7 @@
         <v>45407</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17929,7 +17929,7 @@
         <v>45883</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>45034</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18075,7 +18075,7 @@
         <v>45757</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18148,7 +18148,7 @@
         <v>44977</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>46177</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>45145</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18367,7 +18367,7 @@
         <v>45712</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18440,7 +18440,7 @@
         <v>45705</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18513,7 +18513,7 @@
         <v>46188</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18586,7 +18586,7 @@
         <v>45775</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18659,7 +18659,7 @@
         <v>46190</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18732,7 +18732,7 @@
         <v>45764</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
         <v>46195</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18878,7 +18878,7 @@
         <v>44841</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18951,7 +18951,7 @@
         <v>44899</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19024,7 +19024,7 @@
         <v>45215</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19097,7 +19097,7 @@
         <v>45470</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19170,7 +19170,7 @@
         <v>44869</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19243,7 +19243,7 @@
         <v>45643</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19316,7 +19316,7 @@
         <v>46202</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19394,7 +19394,7 @@
         <v>46204</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19467,7 +19467,7 @@
         <v>45532</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19540,7 +19540,7 @@
         <v>46209</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>45202</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19691,7 +19691,7 @@
         <v>46205</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19769,7 +19769,7 @@
         <v>45062</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>46139</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19915,7 +19915,7 @@
         <v>44893</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -19988,7 +19988,7 @@
         <v>46259</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20061,7 +20061,7 @@
         <v>46258</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20134,7 +20134,7 @@
         <v>45736</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20207,7 +20207,7 @@
         <v>45139</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20280,7 +20280,7 @@
         <v>45467</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20353,7 +20353,7 @@
         <v>44883</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         <v>46262</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20499,7 +20499,7 @@
         <v>44977</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20572,7 +20572,7 @@
         <v>45685</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20645,7 +20645,7 @@
         <v>45159</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20718,7 +20718,7 @@
         <v>45218</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20791,7 +20791,7 @@
         <v>46156</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20864,7 +20864,7 @@
         <v>45239</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20937,7 +20937,7 @@
         <v>46279</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21010,7 +21010,7 @@
         <v>46281</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21083,7 +21083,7 @@
         <v>46239</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21156,7 +21156,7 @@
         <v>44544</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>46195</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21302,7 +21302,7 @@
         <v>44592</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21375,7 +21375,7 @@
         <v>45894</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21448,7 +21448,7 @@
         <v>45168</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21521,7 +21521,7 @@
         <v>44811</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
         <v>46244</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21667,7 +21667,7 @@
         <v>44917</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21740,7 +21740,7 @@
         <v>45643</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21813,7 +21813,7 @@
         <v>45049</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -21886,7 +21886,7 @@
         <v>46288</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -21959,7 +21959,7 @@
         <v>45237</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22032,7 +22032,7 @@
         <v>46248</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22105,7 +22105,7 @@
         <v>44873</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22178,7 +22178,7 @@
         <v>46248</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22251,7 +22251,7 @@
         <v>46252</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22324,7 +22324,7 @@
         <v>46251</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22397,7 +22397,7 @@
         <v>45271</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22470,7 +22470,7 @@
         <v>46251</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22543,7 +22543,7 @@
         <v>45532</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22616,7 +22616,7 @@
         <v>46297</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22689,7 +22689,7 @@
         <v>45324</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22762,7 +22762,7 @@
         <v>45170</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -22835,7 +22835,7 @@
         <v>46297</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -22908,7 +22908,7 @@
         <v>46297</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -22981,7 +22981,7 @@
         <v>45141</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23054,7 +23054,7 @@
         <v>46296</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23132,7 +23132,7 @@
         <v>45670</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23205,7 +23205,7 @@
         <v>45252</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23278,7 +23278,7 @@
         <v>45700</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23351,7 +23351,7 @@
         <v>44879</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23424,7 +23424,7 @@
         <v>45474</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23497,7 +23497,7 @@
         <v>44974</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23570,7 +23570,7 @@
         <v>45427</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
         <v>44893</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23716,7 +23716,7 @@
         <v>45420</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23789,7 +23789,7 @@
         <v>44595</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -23862,7 +23862,7 @@
         <v>44546</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -23935,7 +23935,7 @@
         <v>44777</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>45574</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24081,7 +24081,7 @@
         <v>44749</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24154,7 +24154,7 @@
         <v>45415</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>44895</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24300,7 +24300,7 @@
         <v>45159</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24373,7 +24373,7 @@
         <v>45159</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24446,7 +24446,7 @@
         <v>45159</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24519,7 +24519,7 @@
         <v>45388</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24592,7 +24592,7 @@
         <v>44623</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24665,7 +24665,7 @@
         <v>45034</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24738,7 +24738,7 @@
         <v>45071</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -24811,7 +24811,7 @@
         <v>45776</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -24884,7 +24884,7 @@
         <v>45777</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -24957,7 +24957,7 @@
         <v>45777</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25030,7 +25030,7 @@
         <v>45033</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25103,7 +25103,7 @@
         <v>45338</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25176,7 +25176,7 @@
         <v>45491</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>

--- a/Översikt FÄRGELANDA.xlsx
+++ b/Översikt FÄRGELANDA.xlsx
@@ -601,7 +601,7 @@
         <v>44785</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45904</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>45303</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44935</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>46239</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>45242</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>45547</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>46175</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>45078</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>44504</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>44453</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>45474</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>45714</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>44911</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>45246</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>45766</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>45153</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>44837</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>44490</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>44595</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>44557</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>44490</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>44516</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>44525</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>44475</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>44526</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>44670</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>44658</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>44602</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>44496</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         <v>44566</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>44684</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>44593</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         <v>44858</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>44550</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>44711</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>44670</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>44518</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         <v>44572</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         <v>44686</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>44490</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>44750</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>44777</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v>44490</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4427,7 +4427,7 @@
         <v>44636</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>45273</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>45418</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>45419</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>45315</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         <v>45558</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>44581</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         <v>44928</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         <v>45079</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>44706</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>44706</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
         <v>45091</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         <v>44899</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5381,7 +5381,7 @@
         <v>45384</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>44600</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>45049</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         <v>45687</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
         <v>44998</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>45259</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         <v>46007</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>45244</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>44916</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         <v>45743</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>45740</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         <v>45890</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>45895</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>45894</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>45740</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6476,7 +6476,7 @@
         <v>45758</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>44846</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         <v>45714</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>45196</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         <v>45071</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
         <v>46037</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>45904</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6987,7 +6987,7 @@
         <v>45209</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         <v>45419</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7138,7 +7138,7 @@
         <v>44595</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>44488</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>45917</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         <v>45796</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         <v>45799</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         <v>45355</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>45799</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         <v>45212</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7722,7 +7722,7 @@
         <v>45800</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7795,7 +7795,7 @@
         <v>45805</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>45918</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>46055</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8014,7 +8014,7 @@
         <v>46052</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8087,7 +8087,7 @@
         <v>46058</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>45321</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         <v>46063</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>45351</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         <v>45351</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         <v>45932</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8530,7 +8530,7 @@
         <v>45811</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         <v>44578</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         <v>44896</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>46066</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>44974</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>46069</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8978,7 +8978,7 @@
         <v>44501</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9051,7 +9051,7 @@
         <v>45598</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9124,7 +9124,7 @@
         <v>46069</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>46071</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         <v>46071</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         <v>45937</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>46076</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         <v>45946</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9567,7 +9567,7 @@
         <v>45946</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9640,7 +9640,7 @@
         <v>46080</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>46080</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
         <v>45949</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9859,7 +9859,7 @@
         <v>44546</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9932,7 +9932,7 @@
         <v>45950</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>45950</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>45180</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10151,7 +10151,7 @@
         <v>45957</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
         <v>45260</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>45958</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10370,7 +10370,7 @@
         <v>46086</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>46087</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>45280</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10589,7 +10589,7 @@
         <v>45324</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>44939</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10735,7 +10735,7 @@
         <v>46091</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10808,7 +10808,7 @@
         <v>45965</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
         <v>44522</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10954,7 +10954,7 @@
         <v>45965</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11027,7 +11027,7 @@
         <v>45965</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11100,7 +11100,7 @@
         <v>45815</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11173,7 +11173,7 @@
         <v>45969</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>45969</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11319,7 +11319,7 @@
         <v>45015</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11392,7 +11392,7 @@
         <v>44571</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11465,7 +11465,7 @@
         <v>45247</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11538,7 +11538,7 @@
         <v>45049</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
         <v>45975</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11689,7 +11689,7 @@
         <v>45975</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11767,7 +11767,7 @@
         <v>46101</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11840,7 +11840,7 @@
         <v>45614</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>46107</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11986,7 +11986,7 @@
         <v>45036</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12059,7 +12059,7 @@
         <v>45987</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12132,7 +12132,7 @@
         <v>46113</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12205,7 +12205,7 @@
         <v>45989</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>46119</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         <v>44893</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>44935</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
         <v>46121</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12575,7 +12575,7 @@
         <v>46121</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12653,7 +12653,7 @@
         <v>45958</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12726,7 +12726,7 @@
         <v>46121</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12799,7 +12799,7 @@
         <v>46121</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12877,7 +12877,7 @@
         <v>46121</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12950,7 +12950,7 @@
         <v>46124</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13023,7 +13023,7 @@
         <v>45582</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13096,7 +13096,7 @@
         <v>46125</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13174,7 +13174,7 @@
         <v>45280</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13247,7 +13247,7 @@
         <v>45638</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13320,7 +13320,7 @@
         <v>45987</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13393,7 +13393,7 @@
         <v>45831</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13466,7 +13466,7 @@
         <v>44526</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13539,7 +13539,7 @@
         <v>45832</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13612,7 +13612,7 @@
         <v>45252</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13685,7 +13685,7 @@
         <v>45252</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13758,7 +13758,7 @@
         <v>46134</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
         <v>45524</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
         <v>45835</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>45894</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>45098</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>45835</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14196,7 +14196,7 @@
         <v>45835</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>45481</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14342,7 +14342,7 @@
         <v>46136</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14415,7 +14415,7 @@
         <v>45491</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14488,7 +14488,7 @@
         <v>45362</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14561,7 +14561,7 @@
         <v>45693</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14634,7 +14634,7 @@
         <v>45846</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14707,7 +14707,7 @@
         <v>45267</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14780,7 +14780,7 @@
         <v>45153</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14853,7 +14853,7 @@
         <v>45684</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>45693</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15004,7 +15004,7 @@
         <v>45777</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>45904</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15150,7 +15150,7 @@
         <v>45730</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15223,7 +15223,7 @@
         <v>45308</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15296,7 +15296,7 @@
         <v>45950</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15369,7 +15369,7 @@
         <v>45530</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>45761</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15515,7 +15515,7 @@
         <v>44917</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>44837</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15661,7 +15661,7 @@
         <v>45740</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15734,7 +15734,7 @@
         <v>44578</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15807,7 +15807,7 @@
         <v>45452</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15880,7 +15880,7 @@
         <v>45643</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15953,7 +15953,7 @@
         <v>45730</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16026,7 +16026,7 @@
         <v>44768</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16099,7 +16099,7 @@
         <v>45642</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16172,7 +16172,7 @@
         <v>45478</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16245,7 +16245,7 @@
         <v>46038</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16318,7 +16318,7 @@
         <v>45392</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16391,7 +16391,7 @@
         <v>45293</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>44638</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16537,7 +16537,7 @@
         <v>46150</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16610,7 +16610,7 @@
         <v>44901</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16683,7 +16683,7 @@
         <v>45071</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16756,7 +16756,7 @@
         <v>45936</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16834,7 +16834,7 @@
         <v>45875</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         <v>44488</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16980,7 +16980,7 @@
         <v>46166</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17053,7 +17053,7 @@
         <v>45687</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17126,7 +17126,7 @@
         <v>45040</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17199,7 +17199,7 @@
         <v>45420</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17272,7 +17272,7 @@
         <v>45757</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>45078</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17418,7 +17418,7 @@
         <v>44686</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17491,7 +17491,7 @@
         <v>45558</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
         <v>44958</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17637,7 +17637,7 @@
         <v>45558</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17710,7 +17710,7 @@
         <v>45643</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>45883</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17856,7 +17856,7 @@
         <v>45407</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17929,7 +17929,7 @@
         <v>45883</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>45034</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18075,7 +18075,7 @@
         <v>45757</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18148,7 +18148,7 @@
         <v>44977</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>46177</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>45145</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18367,7 +18367,7 @@
         <v>45712</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18440,7 +18440,7 @@
         <v>45705</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18513,7 +18513,7 @@
         <v>46188</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18586,7 +18586,7 @@
         <v>45775</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18659,7 +18659,7 @@
         <v>46190</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18732,7 +18732,7 @@
         <v>45764</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
         <v>46195</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18878,7 +18878,7 @@
         <v>44841</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18951,7 +18951,7 @@
         <v>44899</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19024,7 +19024,7 @@
         <v>45215</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19097,7 +19097,7 @@
         <v>45470</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19170,7 +19170,7 @@
         <v>44869</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19243,7 +19243,7 @@
         <v>45643</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19316,7 +19316,7 @@
         <v>46202</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19394,7 +19394,7 @@
         <v>46204</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19467,7 +19467,7 @@
         <v>45532</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19540,7 +19540,7 @@
         <v>46209</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>45202</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19691,7 +19691,7 @@
         <v>46205</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19769,7 +19769,7 @@
         <v>45062</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>46139</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19915,7 +19915,7 @@
         <v>44893</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -19988,7 +19988,7 @@
         <v>46259</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20061,7 +20061,7 @@
         <v>46258</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20134,7 +20134,7 @@
         <v>45736</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20207,7 +20207,7 @@
         <v>45139</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20280,7 +20280,7 @@
         <v>45467</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20353,7 +20353,7 @@
         <v>44883</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         <v>46262</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20499,7 +20499,7 @@
         <v>44977</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20572,7 +20572,7 @@
         <v>45685</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20645,7 +20645,7 @@
         <v>45159</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20718,7 +20718,7 @@
         <v>45218</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20791,7 +20791,7 @@
         <v>46156</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20864,7 +20864,7 @@
         <v>45239</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20937,7 +20937,7 @@
         <v>46279</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21010,7 +21010,7 @@
         <v>46281</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21083,7 +21083,7 @@
         <v>46239</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21156,7 +21156,7 @@
         <v>44544</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>46195</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21302,7 +21302,7 @@
         <v>44592</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21375,7 +21375,7 @@
         <v>45894</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21448,7 +21448,7 @@
         <v>45168</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21521,7 +21521,7 @@
         <v>44811</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
         <v>46244</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21667,7 +21667,7 @@
         <v>44917</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21740,7 +21740,7 @@
         <v>45643</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21813,7 +21813,7 @@
         <v>45049</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -21886,7 +21886,7 @@
         <v>46288</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -21959,7 +21959,7 @@
         <v>45237</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22032,7 +22032,7 @@
         <v>46248</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22105,7 +22105,7 @@
         <v>44873</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22178,7 +22178,7 @@
         <v>46248</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22251,7 +22251,7 @@
         <v>46252</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22324,7 +22324,7 @@
         <v>46251</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22397,7 +22397,7 @@
         <v>45271</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22470,7 +22470,7 @@
         <v>46251</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22543,7 +22543,7 @@
         <v>45532</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22616,7 +22616,7 @@
         <v>46297</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22689,7 +22689,7 @@
         <v>45324</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22762,7 +22762,7 @@
         <v>45170</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -22835,7 +22835,7 @@
         <v>46297</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -22908,7 +22908,7 @@
         <v>46297</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -22981,7 +22981,7 @@
         <v>45141</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23054,7 +23054,7 @@
         <v>46296</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23132,7 +23132,7 @@
         <v>45670</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23205,7 +23205,7 @@
         <v>45252</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23278,7 +23278,7 @@
         <v>45700</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23351,7 +23351,7 @@
         <v>44879</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23424,7 +23424,7 @@
         <v>45474</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23497,7 +23497,7 @@
         <v>44974</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23570,7 +23570,7 @@
         <v>45427</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
         <v>44893</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23716,7 +23716,7 @@
         <v>45420</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23789,7 +23789,7 @@
         <v>44595</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -23862,7 +23862,7 @@
         <v>44546</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -23935,7 +23935,7 @@
         <v>44777</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>45574</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24081,7 +24081,7 @@
         <v>44749</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24154,7 +24154,7 @@
         <v>45415</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>44895</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24300,7 +24300,7 @@
         <v>45159</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24373,7 +24373,7 @@
         <v>45159</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24446,7 +24446,7 @@
         <v>45159</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24519,7 +24519,7 @@
         <v>45388</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24592,7 +24592,7 @@
         <v>44623</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24665,7 +24665,7 @@
         <v>45034</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24738,7 +24738,7 @@
         <v>45071</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -24811,7 +24811,7 @@
         <v>45776</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -24884,7 +24884,7 @@
         <v>45777</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -24957,7 +24957,7 @@
         <v>45777</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25030,7 +25030,7 @@
         <v>45033</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25103,7 +25103,7 @@
         <v>45338</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25176,7 +25176,7 @@
         <v>45491</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>

--- a/Översikt FÄRGELANDA.xlsx
+++ b/Översikt FÄRGELANDA.xlsx
@@ -601,7 +601,7 @@
         <v>44785</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45904</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>45303</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>45242</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>44935</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>46239</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>44504</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>45547</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>45078</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>46175</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>44453</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>45474</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>45766</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>45714</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>44911</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>45153</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>45246</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>46303</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>44837</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>44490</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>44595</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>44557</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>44490</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>44516</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>44525</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>44526</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>44670</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>44658</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>44602</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>44496</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>44684</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>44566</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>44593</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>44858</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>44686</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>44711</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>44670</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>44490</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>44750</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>44518</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>44777</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         <v>44490</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>44636</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>44550</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>44572</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>44895</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>44883</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>45736</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>45139</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         <v>45418</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         <v>44958</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>45530</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>45244</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         <v>45384</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>45761</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         <v>45252</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>45252</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         <v>45247</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>45415</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>44873</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>45419</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>45239</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>45764</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>45015</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>45740</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>45758</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>44837</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>44811</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>45700</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>45237</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>44488</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>45049</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>45883</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>45524</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>44546</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         <v>45474</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>45883</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6873,7 +6873,7 @@
         <v>45705</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>45574</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>44777</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>44571</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>44578</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7238,7 +7238,7 @@
         <v>45141</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         <v>45062</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7384,7 +7384,7 @@
         <v>45670</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>45159</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
         <v>45280</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         <v>45757</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         <v>44526</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>45890</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>45321</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>45643</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>45894</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
         <v>45895</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>45078</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>45407</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8260,7 +8260,7 @@
         <v>45687</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>45280</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
         <v>45273</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         <v>45420</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8552,7 +8552,7 @@
         <v>45730</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>45904</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8698,7 +8698,7 @@
         <v>45740</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>44901</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         <v>45452</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8917,7 +8917,7 @@
         <v>44893</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>44899</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9063,7 +9063,7 @@
         <v>44899</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9136,7 +9136,7 @@
         <v>45362</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>45776</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9282,7 +9282,7 @@
         <v>44488</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>44974</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>45777</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9501,7 +9501,7 @@
         <v>45777</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>45491</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9647,7 +9647,7 @@
         <v>45040</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>45470</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9793,7 +9793,7 @@
         <v>45582</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9866,7 +9866,7 @@
         <v>45388</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9939,7 +9939,7 @@
         <v>45033</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
         <v>45917</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10085,7 +10085,7 @@
         <v>44544</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10158,7 +10158,7 @@
         <v>44893</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>45918</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10304,7 +10304,7 @@
         <v>45467</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         <v>45034</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10450,7 +10450,7 @@
         <v>45338</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10523,7 +10523,7 @@
         <v>44939</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10596,7 +10596,7 @@
         <v>44581</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>45259</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10742,7 +10742,7 @@
         <v>45351</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10815,7 +10815,7 @@
         <v>45351</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
         <v>45643</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10961,7 +10961,7 @@
         <v>45714</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>45743</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11107,7 +11107,7 @@
         <v>44595</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11180,7 +11180,7 @@
         <v>45740</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>44977</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>44600</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>44592</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>45796</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11545,7 +11545,7 @@
         <v>45419</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
         <v>44917</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>45355</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11769,7 +11769,7 @@
         <v>45153</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11842,7 +11842,7 @@
         <v>44896</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11915,7 +11915,7 @@
         <v>45799</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11988,7 +11988,7 @@
         <v>45170</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>45315</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12134,7 +12134,7 @@
         <v>45071</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12207,7 +12207,7 @@
         <v>45800</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12280,7 +12280,7 @@
         <v>45799</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12353,7 +12353,7 @@
         <v>45932</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         <v>45937</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12499,7 +12499,7 @@
         <v>45091</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>45805</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12645,7 +12645,7 @@
         <v>45598</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12718,7 +12718,7 @@
         <v>45049</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>44638</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12864,7 +12864,7 @@
         <v>45180</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12937,7 +12937,7 @@
         <v>45558</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13010,7 +13010,7 @@
         <v>45324</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13083,7 +13083,7 @@
         <v>45946</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13156,7 +13156,7 @@
         <v>45811</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         <v>45684</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13307,7 +13307,7 @@
         <v>45946</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13380,7 +13380,7 @@
         <v>45271</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13453,7 +13453,7 @@
         <v>45815</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>45950</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13599,7 +13599,7 @@
         <v>45950</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13672,7 +13672,7 @@
         <v>45949</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13745,7 +13745,7 @@
         <v>45079</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13818,7 +13818,7 @@
         <v>45209</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13891,7 +13891,7 @@
         <v>45643</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13964,7 +13964,7 @@
         <v>45832</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14037,7 +14037,7 @@
         <v>45831</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14110,7 +14110,7 @@
         <v>45957</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14183,7 +14183,7 @@
         <v>45958</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14256,7 +14256,7 @@
         <v>45643</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14329,7 +14329,7 @@
         <v>44998</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14402,7 +14402,7 @@
         <v>45638</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>45835</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14548,7 +14548,7 @@
         <v>45835</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         <v>45145</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14694,7 +14694,7 @@
         <v>44686</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14767,7 +14767,7 @@
         <v>45835</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14840,7 +14840,7 @@
         <v>45965</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14913,7 +14913,7 @@
         <v>45218</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14986,7 +14986,7 @@
         <v>45965</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15059,7 +15059,7 @@
         <v>45965</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15132,7 +15132,7 @@
         <v>44749</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15205,7 +15205,7 @@
         <v>44977</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15278,7 +15278,7 @@
         <v>45420</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15351,7 +15351,7 @@
         <v>44841</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>45846</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15497,7 +15497,7 @@
         <v>45969</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>45969</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15643,7 +15643,7 @@
         <v>45159</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15716,7 +15716,7 @@
         <v>45159</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15789,7 +15789,7 @@
         <v>45159</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15862,7 +15862,7 @@
         <v>45252</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15935,7 +15935,7 @@
         <v>45215</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         <v>45532</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16081,7 +16081,7 @@
         <v>44768</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16154,7 +16154,7 @@
         <v>45975</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>45975</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16310,7 +16310,7 @@
         <v>44706</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16383,7 +16383,7 @@
         <v>45098</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16456,7 +16456,7 @@
         <v>45196</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16529,7 +16529,7 @@
         <v>44869</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16602,7 +16602,7 @@
         <v>45687</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16675,7 +16675,7 @@
         <v>44522</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>45775</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16821,7 +16821,7 @@
         <v>45875</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16894,7 +16894,7 @@
         <v>45757</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16967,7 +16967,7 @@
         <v>44893</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17040,7 +17040,7 @@
         <v>44623</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17113,7 +17113,7 @@
         <v>45071</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17186,7 +17186,7 @@
         <v>45293</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17259,7 +17259,7 @@
         <v>46101</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17332,7 +17332,7 @@
         <v>44916</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17405,7 +17405,7 @@
         <v>45202</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17478,7 +17478,7 @@
         <v>45532</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>44879</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17624,7 +17624,7 @@
         <v>45987</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17697,7 +17697,7 @@
         <v>45260</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17770,7 +17770,7 @@
         <v>46107</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17843,7 +17843,7 @@
         <v>44546</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17916,7 +17916,7 @@
         <v>45989</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17989,7 +17989,7 @@
         <v>45212</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18062,7 +18062,7 @@
         <v>45958</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18135,7 +18135,7 @@
         <v>46113</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18208,7 +18208,7 @@
         <v>45267</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18281,7 +18281,7 @@
         <v>45685</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18354,7 +18354,7 @@
         <v>46119</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18427,7 +18427,7 @@
         <v>46121</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18505,7 +18505,7 @@
         <v>46121</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18583,7 +18583,7 @@
         <v>46121</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18656,7 +18656,7 @@
         <v>46121</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18734,7 +18734,7 @@
         <v>46121</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
         <v>46125</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18885,7 +18885,7 @@
         <v>46124</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18958,7 +18958,7 @@
         <v>44501</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19031,7 +19031,7 @@
         <v>45987</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19104,7 +19104,7 @@
         <v>46134</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19177,7 +19177,7 @@
         <v>45034</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19250,7 +19250,7 @@
         <v>45481</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         <v>45071</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19396,7 +19396,7 @@
         <v>46007</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19469,7 +19469,7 @@
         <v>44595</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>45308</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19615,7 +19615,7 @@
         <v>46136</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19688,7 +19688,7 @@
         <v>45904</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19761,7 +19761,7 @@
         <v>45730</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>44706</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         <v>44917</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -19980,7 +19980,7 @@
         <v>45777</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20053,7 +20053,7 @@
         <v>45693</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20126,7 +20126,7 @@
         <v>45427</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>45614</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20272,7 +20272,7 @@
         <v>44935</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20345,7 +20345,7 @@
         <v>44928</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20418,7 +20418,7 @@
         <v>45478</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20491,7 +20491,7 @@
         <v>45712</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20564,7 +20564,7 @@
         <v>45392</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20637,7 +20637,7 @@
         <v>45894</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>46037</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20783,7 +20783,7 @@
         <v>45049</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20856,7 +20856,7 @@
         <v>46038</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>45168</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21002,7 +21002,7 @@
         <v>44846</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21075,7 +21075,7 @@
         <v>45693</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21148,7 +21148,7 @@
         <v>45950</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21221,7 +21221,7 @@
         <v>45036</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21294,7 +21294,7 @@
         <v>44578</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21367,7 +21367,7 @@
         <v>45324</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21440,7 +21440,7 @@
         <v>44974</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21513,7 +21513,7 @@
         <v>46052</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21586,7 +21586,7 @@
         <v>46055</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21659,7 +21659,7 @@
         <v>46058</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21737,7 +21737,7 @@
         <v>45642</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21810,7 +21810,7 @@
         <v>46063</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -21883,7 +21883,7 @@
         <v>46066</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -21961,7 +21961,7 @@
         <v>46069</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22034,7 +22034,7 @@
         <v>46150</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22107,7 +22107,7 @@
         <v>46069</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22185,7 +22185,7 @@
         <v>46071</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22258,7 +22258,7 @@
         <v>46071</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22331,7 +22331,7 @@
         <v>46076</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22409,7 +22409,7 @@
         <v>46080</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22482,7 +22482,7 @@
         <v>46080</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22555,7 +22555,7 @@
         <v>46086</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22628,7 +22628,7 @@
         <v>46087</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22701,7 +22701,7 @@
         <v>46091</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22774,7 +22774,7 @@
         <v>45936</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -22852,7 +22852,7 @@
         <v>46166</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -22925,7 +22925,7 @@
         <v>45558</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -22998,7 +22998,7 @@
         <v>45558</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23071,7 +23071,7 @@
         <v>46177</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23144,7 +23144,7 @@
         <v>46188</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23217,7 +23217,7 @@
         <v>46190</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23290,7 +23290,7 @@
         <v>46195</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23363,7 +23363,7 @@
         <v>46202</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23441,7 +23441,7 @@
         <v>46204</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23514,7 +23514,7 @@
         <v>46205</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23592,7 +23592,7 @@
         <v>46209</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23670,7 +23670,7 @@
         <v>46139</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23743,7 +23743,7 @@
         <v>46156</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23816,7 +23816,7 @@
         <v>46279</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>46281</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -23962,7 +23962,7 @@
         <v>46244</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24035,7 +24035,7 @@
         <v>46195</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24108,7 +24108,7 @@
         <v>45894</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24181,7 +24181,7 @@
         <v>46288</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24254,7 +24254,7 @@
         <v>46248</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24327,7 +24327,7 @@
         <v>46248</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24400,7 +24400,7 @@
         <v>46296</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24478,7 +24478,7 @@
         <v>46251</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24551,7 +24551,7 @@
         <v>46252</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24624,7 +24624,7 @@
         <v>46251</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24697,7 +24697,7 @@
         <v>46297</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24770,7 +24770,7 @@
         <v>46297</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -24843,7 +24843,7 @@
         <v>46297</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -24916,7 +24916,7 @@
         <v>46300</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -24989,7 +24989,7 @@
         <v>46300</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25062,7 +25062,7 @@
         <v>46239</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25135,7 +25135,7 @@
         <v>46259</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25208,7 +25208,7 @@
         <v>46258</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25281,7 +25281,7 @@
         <v>46262</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>45491</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>

--- a/Översikt FÄRGELANDA.xlsx
+++ b/Översikt FÄRGELANDA.xlsx
@@ -601,7 +601,7 @@
         <v>44785</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45904</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>45303</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>45242</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>44935</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>46239</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>44504</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>45547</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>45078</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>46175</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>44453</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>45474</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>45766</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>45714</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>44911</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>45153</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>45246</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>46303</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>44837</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>44490</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>44595</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>44557</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>44490</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>44516</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>44525</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>44526</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>44670</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>44658</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>44602</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>44496</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>44684</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>44566</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>44593</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>44858</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>44686</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>44711</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>44670</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>44490</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>44750</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>44518</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>44777</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         <v>44490</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>44636</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>44550</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>44572</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>44895</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>44883</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>45736</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>45139</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         <v>45418</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         <v>44958</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>45530</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>45244</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         <v>45384</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>45761</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         <v>45252</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>45252</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         <v>45247</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>45415</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>44873</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>45419</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>45239</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>45764</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>45015</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>45740</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>45758</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>44837</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>44811</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>45700</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>45237</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>44488</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>45049</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>45883</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>45524</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>44546</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         <v>45474</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>45883</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6873,7 +6873,7 @@
         <v>45705</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>45574</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>44777</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>44571</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>44578</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7238,7 +7238,7 @@
         <v>45141</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         <v>45062</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7384,7 +7384,7 @@
         <v>45670</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>45159</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
         <v>45280</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         <v>45757</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         <v>44526</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>45890</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>45321</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>45643</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>45894</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
         <v>45895</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>45078</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>45407</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8260,7 +8260,7 @@
         <v>45687</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>45280</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
         <v>45273</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         <v>45420</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8552,7 +8552,7 @@
         <v>45730</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>45904</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8698,7 +8698,7 @@
         <v>45740</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>44901</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         <v>45452</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8917,7 +8917,7 @@
         <v>44893</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>44899</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9063,7 +9063,7 @@
         <v>44899</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9136,7 +9136,7 @@
         <v>45362</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>45776</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9282,7 +9282,7 @@
         <v>44488</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>44974</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>45777</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9501,7 +9501,7 @@
         <v>45777</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>45491</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9647,7 +9647,7 @@
         <v>45040</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>45470</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9793,7 +9793,7 @@
         <v>45582</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9866,7 +9866,7 @@
         <v>45388</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9939,7 +9939,7 @@
         <v>45033</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
         <v>45917</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10085,7 +10085,7 @@
         <v>44544</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10158,7 +10158,7 @@
         <v>44893</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>45918</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10304,7 +10304,7 @@
         <v>45467</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         <v>45034</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10450,7 +10450,7 @@
         <v>45338</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10523,7 +10523,7 @@
         <v>44939</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10596,7 +10596,7 @@
         <v>44581</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>45259</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10742,7 +10742,7 @@
         <v>45351</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10815,7 +10815,7 @@
         <v>45351</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
         <v>45643</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10961,7 +10961,7 @@
         <v>45714</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>45743</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11107,7 +11107,7 @@
         <v>44595</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11180,7 +11180,7 @@
         <v>45740</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>44977</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>44600</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>44592</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>45796</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11545,7 +11545,7 @@
         <v>45419</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
         <v>44917</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>45355</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11769,7 +11769,7 @@
         <v>45153</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11842,7 +11842,7 @@
         <v>44896</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11915,7 +11915,7 @@
         <v>45799</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11988,7 +11988,7 @@
         <v>45170</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>45315</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12134,7 +12134,7 @@
         <v>45071</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12207,7 +12207,7 @@
         <v>45800</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12280,7 +12280,7 @@
         <v>45799</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12353,7 +12353,7 @@
         <v>45932</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         <v>45937</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12499,7 +12499,7 @@
         <v>45091</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>45805</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12645,7 +12645,7 @@
         <v>45598</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12718,7 +12718,7 @@
         <v>45049</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>44638</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12864,7 +12864,7 @@
         <v>45180</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12937,7 +12937,7 @@
         <v>45558</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13010,7 +13010,7 @@
         <v>45324</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13083,7 +13083,7 @@
         <v>45946</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13156,7 +13156,7 @@
         <v>45811</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         <v>45684</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13307,7 +13307,7 @@
         <v>45946</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13380,7 +13380,7 @@
         <v>45271</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13453,7 +13453,7 @@
         <v>45815</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>45950</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13599,7 +13599,7 @@
         <v>45950</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13672,7 +13672,7 @@
         <v>45949</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13745,7 +13745,7 @@
         <v>45079</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13818,7 +13818,7 @@
         <v>45209</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13891,7 +13891,7 @@
         <v>45643</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13964,7 +13964,7 @@
         <v>45832</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14037,7 +14037,7 @@
         <v>45831</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14110,7 +14110,7 @@
         <v>45957</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14183,7 +14183,7 @@
         <v>45958</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14256,7 +14256,7 @@
         <v>45643</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14329,7 +14329,7 @@
         <v>44998</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14402,7 +14402,7 @@
         <v>45638</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>45835</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14548,7 +14548,7 @@
         <v>45835</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         <v>45145</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14694,7 +14694,7 @@
         <v>44686</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14767,7 +14767,7 @@
         <v>45835</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14840,7 +14840,7 @@
         <v>45965</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14913,7 +14913,7 @@
         <v>45218</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14986,7 +14986,7 @@
         <v>45965</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15059,7 +15059,7 @@
         <v>45965</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15132,7 +15132,7 @@
         <v>44749</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15205,7 +15205,7 @@
         <v>44977</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15278,7 +15278,7 @@
         <v>45420</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15351,7 +15351,7 @@
         <v>44841</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>45846</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15497,7 +15497,7 @@
         <v>45969</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>45969</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15643,7 +15643,7 @@
         <v>45159</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15716,7 +15716,7 @@
         <v>45159</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15789,7 +15789,7 @@
         <v>45159</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15862,7 +15862,7 @@
         <v>45252</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15935,7 +15935,7 @@
         <v>45215</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         <v>45532</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16081,7 +16081,7 @@
         <v>44768</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16154,7 +16154,7 @@
         <v>45975</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>45975</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16310,7 +16310,7 @@
         <v>44706</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16383,7 +16383,7 @@
         <v>45098</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16456,7 +16456,7 @@
         <v>45196</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16529,7 +16529,7 @@
         <v>44869</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16602,7 +16602,7 @@
         <v>45687</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16675,7 +16675,7 @@
         <v>44522</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>45775</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16821,7 +16821,7 @@
         <v>45875</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16894,7 +16894,7 @@
         <v>45757</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16967,7 +16967,7 @@
         <v>44893</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17040,7 +17040,7 @@
         <v>44623</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17113,7 +17113,7 @@
         <v>45071</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17186,7 +17186,7 @@
         <v>45293</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17259,7 +17259,7 @@
         <v>46101</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17332,7 +17332,7 @@
         <v>44916</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17405,7 +17405,7 @@
         <v>45202</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17478,7 +17478,7 @@
         <v>45532</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>44879</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17624,7 +17624,7 @@
         <v>45987</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17697,7 +17697,7 @@
         <v>45260</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17770,7 +17770,7 @@
         <v>46107</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17843,7 +17843,7 @@
         <v>44546</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17916,7 +17916,7 @@
         <v>45989</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17989,7 +17989,7 @@
         <v>45212</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18062,7 +18062,7 @@
         <v>45958</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18135,7 +18135,7 @@
         <v>46113</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18208,7 +18208,7 @@
         <v>45267</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18281,7 +18281,7 @@
         <v>45685</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18354,7 +18354,7 @@
         <v>46119</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18427,7 +18427,7 @@
         <v>46121</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18505,7 +18505,7 @@
         <v>46121</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18583,7 +18583,7 @@
         <v>46121</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18656,7 +18656,7 @@
         <v>46121</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18734,7 +18734,7 @@
         <v>46121</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
         <v>46125</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18885,7 +18885,7 @@
         <v>46124</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18958,7 +18958,7 @@
         <v>44501</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19031,7 +19031,7 @@
         <v>45987</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19104,7 +19104,7 @@
         <v>46134</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19177,7 +19177,7 @@
         <v>45034</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19250,7 +19250,7 @@
         <v>45481</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         <v>45071</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19396,7 +19396,7 @@
         <v>46007</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19469,7 +19469,7 @@
         <v>44595</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>45308</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19615,7 +19615,7 @@
         <v>46136</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19688,7 +19688,7 @@
         <v>45904</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19761,7 +19761,7 @@
         <v>45730</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>44706</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         <v>44917</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -19980,7 +19980,7 @@
         <v>45777</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20053,7 +20053,7 @@
         <v>45693</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20126,7 +20126,7 @@
         <v>45427</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>45614</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20272,7 +20272,7 @@
         <v>44935</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20345,7 +20345,7 @@
         <v>44928</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20418,7 +20418,7 @@
         <v>45478</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20491,7 +20491,7 @@
         <v>45712</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20564,7 +20564,7 @@
         <v>45392</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20637,7 +20637,7 @@
         <v>45894</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>46037</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20783,7 +20783,7 @@
         <v>45049</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20856,7 +20856,7 @@
         <v>46038</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>45168</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21002,7 +21002,7 @@
         <v>44846</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21075,7 +21075,7 @@
         <v>45693</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21148,7 +21148,7 @@
         <v>45950</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21221,7 +21221,7 @@
         <v>45036</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21294,7 +21294,7 @@
         <v>44578</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21367,7 +21367,7 @@
         <v>45324</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21440,7 +21440,7 @@
         <v>44974</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21513,7 +21513,7 @@
         <v>46052</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21586,7 +21586,7 @@
         <v>46055</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21659,7 +21659,7 @@
         <v>46058</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21737,7 +21737,7 @@
         <v>45642</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21810,7 +21810,7 @@
         <v>46063</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -21883,7 +21883,7 @@
         <v>46066</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -21961,7 +21961,7 @@
         <v>46069</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22034,7 +22034,7 @@
         <v>46150</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22107,7 +22107,7 @@
         <v>46069</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22185,7 +22185,7 @@
         <v>46071</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22258,7 +22258,7 @@
         <v>46071</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22331,7 +22331,7 @@
         <v>46076</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22409,7 +22409,7 @@
         <v>46080</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22482,7 +22482,7 @@
         <v>46080</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22555,7 +22555,7 @@
         <v>46086</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22628,7 +22628,7 @@
         <v>46087</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22701,7 +22701,7 @@
         <v>46091</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22774,7 +22774,7 @@
         <v>45936</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -22852,7 +22852,7 @@
         <v>46166</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -22925,7 +22925,7 @@
         <v>45558</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -22998,7 +22998,7 @@
         <v>45558</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23071,7 +23071,7 @@
         <v>46177</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23144,7 +23144,7 @@
         <v>46188</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23217,7 +23217,7 @@
         <v>46190</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23290,7 +23290,7 @@
         <v>46195</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23363,7 +23363,7 @@
         <v>46202</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23441,7 +23441,7 @@
         <v>46204</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23514,7 +23514,7 @@
         <v>46205</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23592,7 +23592,7 @@
         <v>46209</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23670,7 +23670,7 @@
         <v>46139</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23743,7 +23743,7 @@
         <v>46156</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23816,7 +23816,7 @@
         <v>46279</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>46281</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -23962,7 +23962,7 @@
         <v>46244</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24035,7 +24035,7 @@
         <v>46195</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24108,7 +24108,7 @@
         <v>45894</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24181,7 +24181,7 @@
         <v>46288</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24254,7 +24254,7 @@
         <v>46248</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24327,7 +24327,7 @@
         <v>46248</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24400,7 +24400,7 @@
         <v>46296</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24478,7 +24478,7 @@
         <v>46251</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24551,7 +24551,7 @@
         <v>46252</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24624,7 +24624,7 @@
         <v>46251</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24697,7 +24697,7 @@
         <v>46297</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24770,7 +24770,7 @@
         <v>46297</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -24843,7 +24843,7 @@
         <v>46297</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -24916,7 +24916,7 @@
         <v>46300</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -24989,7 +24989,7 @@
         <v>46300</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25062,7 +25062,7 @@
         <v>46239</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25135,7 +25135,7 @@
         <v>46259</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25208,7 +25208,7 @@
         <v>46258</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25281,7 +25281,7 @@
         <v>46262</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>45491</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>

--- a/Översikt FÄRGELANDA.xlsx
+++ b/Översikt FÄRGELANDA.xlsx
@@ -601,7 +601,7 @@
         <v>44785</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45904</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>45303</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44935</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>46239</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>45242</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>45547</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>46175</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>45078</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>44504</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>44453</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>45474</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>45714</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>44911</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>45246</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>45766</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>45153</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>46303</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>44837</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>44490</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>44595</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>44557</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>44490</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>44516</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>44525</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>44526</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>44670</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>44658</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>44602</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>44496</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>44566</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>44684</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>44593</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>44858</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>44550</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>44711</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>44670</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>44518</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>44572</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>44686</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>44490</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         <v>44750</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>44777</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>44490</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>44636</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>45273</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>45315</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>45418</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>45419</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>45558</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         <v>44928</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>45079</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>44581</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         <v>44706</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>44706</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         <v>45091</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>44899</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         <v>45049</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>45384</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>45687</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>44600</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>44998</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>45244</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>44916</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>45740</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>44846</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>45758</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>45196</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>45071</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>45209</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>44488</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>44595</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>45212</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>45321</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>44974</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         <v>44501</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>44578</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6873,7 +6873,7 @@
         <v>44546</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>45180</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>45260</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>45280</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>44939</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7238,7 +7238,7 @@
         <v>44522</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         <v>45351</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7384,7 +7384,7 @@
         <v>45351</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>45015</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
         <v>45049</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         <v>44571</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         <v>45614</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>45036</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>44893</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>44935</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>45693</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
         <v>45582</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>45777</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>45904</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8260,7 +8260,7 @@
         <v>45280</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>45757</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
         <v>45730</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         <v>45638</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8552,7 +8552,7 @@
         <v>45890</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>45950</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8698,7 +8698,7 @@
         <v>45895</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>45894</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         <v>44526</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8917,7 +8917,7 @@
         <v>45252</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>45252</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9063,7 +9063,7 @@
         <v>44578</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9136,7 +9136,7 @@
         <v>45524</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>45642</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9282,7 +9282,7 @@
         <v>45478</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>45904</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>45098</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9501,7 +9501,7 @@
         <v>46038</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>45491</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9647,7 +9647,7 @@
         <v>45362</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>45917</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9793,7 +9793,7 @@
         <v>45918</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9866,7 +9866,7 @@
         <v>45267</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9939,7 +9939,7 @@
         <v>45153</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
         <v>45684</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>45932</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10163,7 +10163,7 @@
         <v>46150</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10236,7 +10236,7 @@
         <v>44896</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10309,7 +10309,7 @@
         <v>45308</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10382,7 +10382,7 @@
         <v>45937</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>45530</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>45761</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
         <v>44917</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10674,7 +10674,7 @@
         <v>44837</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10747,7 +10747,7 @@
         <v>45740</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10820,7 +10820,7 @@
         <v>45452</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10893,7 +10893,7 @@
         <v>45946</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10966,7 +10966,7 @@
         <v>45946</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11039,7 +11039,7 @@
         <v>45949</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11112,7 +11112,7 @@
         <v>45950</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11185,7 +11185,7 @@
         <v>45950</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11258,7 +11258,7 @@
         <v>45643</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11331,7 +11331,7 @@
         <v>45730</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11404,7 +11404,7 @@
         <v>44768</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11477,7 +11477,7 @@
         <v>45957</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11550,7 +11550,7 @@
         <v>45958</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
         <v>45965</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>45965</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11769,7 +11769,7 @@
         <v>45965</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11842,7 +11842,7 @@
         <v>45936</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         <v>45969</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>45969</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12066,7 +12066,7 @@
         <v>45392</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>45293</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
         <v>44638</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12285,7 +12285,7 @@
         <v>45975</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12363,7 +12363,7 @@
         <v>45975</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12441,7 +12441,7 @@
         <v>46166</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12514,7 +12514,7 @@
         <v>44901</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
         <v>45987</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         <v>45989</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>45071</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12806,7 +12806,7 @@
         <v>45558</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12879,7 +12879,7 @@
         <v>45958</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12952,7 +12952,7 @@
         <v>44488</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13025,7 +13025,7 @@
         <v>45558</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13098,7 +13098,7 @@
         <v>45687</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13171,7 +13171,7 @@
         <v>45987</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
         <v>45040</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13317,7 +13317,7 @@
         <v>45420</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
         <v>45078</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>44686</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13536,7 +13536,7 @@
         <v>44958</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13609,7 +13609,7 @@
         <v>46007</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>45643</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13755,7 +13755,7 @@
         <v>45407</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
         <v>45034</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13901,7 +13901,7 @@
         <v>44977</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>45145</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
         <v>45712</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14120,7 +14120,7 @@
         <v>45705</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14193,7 +14193,7 @@
         <v>46037</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14266,7 +14266,7 @@
         <v>46177</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14339,7 +14339,7 @@
         <v>45775</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14412,7 +14412,7 @@
         <v>45764</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14485,7 +14485,7 @@
         <v>46055</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         <v>46052</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14631,7 +14631,7 @@
         <v>46058</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14709,7 +14709,7 @@
         <v>44841</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>44899</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>46063</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14928,7 +14928,7 @@
         <v>45215</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15001,7 +15001,7 @@
         <v>46066</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>45470</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15152,7 +15152,7 @@
         <v>46069</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15230,7 +15230,7 @@
         <v>44869</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15303,7 +15303,7 @@
         <v>46188</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15376,7 +15376,7 @@
         <v>45643</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15449,7 +15449,7 @@
         <v>46069</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15522,7 +15522,7 @@
         <v>46071</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>46071</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15668,7 +15668,7 @@
         <v>45532</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15741,7 +15741,7 @@
         <v>46076</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15819,7 +15819,7 @@
         <v>46080</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15892,7 +15892,7 @@
         <v>46080</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15965,7 +15965,7 @@
         <v>45202</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         <v>46086</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16111,7 +16111,7 @@
         <v>46087</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16184,7 +16184,7 @@
         <v>46190</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16257,7 +16257,7 @@
         <v>46091</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16330,7 +16330,7 @@
         <v>45062</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16403,7 +16403,7 @@
         <v>44893</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16476,7 +16476,7 @@
         <v>46195</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16549,7 +16549,7 @@
         <v>45736</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16622,7 +16622,7 @@
         <v>45139</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16695,7 +16695,7 @@
         <v>46101</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16768,7 +16768,7 @@
         <v>45467</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
         <v>44883</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16914,7 +16914,7 @@
         <v>46107</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16987,7 +16987,7 @@
         <v>46113</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
         <v>44977</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
         <v>46119</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>45685</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17279,7 +17279,7 @@
         <v>46121</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17357,7 +17357,7 @@
         <v>45159</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17430,7 +17430,7 @@
         <v>46121</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17508,7 +17508,7 @@
         <v>46121</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17581,7 +17581,7 @@
         <v>46121</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17659,7 +17659,7 @@
         <v>46121</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>46124</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
         <v>46202</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17883,7 +17883,7 @@
         <v>46125</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17961,7 +17961,7 @@
         <v>46204</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18034,7 +18034,7 @@
         <v>46134</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18107,7 +18107,7 @@
         <v>45218</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>45239</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18253,7 +18253,7 @@
         <v>45894</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18326,7 +18326,7 @@
         <v>45481</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18399,7 +18399,7 @@
         <v>46136</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18472,7 +18472,7 @@
         <v>45693</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18545,7 +18545,7 @@
         <v>46209</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18623,7 +18623,7 @@
         <v>46205</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18701,7 +18701,7 @@
         <v>44544</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18774,7 +18774,7 @@
         <v>44592</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18847,7 +18847,7 @@
         <v>46139</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18920,7 +18920,7 @@
         <v>45168</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18993,7 +18993,7 @@
         <v>44811</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>44917</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>45643</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19212,7 +19212,7 @@
         <v>45049</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19285,7 +19285,7 @@
         <v>45237</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>46156</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19431,7 +19431,7 @@
         <v>44873</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>46279</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19577,7 +19577,7 @@
         <v>45271</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         <v>45532</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19723,7 +19723,7 @@
         <v>45324</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19796,7 +19796,7 @@
         <v>45170</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19869,7 +19869,7 @@
         <v>46281</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19942,7 +19942,7 @@
         <v>45141</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20015,7 +20015,7 @@
         <v>46195</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20088,7 +20088,7 @@
         <v>45894</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>45670</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20234,7 +20234,7 @@
         <v>45252</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20307,7 +20307,7 @@
         <v>46244</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20380,7 +20380,7 @@
         <v>45700</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20453,7 +20453,7 @@
         <v>46288</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20526,7 +20526,7 @@
         <v>44879</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20599,7 +20599,7 @@
         <v>45474</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20672,7 +20672,7 @@
         <v>44974</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>46248</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20818,7 +20818,7 @@
         <v>45427</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20891,7 +20891,7 @@
         <v>44893</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>45420</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21037,7 +21037,7 @@
         <v>44595</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>44546</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21183,7 +21183,7 @@
         <v>44777</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21256,7 +21256,7 @@
         <v>45574</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21329,7 +21329,7 @@
         <v>46248</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21402,7 +21402,7 @@
         <v>44749</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>46252</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21548,7 +21548,7 @@
         <v>46251</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21621,7 +21621,7 @@
         <v>45415</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>46251</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21767,7 +21767,7 @@
         <v>44895</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21840,7 +21840,7 @@
         <v>46297</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -21913,7 +21913,7 @@
         <v>45159</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -21986,7 +21986,7 @@
         <v>45159</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>45159</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22132,7 +22132,7 @@
         <v>46297</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22205,7 +22205,7 @@
         <v>45388</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>46297</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22351,7 +22351,7 @@
         <v>44623</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22424,7 +22424,7 @@
         <v>46296</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>45034</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>45071</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22648,7 +22648,7 @@
         <v>45776</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22721,7 +22721,7 @@
         <v>46300</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22794,7 +22794,7 @@
         <v>46300</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -22867,7 +22867,7 @@
         <v>45777</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -22940,7 +22940,7 @@
         <v>45777</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23013,7 +23013,7 @@
         <v>45033</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>45338</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23159,7 +23159,7 @@
         <v>46258</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23232,7 +23232,7 @@
         <v>45259</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23305,7 +23305,7 @@
         <v>46259</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23378,7 +23378,7 @@
         <v>46239</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23451,7 +23451,7 @@
         <v>45743</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23524,7 +23524,7 @@
         <v>45740</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23597,7 +23597,7 @@
         <v>45714</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23670,7 +23670,7 @@
         <v>45419</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23748,7 +23748,7 @@
         <v>46262</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23821,7 +23821,7 @@
         <v>45796</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>45799</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -23967,7 +23967,7 @@
         <v>45355</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         <v>45799</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24113,7 +24113,7 @@
         <v>45800</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24186,7 +24186,7 @@
         <v>45247</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
         <v>45805</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24332,7 +24332,7 @@
         <v>46308</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24405,7 +24405,7 @@
         <v>45811</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24478,7 +24478,7 @@
         <v>45598</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24551,7 +24551,7 @@
         <v>45324</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24624,7 +24624,7 @@
         <v>45815</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24697,7 +24697,7 @@
         <v>45831</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24770,7 +24770,7 @@
         <v>45832</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -24843,7 +24843,7 @@
         <v>45835</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -24916,7 +24916,7 @@
         <v>45835</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -24989,7 +24989,7 @@
         <v>45835</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25062,7 +25062,7 @@
         <v>45846</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25135,7 +25135,7 @@
         <v>45875</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25208,7 +25208,7 @@
         <v>45757</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25281,7 +25281,7 @@
         <v>45883</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>45883</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25427,7 +25427,7 @@
         <v>45491</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>

--- a/Översikt FÄRGELANDA.xlsx
+++ b/Översikt FÄRGELANDA.xlsx
@@ -601,7 +601,7 @@
         <v>44785</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45904</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>45303</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44935</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>46239</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>45242</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>45547</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>46175</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>45078</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>44504</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>44453</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>45474</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>45714</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>44911</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>45246</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>45766</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>45153</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>46303</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>44837</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>44490</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>44595</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>44557</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>44490</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>44516</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>44525</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>44526</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>44670</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>44658</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>44602</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>44496</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>44566</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>44684</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>44593</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>44858</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>44550</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>44711</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>44670</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>44518</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>44572</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>44686</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>44490</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         <v>44750</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>44777</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>44490</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>44636</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>45273</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>45315</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>45418</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>45419</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>45558</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         <v>44928</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>45079</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>44581</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         <v>44706</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>44706</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         <v>45091</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>44899</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         <v>45049</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>45384</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>45687</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>44600</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>44998</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>45244</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>44916</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>45740</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>44846</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>45758</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>45196</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>45071</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>45209</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>44488</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>44595</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>45212</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>45321</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>44974</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         <v>44501</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>44578</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6873,7 +6873,7 @@
         <v>44546</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>45180</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>45260</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>45280</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>44939</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7238,7 +7238,7 @@
         <v>44522</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         <v>45351</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7384,7 +7384,7 @@
         <v>45351</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>45015</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
         <v>45049</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         <v>44571</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         <v>45614</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>45036</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>44893</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>44935</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>45693</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
         <v>45582</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>45777</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>45904</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8260,7 +8260,7 @@
         <v>45280</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>45757</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
         <v>45730</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         <v>45638</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8552,7 +8552,7 @@
         <v>45890</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>45950</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8698,7 +8698,7 @@
         <v>45895</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>45894</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         <v>44526</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8917,7 +8917,7 @@
         <v>45252</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>45252</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9063,7 +9063,7 @@
         <v>44578</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9136,7 +9136,7 @@
         <v>45524</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>45642</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9282,7 +9282,7 @@
         <v>45478</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>45904</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>45098</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9501,7 +9501,7 @@
         <v>46038</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>45491</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9647,7 +9647,7 @@
         <v>45362</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>45917</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9793,7 +9793,7 @@
         <v>45918</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9866,7 +9866,7 @@
         <v>45267</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9939,7 +9939,7 @@
         <v>45153</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
         <v>45684</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>45932</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10163,7 +10163,7 @@
         <v>46150</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10236,7 +10236,7 @@
         <v>44896</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10309,7 +10309,7 @@
         <v>45308</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10382,7 +10382,7 @@
         <v>45937</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>45530</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>45761</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
         <v>44917</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10674,7 +10674,7 @@
         <v>44837</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10747,7 +10747,7 @@
         <v>45740</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10820,7 +10820,7 @@
         <v>45452</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10893,7 +10893,7 @@
         <v>45946</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10966,7 +10966,7 @@
         <v>45946</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11039,7 +11039,7 @@
         <v>45949</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11112,7 +11112,7 @@
         <v>45950</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11185,7 +11185,7 @@
         <v>45950</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11258,7 +11258,7 @@
         <v>45643</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11331,7 +11331,7 @@
         <v>45730</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11404,7 +11404,7 @@
         <v>44768</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11477,7 +11477,7 @@
         <v>45957</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11550,7 +11550,7 @@
         <v>45958</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
         <v>45965</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>45965</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11769,7 +11769,7 @@
         <v>45965</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11842,7 +11842,7 @@
         <v>45936</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         <v>45969</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>45969</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12066,7 +12066,7 @@
         <v>45392</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>45293</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
         <v>44638</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12285,7 +12285,7 @@
         <v>45975</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12363,7 +12363,7 @@
         <v>45975</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12441,7 +12441,7 @@
         <v>46166</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12514,7 +12514,7 @@
         <v>44901</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
         <v>45987</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         <v>45989</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>45071</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12806,7 +12806,7 @@
         <v>45558</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12879,7 +12879,7 @@
         <v>45958</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12952,7 +12952,7 @@
         <v>44488</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13025,7 +13025,7 @@
         <v>45558</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13098,7 +13098,7 @@
         <v>45687</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13171,7 +13171,7 @@
         <v>45987</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
         <v>45040</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13317,7 +13317,7 @@
         <v>45420</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
         <v>45078</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>44686</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13536,7 +13536,7 @@
         <v>44958</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13609,7 +13609,7 @@
         <v>46007</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>45643</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13755,7 +13755,7 @@
         <v>45407</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
         <v>45034</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13901,7 +13901,7 @@
         <v>44977</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>45145</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
         <v>45712</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14120,7 +14120,7 @@
         <v>45705</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14193,7 +14193,7 @@
         <v>46037</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14266,7 +14266,7 @@
         <v>46177</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14339,7 +14339,7 @@
         <v>45775</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14412,7 +14412,7 @@
         <v>45764</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14485,7 +14485,7 @@
         <v>46055</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         <v>46052</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14631,7 +14631,7 @@
         <v>46058</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14709,7 +14709,7 @@
         <v>44841</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>44899</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>46063</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14928,7 +14928,7 @@
         <v>45215</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15001,7 +15001,7 @@
         <v>46066</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>45470</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15152,7 +15152,7 @@
         <v>46069</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15230,7 +15230,7 @@
         <v>44869</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15303,7 +15303,7 @@
         <v>46188</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15376,7 +15376,7 @@
         <v>45643</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15449,7 +15449,7 @@
         <v>46069</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15522,7 +15522,7 @@
         <v>46071</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>46071</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15668,7 +15668,7 @@
         <v>45532</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15741,7 +15741,7 @@
         <v>46076</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15819,7 +15819,7 @@
         <v>46080</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15892,7 +15892,7 @@
         <v>46080</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15965,7 +15965,7 @@
         <v>45202</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         <v>46086</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16111,7 +16111,7 @@
         <v>46087</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16184,7 +16184,7 @@
         <v>46190</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16257,7 +16257,7 @@
         <v>46091</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16330,7 +16330,7 @@
         <v>45062</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16403,7 +16403,7 @@
         <v>44893</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16476,7 +16476,7 @@
         <v>46195</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16549,7 +16549,7 @@
         <v>45736</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16622,7 +16622,7 @@
         <v>45139</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16695,7 +16695,7 @@
         <v>46101</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16768,7 +16768,7 @@
         <v>45467</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
         <v>44883</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16914,7 +16914,7 @@
         <v>46107</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16987,7 +16987,7 @@
         <v>46113</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
         <v>44977</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
         <v>46119</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>45685</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17279,7 +17279,7 @@
         <v>46121</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17357,7 +17357,7 @@
         <v>45159</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17430,7 +17430,7 @@
         <v>46121</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17508,7 +17508,7 @@
         <v>46121</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17581,7 +17581,7 @@
         <v>46121</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17659,7 +17659,7 @@
         <v>46121</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>46124</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
         <v>46202</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17883,7 +17883,7 @@
         <v>46125</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17961,7 +17961,7 @@
         <v>46204</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18034,7 +18034,7 @@
         <v>46134</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18107,7 +18107,7 @@
         <v>45218</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>45239</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18253,7 +18253,7 @@
         <v>45894</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18326,7 +18326,7 @@
         <v>45481</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18399,7 +18399,7 @@
         <v>46136</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18472,7 +18472,7 @@
         <v>45693</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18545,7 +18545,7 @@
         <v>46209</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18623,7 +18623,7 @@
         <v>46205</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18701,7 +18701,7 @@
         <v>44544</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18774,7 +18774,7 @@
         <v>44592</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18847,7 +18847,7 @@
         <v>46139</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18920,7 +18920,7 @@
         <v>45168</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18993,7 +18993,7 @@
         <v>44811</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>44917</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>45643</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19212,7 +19212,7 @@
         <v>45049</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19285,7 +19285,7 @@
         <v>45237</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>46156</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19431,7 +19431,7 @@
         <v>44873</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>46279</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19577,7 +19577,7 @@
         <v>45271</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         <v>45532</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19723,7 +19723,7 @@
         <v>45324</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19796,7 +19796,7 @@
         <v>45170</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19869,7 +19869,7 @@
         <v>46281</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19942,7 +19942,7 @@
         <v>45141</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20015,7 +20015,7 @@
         <v>46195</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20088,7 +20088,7 @@
         <v>45894</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>45670</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20234,7 +20234,7 @@
         <v>45252</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20307,7 +20307,7 @@
         <v>46244</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20380,7 +20380,7 @@
         <v>45700</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20453,7 +20453,7 @@
         <v>46288</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20526,7 +20526,7 @@
         <v>44879</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20599,7 +20599,7 @@
         <v>45474</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20672,7 +20672,7 @@
         <v>44974</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>46248</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20818,7 +20818,7 @@
         <v>45427</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20891,7 +20891,7 @@
         <v>44893</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>45420</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21037,7 +21037,7 @@
         <v>44595</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>44546</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21183,7 +21183,7 @@
         <v>44777</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21256,7 +21256,7 @@
         <v>45574</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21329,7 +21329,7 @@
         <v>46248</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21402,7 +21402,7 @@
         <v>44749</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>46252</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21548,7 +21548,7 @@
         <v>46251</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21621,7 +21621,7 @@
         <v>45415</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>46251</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21767,7 +21767,7 @@
         <v>44895</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21840,7 +21840,7 @@
         <v>46297</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -21913,7 +21913,7 @@
         <v>45159</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -21986,7 +21986,7 @@
         <v>45159</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>45159</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22132,7 +22132,7 @@
         <v>46297</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22205,7 +22205,7 @@
         <v>45388</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>46297</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22351,7 +22351,7 @@
         <v>44623</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22424,7 +22424,7 @@
         <v>46296</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>45034</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>45071</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22648,7 +22648,7 @@
         <v>45776</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22721,7 +22721,7 @@
         <v>46300</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22794,7 +22794,7 @@
         <v>46300</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -22867,7 +22867,7 @@
         <v>45777</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -22940,7 +22940,7 @@
         <v>45777</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23013,7 +23013,7 @@
         <v>45033</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>45338</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23159,7 +23159,7 @@
         <v>46258</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23232,7 +23232,7 @@
         <v>45259</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23305,7 +23305,7 @@
         <v>46259</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23378,7 +23378,7 @@
         <v>46239</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23451,7 +23451,7 @@
         <v>45743</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23524,7 +23524,7 @@
         <v>45740</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23597,7 +23597,7 @@
         <v>45714</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23670,7 +23670,7 @@
         <v>45419</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23748,7 +23748,7 @@
         <v>46262</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23821,7 +23821,7 @@
         <v>45796</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>45799</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -23967,7 +23967,7 @@
         <v>45355</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         <v>45799</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24113,7 +24113,7 @@
         <v>45800</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24186,7 +24186,7 @@
         <v>45247</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
         <v>45805</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24332,7 +24332,7 @@
         <v>46308</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24405,7 +24405,7 @@
         <v>45811</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24478,7 +24478,7 @@
         <v>45598</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24551,7 +24551,7 @@
         <v>45324</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24624,7 +24624,7 @@
         <v>45815</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24697,7 +24697,7 @@
         <v>45831</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24770,7 +24770,7 @@
         <v>45832</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -24843,7 +24843,7 @@
         <v>45835</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -24916,7 +24916,7 @@
         <v>45835</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -24989,7 +24989,7 @@
         <v>45835</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25062,7 +25062,7 @@
         <v>45846</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25135,7 +25135,7 @@
         <v>45875</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25208,7 +25208,7 @@
         <v>45757</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25281,7 +25281,7 @@
         <v>45883</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>45883</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25427,7 +25427,7 @@
         <v>45491</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>

--- a/Översikt FÄRGELANDA.xlsx
+++ b/Översikt FÄRGELANDA.xlsx
@@ -601,7 +601,7 @@
         <v>44785</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45904</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>45303</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>46239</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>44935</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>45242</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>44504</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>45547</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>46175</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>45078</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>44453</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>45474</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>45714</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>45246</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>45766</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>46303</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>44911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>45153</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>44837</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>44595</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>44557</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>44516</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>44525</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>44526</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>44670</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>44658</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>44602</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>44496</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>44566</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>44684</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>44593</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>44858</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>44550</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>44711</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>44670</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>44518</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>44572</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>44686</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>44750</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>44777</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>44636</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         <v>45034</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>45244</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>45757</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>45883</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>45890</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>45071</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>45894</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>45895</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         <v>44595</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>45308</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>44811</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         <v>45700</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>44883</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         <v>45904</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>44706</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5335,7 +5335,7 @@
         <v>44917</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>45736</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
         <v>45427</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>45614</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5627,7 +5627,7 @@
         <v>44935</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5700,7 +5700,7 @@
         <v>44928</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         <v>45917</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>45712</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5919,7 +5919,7 @@
         <v>45918</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5992,7 +5992,7 @@
         <v>45392</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6065,7 +6065,7 @@
         <v>46166</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>45049</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
         <v>45168</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
         <v>44846</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6357,7 +6357,7 @@
         <v>45558</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
         <v>45558</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6503,7 +6503,7 @@
         <v>45418</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>45036</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>44896</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         <v>45932</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>45937</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6873,7 +6873,7 @@
         <v>45324</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>44974</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>45384</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>46177</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>45139</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7238,7 +7238,7 @@
         <v>45946</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         <v>45419</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7384,7 +7384,7 @@
         <v>45239</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>44958</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
         <v>45946</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         <v>44837</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         <v>45530</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>45950</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>45950</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>45949</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>45761</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
         <v>45415</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>45957</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>45764</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8260,7 +8260,7 @@
         <v>45740</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>45958</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
         <v>46188</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         <v>45965</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8552,7 +8552,7 @@
         <v>45965</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>45965</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8698,7 +8698,7 @@
         <v>46190</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>46195</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         <v>45049</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8917,7 +8917,7 @@
         <v>45969</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>45969</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9063,7 +9063,7 @@
         <v>45524</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9136,7 +9136,7 @@
         <v>45474</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>45705</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9282,7 +9282,7 @@
         <v>45975</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>45975</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
         <v>46202</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         <v>45574</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
         <v>44777</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>44571</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9735,7 +9735,7 @@
         <v>45141</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9808,7 +9808,7 @@
         <v>45670</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9881,7 +9881,7 @@
         <v>45159</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>46204</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10027,7 +10027,7 @@
         <v>45280</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         <v>45321</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10173,7 +10173,7 @@
         <v>46205</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         <v>45643</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>44546</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         <v>45987</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>46209</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>45407</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10621,7 +10621,7 @@
         <v>45687</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10694,7 +10694,7 @@
         <v>45273</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>45989</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10840,7 +10840,7 @@
         <v>45958</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
         <v>45730</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10986,7 +10986,7 @@
         <v>46139</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>45740</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11132,7 +11132,7 @@
         <v>45776</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>45987</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         <v>45777</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11351,7 +11351,7 @@
         <v>45777</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11424,7 +11424,7 @@
         <v>45033</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>46007</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>46156</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11643,7 +11643,7 @@
         <v>46279</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
         <v>45338</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>45259</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>45714</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>45743</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>45740</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12081,7 +12081,7 @@
         <v>46281</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12154,7 +12154,7 @@
         <v>46037</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12227,7 +12227,7 @@
         <v>45796</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>45419</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>45355</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12451,7 +12451,7 @@
         <v>46244</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>46195</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>45894</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12670,7 +12670,7 @@
         <v>45799</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12743,7 +12743,7 @@
         <v>45800</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>45799</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12889,7 +12889,7 @@
         <v>46052</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>45805</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
         <v>45598</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13108,7 +13108,7 @@
         <v>46055</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>46058</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13259,7 +13259,7 @@
         <v>45324</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13332,7 +13332,7 @@
         <v>46248</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13405,7 +13405,7 @@
         <v>45811</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13478,7 +13478,7 @@
         <v>46063</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13551,7 +13551,7 @@
         <v>46248</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13624,7 +13624,7 @@
         <v>46066</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13702,7 +13702,7 @@
         <v>46069</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
         <v>45815</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13848,7 +13848,7 @@
         <v>46069</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13926,7 +13926,7 @@
         <v>46071</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13999,7 +13999,7 @@
         <v>46296</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14077,7 +14077,7 @@
         <v>46071</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>46251</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14223,7 +14223,7 @@
         <v>46076</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14301,7 +14301,7 @@
         <v>46252</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14374,7 +14374,7 @@
         <v>46080</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14447,7 +14447,7 @@
         <v>46080</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
         <v>46251</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14593,7 +14593,7 @@
         <v>45832</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>45831</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>46086</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14812,7 +14812,7 @@
         <v>46087</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14885,7 +14885,7 @@
         <v>44526</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         <v>46297</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15031,7 +15031,7 @@
         <v>46091</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15104,7 +15104,7 @@
         <v>45835</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15177,7 +15177,7 @@
         <v>45835</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>45835</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15323,7 +15323,7 @@
         <v>46297</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15396,7 +15396,7 @@
         <v>46297</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15469,7 +15469,7 @@
         <v>46300</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15542,7 +15542,7 @@
         <v>46300</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15615,7 +15615,7 @@
         <v>45846</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15688,7 +15688,7 @@
         <v>46101</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15761,7 +15761,7 @@
         <v>46239</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15834,7 +15834,7 @@
         <v>46107</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15907,7 +15907,7 @@
         <v>46259</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15980,7 +15980,7 @@
         <v>46258</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16053,7 +16053,7 @@
         <v>46113</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>45280</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16199,7 +16199,7 @@
         <v>46119</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         <v>46121</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16350,7 +16350,7 @@
         <v>46121</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16428,7 +16428,7 @@
         <v>46121</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>46121</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16579,7 +16579,7 @@
         <v>46121</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16652,7 +16652,7 @@
         <v>45420</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16725,7 +16725,7 @@
         <v>46125</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16803,7 +16803,7 @@
         <v>46124</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16876,7 +16876,7 @@
         <v>45875</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16949,7 +16949,7 @@
         <v>45757</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17022,7 +17022,7 @@
         <v>44901</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17095,7 +17095,7 @@
         <v>46308</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17168,7 +17168,7 @@
         <v>46262</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17241,7 +17241,7 @@
         <v>45452</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17314,7 +17314,7 @@
         <v>44893</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>44899</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17460,7 +17460,7 @@
         <v>44899</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17533,7 +17533,7 @@
         <v>46134</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17606,7 +17606,7 @@
         <v>45362</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17679,7 +17679,7 @@
         <v>45883</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17752,7 +17752,7 @@
         <v>45481</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17825,7 +17825,7 @@
         <v>45491</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>45247</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17971,7 +17971,7 @@
         <v>46136</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18044,7 +18044,7 @@
         <v>44544</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         <v>45904</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18190,7 +18190,7 @@
         <v>45730</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18263,7 +18263,7 @@
         <v>46311</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18336,7 +18336,7 @@
         <v>45777</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18409,7 +18409,7 @@
         <v>44939</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18482,7 +18482,7 @@
         <v>45693</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18555,7 +18555,7 @@
         <v>45351</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18628,7 +18628,7 @@
         <v>45351</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18701,7 +18701,7 @@
         <v>46288</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18774,7 +18774,7 @@
         <v>45478</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18847,7 +18847,7 @@
         <v>45894</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18920,7 +18920,7 @@
         <v>46038</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18993,7 +18993,7 @@
         <v>45693</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>45950</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>44977</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19212,7 +19212,7 @@
         <v>44578</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19285,7 +19285,7 @@
         <v>44600</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>44592</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19431,7 +19431,7 @@
         <v>46316</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>44917</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19577,7 +19577,7 @@
         <v>46316</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         <v>45642</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19723,7 +19723,7 @@
         <v>45071</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19796,7 +19796,7 @@
         <v>46150</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19869,7 +19869,7 @@
         <v>45049</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19942,7 +19942,7 @@
         <v>44638</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20015,7 +20015,7 @@
         <v>45558</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20088,7 +20088,7 @@
         <v>45271</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>45936</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20239,7 +20239,7 @@
         <v>45079</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20312,7 +20312,7 @@
         <v>45643</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20385,7 +20385,7 @@
         <v>45643</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20458,7 +20458,7 @@
         <v>44998</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20531,7 +20531,7 @@
         <v>45638</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20604,7 +20604,7 @@
         <v>45145</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20677,7 +20677,7 @@
         <v>44977</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20750,7 +20750,7 @@
         <v>45098</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20823,7 +20823,7 @@
         <v>45687</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20896,7 +20896,7 @@
         <v>44522</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20969,7 +20969,7 @@
         <v>45775</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21042,7 +21042,7 @@
         <v>45071</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21115,7 +21115,7 @@
         <v>44916</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21188,7 +21188,7 @@
         <v>45532</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21261,7 +21261,7 @@
         <v>45260</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21334,7 +21334,7 @@
         <v>45212</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21407,7 +21407,7 @@
         <v>44895</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21480,7 +21480,7 @@
         <v>45252</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
         <v>45252</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21626,7 +21626,7 @@
         <v>44873</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21699,7 +21699,7 @@
         <v>45015</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>45758</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21845,7 +21845,7 @@
         <v>45237</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>44578</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -21991,7 +21991,7 @@
         <v>45062</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22064,7 +22064,7 @@
         <v>45078</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22137,7 +22137,7 @@
         <v>44974</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22210,7 +22210,7 @@
         <v>45040</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22283,7 +22283,7 @@
         <v>45470</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22356,7 +22356,7 @@
         <v>45582</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>45388</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>44893</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>45467</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22648,7 +22648,7 @@
         <v>45034</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22721,7 +22721,7 @@
         <v>44581</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22794,7 +22794,7 @@
         <v>45643</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -22867,7 +22867,7 @@
         <v>44595</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -22940,7 +22940,7 @@
         <v>45153</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23013,7 +23013,7 @@
         <v>45170</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>45315</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23159,7 +23159,7 @@
         <v>45091</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23232,7 +23232,7 @@
         <v>45180</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23305,7 +23305,7 @@
         <v>45684</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23383,7 +23383,7 @@
         <v>45209</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23456,7 +23456,7 @@
         <v>44686</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>45218</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23602,7 +23602,7 @@
         <v>44749</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23675,7 +23675,7 @@
         <v>45420</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23748,7 +23748,7 @@
         <v>44841</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23821,7 +23821,7 @@
         <v>45159</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>45159</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -23967,7 +23967,7 @@
         <v>45159</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         <v>45252</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24113,7 +24113,7 @@
         <v>45215</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24186,7 +24186,7 @@
         <v>45532</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
         <v>44768</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24332,7 +24332,7 @@
         <v>44706</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24405,7 +24405,7 @@
         <v>45196</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24478,7 +24478,7 @@
         <v>44869</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24551,7 +24551,7 @@
         <v>44893</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24624,7 +24624,7 @@
         <v>44623</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24697,7 +24697,7 @@
         <v>45293</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24770,7 +24770,7 @@
         <v>45202</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -24843,7 +24843,7 @@
         <v>44879</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -24916,7 +24916,7 @@
         <v>44546</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -24989,7 +24989,7 @@
         <v>45267</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25062,7 +25062,7 @@
         <v>45685</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25135,7 +25135,7 @@
         <v>44501</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25208,7 +25208,7 @@
         <v>45491</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>

--- a/Översikt FÄRGELANDA.xlsx
+++ b/Översikt FÄRGELANDA.xlsx
@@ -601,7 +601,7 @@
         <v>44785</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45904</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>45303</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>46239</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>44935</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>45242</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>44504</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>45547</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>46175</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>45078</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>44453</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>45474</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>45714</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>45246</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>45766</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>46303</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>44911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>45153</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>44837</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>44595</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>44557</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>44516</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>44525</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>44526</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>44670</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>44658</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>44602</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>44496</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>44566</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>44684</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>44593</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>44858</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>44550</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>44711</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>44670</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>44518</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>44572</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>44686</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>44750</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>44777</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>44636</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         <v>45034</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>45244</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>45757</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>45883</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>45890</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>45071</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>45894</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>45895</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         <v>44595</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>45308</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>44811</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         <v>45700</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>44883</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         <v>45904</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>44706</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5335,7 +5335,7 @@
         <v>44917</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>45736</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
         <v>45427</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>45614</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5627,7 +5627,7 @@
         <v>44935</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5700,7 +5700,7 @@
         <v>44928</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         <v>45917</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>45712</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5919,7 +5919,7 @@
         <v>45918</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5992,7 +5992,7 @@
         <v>45392</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6065,7 +6065,7 @@
         <v>46166</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>45049</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
         <v>45168</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
         <v>44846</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6357,7 +6357,7 @@
         <v>45558</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
         <v>45558</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6503,7 +6503,7 @@
         <v>45418</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>45036</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>44896</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         <v>45932</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>45937</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6873,7 +6873,7 @@
         <v>45324</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>44974</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>45384</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>46177</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>45139</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7238,7 +7238,7 @@
         <v>45946</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         <v>45419</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7384,7 +7384,7 @@
         <v>45239</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>44958</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
         <v>45946</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         <v>44837</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         <v>45530</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>45950</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>45950</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>45949</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>45761</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
         <v>45415</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>45957</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>45764</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8260,7 +8260,7 @@
         <v>45740</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>45958</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
         <v>46188</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         <v>45965</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8552,7 +8552,7 @@
         <v>45965</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>45965</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8698,7 +8698,7 @@
         <v>46190</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>46195</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         <v>45049</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8917,7 +8917,7 @@
         <v>45969</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>45969</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9063,7 +9063,7 @@
         <v>45524</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9136,7 +9136,7 @@
         <v>45474</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>45705</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9282,7 +9282,7 @@
         <v>45975</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>45975</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
         <v>46202</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         <v>45574</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
         <v>44777</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>44571</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9735,7 +9735,7 @@
         <v>45141</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9808,7 +9808,7 @@
         <v>45670</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9881,7 +9881,7 @@
         <v>45159</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>46204</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10027,7 +10027,7 @@
         <v>45280</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         <v>45321</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10173,7 +10173,7 @@
         <v>46205</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         <v>45643</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>44546</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         <v>45987</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>46209</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>45407</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10621,7 +10621,7 @@
         <v>45687</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10694,7 +10694,7 @@
         <v>45273</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>45989</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10840,7 +10840,7 @@
         <v>45958</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
         <v>45730</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10986,7 +10986,7 @@
         <v>46139</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>45740</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11132,7 +11132,7 @@
         <v>45776</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>45987</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         <v>45777</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11351,7 +11351,7 @@
         <v>45777</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11424,7 +11424,7 @@
         <v>45033</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>46007</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>46156</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11643,7 +11643,7 @@
         <v>46279</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
         <v>45338</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>45259</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>45714</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>45743</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>45740</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12081,7 +12081,7 @@
         <v>46281</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12154,7 +12154,7 @@
         <v>46037</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12227,7 +12227,7 @@
         <v>45796</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>45419</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>45355</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12451,7 +12451,7 @@
         <v>46244</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>46195</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>45894</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12670,7 +12670,7 @@
         <v>45799</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12743,7 +12743,7 @@
         <v>45800</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>45799</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12889,7 +12889,7 @@
         <v>46052</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>45805</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
         <v>45598</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13108,7 +13108,7 @@
         <v>46055</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>46058</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13259,7 +13259,7 @@
         <v>45324</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13332,7 +13332,7 @@
         <v>46248</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13405,7 +13405,7 @@
         <v>45811</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13478,7 +13478,7 @@
         <v>46063</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13551,7 +13551,7 @@
         <v>46248</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13624,7 +13624,7 @@
         <v>46066</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13702,7 +13702,7 @@
         <v>46069</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
         <v>45815</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13848,7 +13848,7 @@
         <v>46069</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13926,7 +13926,7 @@
         <v>46071</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13999,7 +13999,7 @@
         <v>46296</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14077,7 +14077,7 @@
         <v>46071</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>46251</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14223,7 +14223,7 @@
         <v>46076</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14301,7 +14301,7 @@
         <v>46252</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14374,7 +14374,7 @@
         <v>46080</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14447,7 +14447,7 @@
         <v>46080</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
         <v>46251</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14593,7 +14593,7 @@
         <v>45832</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>45831</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>46086</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14812,7 +14812,7 @@
         <v>46087</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14885,7 +14885,7 @@
         <v>44526</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         <v>46297</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15031,7 +15031,7 @@
         <v>46091</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15104,7 +15104,7 @@
         <v>45835</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15177,7 +15177,7 @@
         <v>45835</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>45835</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15323,7 +15323,7 @@
         <v>46297</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15396,7 +15396,7 @@
         <v>46297</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15469,7 +15469,7 @@
         <v>46300</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15542,7 +15542,7 @@
         <v>46300</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15615,7 +15615,7 @@
         <v>45846</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15688,7 +15688,7 @@
         <v>46101</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15761,7 +15761,7 @@
         <v>46239</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15834,7 +15834,7 @@
         <v>46107</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15907,7 +15907,7 @@
         <v>46259</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15980,7 +15980,7 @@
         <v>46258</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16053,7 +16053,7 @@
         <v>46113</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>45280</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16199,7 +16199,7 @@
         <v>46119</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         <v>46121</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16350,7 +16350,7 @@
         <v>46121</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16428,7 +16428,7 @@
         <v>46121</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>46121</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16579,7 +16579,7 @@
         <v>46121</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16652,7 +16652,7 @@
         <v>45420</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16725,7 +16725,7 @@
         <v>46125</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16803,7 +16803,7 @@
         <v>46124</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16876,7 +16876,7 @@
         <v>45875</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16949,7 +16949,7 @@
         <v>45757</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17022,7 +17022,7 @@
         <v>44901</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17095,7 +17095,7 @@
         <v>46308</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17168,7 +17168,7 @@
         <v>46262</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17241,7 +17241,7 @@
         <v>45452</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17314,7 +17314,7 @@
         <v>44893</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>44899</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17460,7 +17460,7 @@
         <v>44899</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17533,7 +17533,7 @@
         <v>46134</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17606,7 +17606,7 @@
         <v>45362</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17679,7 +17679,7 @@
         <v>45883</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17752,7 +17752,7 @@
         <v>45481</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17825,7 +17825,7 @@
         <v>45491</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>45247</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17971,7 +17971,7 @@
         <v>46136</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18044,7 +18044,7 @@
         <v>44544</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         <v>45904</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18190,7 +18190,7 @@
         <v>45730</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18263,7 +18263,7 @@
         <v>46311</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18336,7 +18336,7 @@
         <v>45777</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18409,7 +18409,7 @@
         <v>44939</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18482,7 +18482,7 @@
         <v>45693</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18555,7 +18555,7 @@
         <v>45351</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18628,7 +18628,7 @@
         <v>45351</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18701,7 +18701,7 @@
         <v>46288</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18774,7 +18774,7 @@
         <v>45478</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18847,7 +18847,7 @@
         <v>45894</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18920,7 +18920,7 @@
         <v>46038</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18993,7 +18993,7 @@
         <v>45693</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>45950</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>44977</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19212,7 +19212,7 @@
         <v>44578</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19285,7 +19285,7 @@
         <v>44600</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>44592</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19431,7 +19431,7 @@
         <v>46316</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>44917</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19577,7 +19577,7 @@
         <v>46316</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         <v>45642</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19723,7 +19723,7 @@
         <v>45071</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19796,7 +19796,7 @@
         <v>46150</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19869,7 +19869,7 @@
         <v>45049</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19942,7 +19942,7 @@
         <v>44638</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20015,7 +20015,7 @@
         <v>45558</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20088,7 +20088,7 @@
         <v>45271</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>45936</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20239,7 +20239,7 @@
         <v>45079</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20312,7 +20312,7 @@
         <v>45643</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20385,7 +20385,7 @@
         <v>45643</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20458,7 +20458,7 @@
         <v>44998</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20531,7 +20531,7 @@
         <v>45638</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20604,7 +20604,7 @@
         <v>45145</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20677,7 +20677,7 @@
         <v>44977</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20750,7 +20750,7 @@
         <v>45098</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20823,7 +20823,7 @@
         <v>45687</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20896,7 +20896,7 @@
         <v>44522</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20969,7 +20969,7 @@
         <v>45775</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21042,7 +21042,7 @@
         <v>45071</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21115,7 +21115,7 @@
         <v>44916</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21188,7 +21188,7 @@
         <v>45532</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21261,7 +21261,7 @@
         <v>45260</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21334,7 +21334,7 @@
         <v>45212</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21407,7 +21407,7 @@
         <v>44895</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21480,7 +21480,7 @@
         <v>45252</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
         <v>45252</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21626,7 +21626,7 @@
         <v>44873</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21699,7 +21699,7 @@
         <v>45015</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>45758</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21845,7 +21845,7 @@
         <v>45237</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>44578</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -21991,7 +21991,7 @@
         <v>45062</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22064,7 +22064,7 @@
         <v>45078</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22137,7 +22137,7 @@
         <v>44974</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22210,7 +22210,7 @@
         <v>45040</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22283,7 +22283,7 @@
         <v>45470</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22356,7 +22356,7 @@
         <v>45582</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>45388</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>44893</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>45467</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22648,7 +22648,7 @@
         <v>45034</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22721,7 +22721,7 @@
         <v>44581</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22794,7 +22794,7 @@
         <v>45643</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -22867,7 +22867,7 @@
         <v>44595</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -22940,7 +22940,7 @@
         <v>45153</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23013,7 +23013,7 @@
         <v>45170</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>45315</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23159,7 +23159,7 @@
         <v>45091</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23232,7 +23232,7 @@
         <v>45180</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23305,7 +23305,7 @@
         <v>45684</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23383,7 +23383,7 @@
         <v>45209</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23456,7 +23456,7 @@
         <v>44686</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>45218</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23602,7 +23602,7 @@
         <v>44749</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23675,7 +23675,7 @@
         <v>45420</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23748,7 +23748,7 @@
         <v>44841</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23821,7 +23821,7 @@
         <v>45159</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>45159</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -23967,7 +23967,7 @@
         <v>45159</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         <v>45252</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24113,7 +24113,7 @@
         <v>45215</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24186,7 +24186,7 @@
         <v>45532</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
         <v>44768</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24332,7 +24332,7 @@
         <v>44706</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24405,7 +24405,7 @@
         <v>45196</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24478,7 +24478,7 @@
         <v>44869</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24551,7 +24551,7 @@
         <v>44893</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24624,7 +24624,7 @@
         <v>44623</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24697,7 +24697,7 @@
         <v>45293</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24770,7 +24770,7 @@
         <v>45202</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -24843,7 +24843,7 @@
         <v>44879</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -24916,7 +24916,7 @@
         <v>44546</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -24989,7 +24989,7 @@
         <v>45267</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25062,7 +25062,7 @@
         <v>45685</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25135,7 +25135,7 @@
         <v>44501</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25208,7 +25208,7 @@
         <v>45491</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
